--- a/2026/PCB/WheelVoltageBooster/LM5170_DESIGN-CALC_V1.1.0.xlsx
+++ b/2026/PCB/WheelVoltageBooster/LM5170_DESIGN-CALC_V1.1.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tsukigake/Documents/GitHub/ssl-Circuit/2026/PCB/WheelVoltageBooster/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90A43CD5-DA1E-4A44-9446-484B46DF6CA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DC2F4CE-B180-E449-8FB8-69432284C240}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="FTbea0zNh/M4QFFIjkWMzUxKnz4OFezzA9/BRwWSIIMWDYlyn+LFccWDum1tXS3mgTwJKFr3ZBSW6d5DYWBVMg==" workbookSaltValue="UMfWwVJIqsWZTSD9g7ReYQ==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="1400" yWindow="880" windowWidth="32800" windowHeight="21360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
@@ -3495,7 +3495,7 @@
           <rPr>
             <b/>
             <sz val="9"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -3506,7 +3506,7 @@
             <b/>
             <vertAlign val="subscript"/>
             <sz val="9"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -3516,7 +3516,7 @@
           <rPr>
             <b/>
             <sz val="9"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -3525,8 +3525,19 @@
         </r>
         <r>
           <rPr>
+            <b/>
             <sz val="9"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -3566,7 +3577,7 @@
           <rPr>
             <b/>
             <sz val="9"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -3575,8 +3586,19 @@
         </r>
         <r>
           <rPr>
+            <b/>
             <sz val="9"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -3590,7 +3612,7 @@
           <rPr>
             <b/>
             <sz val="9"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -3600,12 +3622,21 @@
         <r>
           <rPr>
             <sz val="9"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-This is the UVLO input rail voltage at which an Undervoltage event occurs. If the input rail voltage is less than this value the LM5170 is in standby mode.</t>
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>This is the UVLO input rail voltage at which an Undervoltage event occurs. If the input rail voltage is less than this value the LM5170 is in standby mode.</t>
         </r>
       </text>
     </comment>
@@ -3615,7 +3646,7 @@
           <rPr>
             <b/>
             <sz val="9"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -3624,8 +3655,19 @@
         </r>
         <r>
           <rPr>
+            <b/>
             <sz val="9"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -3635,7 +3677,7 @@
           <rPr>
             <b/>
             <sz val="9"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -4467,7 +4509,7 @@
           <rPr>
             <b/>
             <sz val="9"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -4476,12 +4518,31 @@
         <r>
           <rPr>
             <sz val="9"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-This is the dead time between the LO and HO signal</t>
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>This is the dead time between the LO and HO signal</t>
         </r>
       </text>
     </comment>
@@ -5757,7 +5818,7 @@
           <rPr>
             <b/>
             <sz val="9"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -5768,7 +5829,7 @@
             <b/>
             <vertAlign val="subscript"/>
             <sz val="9"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -5778,7 +5839,7 @@
           <rPr>
             <b/>
             <sz val="9"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -5788,18 +5849,27 @@
         <r>
           <rPr>
             <sz val="9"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-This is the location of the zero in the compensation network based upon the selection of R</t>
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>This is the location of the zero in the compensation network based upon the selection of R</t>
         </r>
         <r>
           <rPr>
             <vertAlign val="subscript"/>
             <sz val="9"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -5808,7 +5878,7 @@
         <r>
           <rPr>
             <sz val="9"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -5818,7 +5888,7 @@
           <rPr>
             <vertAlign val="subscript"/>
             <sz val="9"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -5827,7 +5897,7 @@
         <r>
           <rPr>
             <sz val="9"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -6234,7 +6304,7 @@
           <rPr>
             <b/>
             <sz val="9"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -6245,7 +6315,7 @@
             <b/>
             <vertAlign val="subscript"/>
             <sz val="9"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -6255,7 +6325,7 @@
           <rPr>
             <b/>
             <sz val="9"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -6264,8 +6334,19 @@
         </r>
         <r>
           <rPr>
+            <b/>
             <sz val="9"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -6275,7 +6356,7 @@
           <rPr>
             <vertAlign val="subscript"/>
             <sz val="9"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -6284,7 +6365,7 @@
         <r>
           <rPr>
             <sz val="9"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -11504,6 +11585,26 @@
       <alignment horizontal="left"/>
       <protection hidden="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection hidden="1"/>
@@ -11515,6 +11616,14 @@
     <xf numFmtId="0" fontId="7" fillId="8" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0" hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
@@ -11536,34 +11645,6 @@
       <alignment horizontal="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -11581,6 +11662,18 @@
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -11604,39 +11697,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
@@ -11655,6 +11721,21 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
@@ -31310,16 +31391,16 @@
     <col min="20" max="16384" width="9.1640625" style="128"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" s="178" customFormat="1">
-      <c r="A1" s="177" t="s">
+    <row r="1" spans="1:22" s="185" customFormat="1">
+      <c r="A1" s="184" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="2" spans="1:22" s="180" customFormat="1">
-      <c r="A2" s="179"/>
+    <row r="2" spans="1:22" s="187" customFormat="1">
+      <c r="A2" s="186"/>
     </row>
-    <row r="3" spans="1:22" s="180" customFormat="1" ht="12.75" customHeight="1">
-      <c r="A3" s="179"/>
+    <row r="3" spans="1:22" s="187" customFormat="1" ht="12.75" customHeight="1">
+      <c r="A3" s="186"/>
     </row>
     <row r="4" spans="1:22" s="116" customFormat="1" ht="15" thickBot="1">
       <c r="A4" s="115"/>
@@ -31453,21 +31534,21 @@
       <c r="V9" s="129"/>
     </row>
     <row r="10" spans="1:22" ht="17.25" customHeight="1" thickBot="1">
-      <c r="A10" s="174" t="s">
+      <c r="A10" s="179" t="s">
         <v>321</v>
       </c>
-      <c r="B10" s="175"/>
-      <c r="C10" s="176"/>
+      <c r="B10" s="180"/>
+      <c r="C10" s="181"/>
       <c r="F10" s="129"/>
-      <c r="G10" s="184" t="s">
+      <c r="G10" s="174" t="s">
         <v>281</v>
       </c>
-      <c r="H10" s="184"/>
-      <c r="I10" s="184"/>
-      <c r="J10" s="184"/>
-      <c r="K10" s="184"/>
-      <c r="L10" s="184"/>
-      <c r="M10" s="184"/>
+      <c r="H10" s="174"/>
+      <c r="I10" s="174"/>
+      <c r="J10" s="174"/>
+      <c r="K10" s="174"/>
+      <c r="L10" s="174"/>
+      <c r="M10" s="174"/>
       <c r="N10" s="132"/>
       <c r="O10" s="132"/>
       <c r="P10" s="129"/>
@@ -31489,13 +31570,13 @@
         <v>1</v>
       </c>
       <c r="F11" s="129"/>
-      <c r="G11" s="184"/>
-      <c r="H11" s="184"/>
-      <c r="I11" s="184"/>
-      <c r="J11" s="184"/>
-      <c r="K11" s="184"/>
-      <c r="L11" s="184"/>
-      <c r="M11" s="184"/>
+      <c r="G11" s="174"/>
+      <c r="H11" s="174"/>
+      <c r="I11" s="174"/>
+      <c r="J11" s="174"/>
+      <c r="K11" s="174"/>
+      <c r="L11" s="174"/>
+      <c r="M11" s="174"/>
       <c r="N11" s="132"/>
       <c r="O11" s="132"/>
       <c r="Q11" s="129"/>
@@ -31573,11 +31654,11 @@
       <c r="V14" s="129"/>
     </row>
     <row r="15" spans="1:22" ht="15" thickBot="1">
-      <c r="A15" s="174" t="s">
+      <c r="A15" s="179" t="s">
         <v>320</v>
       </c>
-      <c r="B15" s="175"/>
-      <c r="C15" s="176"/>
+      <c r="B15" s="180"/>
+      <c r="C15" s="181"/>
       <c r="F15" s="129"/>
       <c r="G15" s="129"/>
       <c r="H15" s="129"/>
@@ -31701,11 +31782,11 @@
       <c r="V19" s="129"/>
     </row>
     <row r="20" spans="1:22" ht="15" thickBot="1">
-      <c r="A20" s="174" t="s">
+      <c r="A20" s="179" t="s">
         <v>2</v>
       </c>
-      <c r="B20" s="175"/>
-      <c r="C20" s="176"/>
+      <c r="B20" s="180"/>
+      <c r="C20" s="181"/>
       <c r="F20" s="129"/>
       <c r="G20" s="129"/>
       <c r="H20" s="129"/>
@@ -31801,11 +31882,11 @@
       <c r="V23" s="129"/>
     </row>
     <row r="24" spans="1:22" ht="15" thickBot="1">
-      <c r="A24" s="174" t="s">
+      <c r="A24" s="179" t="s">
         <v>282</v>
       </c>
-      <c r="B24" s="175"/>
-      <c r="C24" s="176"/>
+      <c r="B24" s="180"/>
+      <c r="C24" s="181"/>
       <c r="F24" s="129"/>
       <c r="G24" s="129"/>
       <c r="H24" s="129"/>
@@ -31994,9 +32075,9 @@
       <c r="V30" s="129"/>
     </row>
     <row r="31" spans="1:22" ht="17">
-      <c r="A31" s="181"/>
-      <c r="B31" s="181"/>
-      <c r="C31" s="181"/>
+      <c r="A31" s="188"/>
+      <c r="B31" s="188"/>
+      <c r="C31" s="188"/>
       <c r="F31" s="129"/>
       <c r="G31" s="129"/>
       <c r="H31" s="129"/>
@@ -32062,11 +32143,11 @@
       <c r="V33" s="129"/>
     </row>
     <row r="34" spans="1:22" ht="15" thickBot="1">
-      <c r="A34" s="174" t="s">
+      <c r="A34" s="179" t="s">
         <v>9</v>
       </c>
-      <c r="B34" s="175"/>
-      <c r="C34" s="176"/>
+      <c r="B34" s="180"/>
+      <c r="C34" s="181"/>
       <c r="F34" s="129"/>
       <c r="G34" s="129"/>
       <c r="H34" s="129"/>
@@ -32295,11 +32376,11 @@
       <c r="V42" s="129"/>
     </row>
     <row r="43" spans="1:22" ht="15" thickBot="1">
-      <c r="A43" s="174" t="s">
+      <c r="A43" s="179" t="s">
         <v>287</v>
       </c>
-      <c r="B43" s="175"/>
-      <c r="C43" s="176"/>
+      <c r="B43" s="180"/>
+      <c r="C43" s="181"/>
       <c r="F43" s="129"/>
       <c r="G43" s="129"/>
       <c r="H43" s="129"/>
@@ -32526,11 +32607,11 @@
       <c r="V51" s="129"/>
     </row>
     <row r="52" spans="1:22" ht="15" thickBot="1">
-      <c r="A52" s="174" t="s">
+      <c r="A52" s="179" t="s">
         <v>338</v>
       </c>
-      <c r="B52" s="175"/>
-      <c r="C52" s="176"/>
+      <c r="B52" s="180"/>
+      <c r="C52" s="181"/>
       <c r="F52" s="129"/>
       <c r="G52" s="129"/>
       <c r="H52" s="129"/>
@@ -32606,11 +32687,11 @@
       <c r="V54" s="129"/>
     </row>
     <row r="55" spans="1:22" ht="15" thickBot="1">
-      <c r="A55" s="174" t="s">
+      <c r="A55" s="179" t="s">
         <v>339</v>
       </c>
-      <c r="B55" s="175"/>
-      <c r="C55" s="176"/>
+      <c r="B55" s="180"/>
+      <c r="C55" s="181"/>
       <c r="F55" s="129"/>
       <c r="G55" s="129"/>
       <c r="H55" s="129"/>
@@ -32748,11 +32829,11 @@
       <c r="V60" s="129"/>
     </row>
     <row r="61" spans="1:22" ht="15" thickBot="1">
-      <c r="A61" s="174" t="s">
+      <c r="A61" s="179" t="s">
         <v>296</v>
       </c>
-      <c r="B61" s="175"/>
-      <c r="C61" s="176"/>
+      <c r="B61" s="180"/>
+      <c r="C61" s="181"/>
       <c r="F61" s="129"/>
       <c r="G61" s="129"/>
       <c r="H61" s="129"/>
@@ -32763,10 +32844,10 @@
       <c r="M61" s="129"/>
       <c r="N61" s="129"/>
       <c r="O61" s="129"/>
-      <c r="P61" s="187" t="s">
+      <c r="P61" s="177" t="s">
         <v>384</v>
       </c>
-      <c r="Q61" s="188"/>
+      <c r="Q61" s="178"/>
       <c r="R61" s="129"/>
       <c r="S61" s="130"/>
       <c r="T61" s="129"/>
@@ -33008,11 +33089,11 @@
       <c r="V70" s="129"/>
     </row>
     <row r="71" spans="1:22" ht="15" thickBot="1">
-      <c r="A71" s="174" t="s">
+      <c r="A71" s="179" t="s">
         <v>112</v>
       </c>
-      <c r="B71" s="175"/>
-      <c r="C71" s="176"/>
+      <c r="B71" s="180"/>
+      <c r="C71" s="181"/>
       <c r="F71" s="129"/>
       <c r="G71" s="129"/>
       <c r="H71" s="129"/>
@@ -33070,10 +33151,10 @@
       <c r="C73" s="134" t="s">
         <v>32</v>
       </c>
-      <c r="P73" s="187" t="s">
+      <c r="P73" s="177" t="s">
         <v>384</v>
       </c>
-      <c r="Q73" s="188"/>
+      <c r="Q73" s="178"/>
     </row>
     <row r="74" spans="1:22" ht="16">
       <c r="A74" s="133" t="s">
@@ -33107,11 +33188,11 @@
     </row>
     <row r="78" spans="1:22" ht="7.5" customHeight="1" thickBot="1"/>
     <row r="79" spans="1:22" ht="15" thickBot="1">
-      <c r="A79" s="174" t="s">
+      <c r="A79" s="179" t="s">
         <v>298</v>
       </c>
-      <c r="B79" s="175"/>
-      <c r="C79" s="176"/>
+      <c r="B79" s="180"/>
+      <c r="C79" s="181"/>
     </row>
     <row r="80" spans="1:22">
       <c r="A80" s="133" t="s">
@@ -33160,11 +33241,11 @@
       </c>
     </row>
     <row r="84" spans="1:19" ht="15" thickBot="1">
-      <c r="A84" s="174" t="s">
+      <c r="A84" s="179" t="s">
         <v>299</v>
       </c>
-      <c r="B84" s="175"/>
-      <c r="C84" s="176"/>
+      <c r="B84" s="180"/>
+      <c r="C84" s="181"/>
     </row>
     <row r="85" spans="1:19">
       <c r="A85" s="133" t="s">
@@ -33237,11 +33318,11 @@
       <c r="S91" s="130"/>
     </row>
     <row r="92" spans="1:19" ht="15" thickBot="1">
-      <c r="A92" s="174" t="s">
+      <c r="A92" s="179" t="s">
         <v>113</v>
       </c>
-      <c r="B92" s="175"/>
-      <c r="C92" s="176"/>
+      <c r="B92" s="180"/>
+      <c r="C92" s="181"/>
       <c r="E92" s="129"/>
       <c r="F92" s="129"/>
       <c r="G92" s="129"/>
@@ -33267,25 +33348,25 @@
       </c>
       <c r="C93" s="183"/>
       <c r="E93" s="129"/>
-      <c r="F93" s="185" t="s">
+      <c r="F93" s="175" t="s">
         <v>309</v>
       </c>
-      <c r="G93" s="185"/>
-      <c r="H93" s="185"/>
+      <c r="G93" s="175"/>
+      <c r="H93" s="175"/>
       <c r="I93" s="129"/>
       <c r="J93" s="129"/>
-      <c r="K93" s="185" t="s">
+      <c r="K93" s="175" t="s">
         <v>307</v>
       </c>
-      <c r="L93" s="185"/>
-      <c r="M93" s="185"/>
+      <c r="L93" s="175"/>
+      <c r="M93" s="175"/>
       <c r="N93" s="129"/>
       <c r="O93" s="129"/>
       <c r="P93" s="129"/>
-      <c r="Q93" s="185" t="s">
+      <c r="Q93" s="175" t="s">
         <v>308</v>
       </c>
-      <c r="R93" s="185"/>
+      <c r="R93" s="175"/>
       <c r="S93" s="130"/>
     </row>
     <row r="94" spans="1:19">
@@ -33663,11 +33744,11 @@
       <c r="S108" s="130"/>
     </row>
     <row r="109" spans="1:21" ht="15" thickBot="1">
-      <c r="A109" s="174" t="s">
+      <c r="A109" s="179" t="s">
         <v>302</v>
       </c>
-      <c r="B109" s="175"/>
-      <c r="C109" s="176"/>
+      <c r="B109" s="180"/>
+      <c r="C109" s="181"/>
       <c r="E109" s="129"/>
       <c r="F109" s="129"/>
       <c r="G109" s="129"/>
@@ -33981,21 +34062,21 @@
       <c r="S121" s="130"/>
     </row>
     <row r="122" spans="1:19" ht="15" thickBot="1">
-      <c r="A122" s="174" t="s">
+      <c r="A122" s="179" t="s">
         <v>303</v>
       </c>
-      <c r="B122" s="175"/>
-      <c r="C122" s="176"/>
-      <c r="E122" s="186" t="s">
+      <c r="B122" s="180"/>
+      <c r="C122" s="181"/>
+      <c r="E122" s="176" t="s">
         <v>361</v>
       </c>
-      <c r="F122" s="186"/>
-      <c r="G122" s="186"/>
-      <c r="I122" s="186" t="s">
+      <c r="F122" s="176"/>
+      <c r="G122" s="176"/>
+      <c r="I122" s="176" t="s">
         <v>362</v>
       </c>
-      <c r="J122" s="186"/>
-      <c r="K122" s="186"/>
+      <c r="J122" s="176"/>
+      <c r="K122" s="176"/>
     </row>
     <row r="123" spans="1:19">
       <c r="A123" s="133" t="s">
@@ -34073,11 +34154,11 @@
     </row>
     <row r="132" spans="1:3" ht="15" thickBot="1"/>
     <row r="133" spans="1:3" ht="15" thickBot="1">
-      <c r="A133" s="174" t="s">
+      <c r="A133" s="179" t="s">
         <v>306</v>
       </c>
-      <c r="B133" s="175"/>
-      <c r="C133" s="176"/>
+      <c r="B133" s="180"/>
+      <c r="C133" s="181"/>
     </row>
     <row r="134" spans="1:3">
       <c r="A134" s="133" t="s">
@@ -34227,11 +34308,11 @@
     </row>
     <row r="150" spans="1:3" ht="8.25" customHeight="1" thickBot="1"/>
     <row r="151" spans="1:3" ht="15" thickBot="1">
-      <c r="A151" s="174" t="s">
+      <c r="A151" s="179" t="s">
         <v>459</v>
       </c>
-      <c r="B151" s="175"/>
-      <c r="C151" s="176"/>
+      <c r="B151" s="180"/>
+      <c r="C151" s="181"/>
     </row>
     <row r="152" spans="1:3" ht="16">
       <c r="A152" s="146" t="s">
@@ -34403,11 +34484,11 @@
     </row>
     <row r="169" spans="1:3" ht="15" thickBot="1"/>
     <row r="170" spans="1:3" ht="15" thickBot="1">
-      <c r="A170" s="174" t="s">
+      <c r="A170" s="179" t="s">
         <v>461</v>
       </c>
-      <c r="B170" s="175"/>
-      <c r="C170" s="176"/>
+      <c r="B170" s="180"/>
+      <c r="C170" s="181"/>
     </row>
     <row r="171" spans="1:3" ht="16">
       <c r="A171" s="146" t="s">
@@ -34573,6 +34654,34 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="fdU52W4crYajbraSt7Ih5pmYR8gmHjUDwlpQIF4YYH9Fakzt1D1AAwKy17nH/MLXUijSXtaMyzWZLUNwvQ0pfg==" saltValue="U5ME1tcmw0TPKCAZJxVidQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="44">
+    <mergeCell ref="A149:C149"/>
+    <mergeCell ref="A151:C151"/>
+    <mergeCell ref="A168:C168"/>
+    <mergeCell ref="A170:C170"/>
+    <mergeCell ref="A1:XFD3"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A133:C133"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="A52:C52"/>
+    <mergeCell ref="A55:C55"/>
+    <mergeCell ref="A59:C59"/>
+    <mergeCell ref="A69:C69"/>
+    <mergeCell ref="A84:C84"/>
+    <mergeCell ref="A77:C77"/>
+    <mergeCell ref="A90:C90"/>
+    <mergeCell ref="A109:C109"/>
+    <mergeCell ref="A107:C107"/>
+    <mergeCell ref="A122:C122"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="B98:C98"/>
     <mergeCell ref="A131:C131"/>
     <mergeCell ref="G10:M11"/>
     <mergeCell ref="F93:H93"/>
@@ -34589,34 +34698,6 @@
     <mergeCell ref="A71:C71"/>
     <mergeCell ref="A43:C43"/>
     <mergeCell ref="A61:C61"/>
-    <mergeCell ref="A90:C90"/>
-    <mergeCell ref="A109:C109"/>
-    <mergeCell ref="A107:C107"/>
-    <mergeCell ref="A122:C122"/>
-    <mergeCell ref="B123:C123"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="A52:C52"/>
-    <mergeCell ref="A55:C55"/>
-    <mergeCell ref="A59:C59"/>
-    <mergeCell ref="A69:C69"/>
-    <mergeCell ref="A84:C84"/>
-    <mergeCell ref="A77:C77"/>
-    <mergeCell ref="A149:C149"/>
-    <mergeCell ref="A151:C151"/>
-    <mergeCell ref="A168:C168"/>
-    <mergeCell ref="A170:C170"/>
-    <mergeCell ref="A1:XFD3"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="A133:C133"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="A50:C50"/>
   </mergeCells>
   <phoneticPr fontId="30"/>
   <hyperlinks>
@@ -35183,12 +35264,6 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="5qE34U5q/yBhg7STOFPUv88vScnDIX6LSJXkXZZoEDGlf2xyJ9tb1iRHmvB8K7kFYfV2kEAhxpH5QBakawGgAg==" saltValue="eUds3aBXmyc9/xlWEDMFXg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1" selectUnlockedCells="1"/>
   <mergeCells count="14">
-    <mergeCell ref="B39:K39"/>
-    <mergeCell ref="A1:L3"/>
-    <mergeCell ref="A4:L4"/>
-    <mergeCell ref="B36:K36"/>
-    <mergeCell ref="B37:K37"/>
-    <mergeCell ref="B38:K38"/>
     <mergeCell ref="B46:K46"/>
     <mergeCell ref="B47:K47"/>
     <mergeCell ref="B40:K40"/>
@@ -35197,6 +35272,12 @@
     <mergeCell ref="B43:K43"/>
     <mergeCell ref="B44:K44"/>
     <mergeCell ref="B45:K45"/>
+    <mergeCell ref="B39:K39"/>
+    <mergeCell ref="A1:L3"/>
+    <mergeCell ref="A4:L4"/>
+    <mergeCell ref="B36:K36"/>
+    <mergeCell ref="B37:K37"/>
+    <mergeCell ref="B38:K38"/>
   </mergeCells>
   <phoneticPr fontId="30"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -35236,42 +35317,42 @@
     </row>
     <row r="3" spans="1:39" ht="15" thickBot="1"/>
     <row r="4" spans="1:39">
-      <c r="P4" s="203" t="s">
+      <c r="P4" s="196" t="s">
         <v>375</v>
       </c>
-      <c r="Q4" s="204"/>
-      <c r="R4" s="204"/>
-      <c r="S4" s="205"/>
-      <c r="T4" s="203" t="s">
+      <c r="Q4" s="197"/>
+      <c r="R4" s="197"/>
+      <c r="S4" s="198"/>
+      <c r="T4" s="196" t="s">
         <v>24</v>
       </c>
-      <c r="U4" s="204"/>
-      <c r="V4" s="204"/>
-      <c r="W4" s="205"/>
-      <c r="X4" s="203" t="s">
+      <c r="U4" s="197"/>
+      <c r="V4" s="197"/>
+      <c r="W4" s="198"/>
+      <c r="X4" s="196" t="s">
         <v>75</v>
       </c>
-      <c r="Y4" s="204"/>
-      <c r="Z4" s="204"/>
-      <c r="AA4" s="205"/>
-      <c r="AB4" s="203" t="s">
+      <c r="Y4" s="197"/>
+      <c r="Z4" s="197"/>
+      <c r="AA4" s="198"/>
+      <c r="AB4" s="196" t="s">
         <v>376</v>
       </c>
-      <c r="AC4" s="204"/>
-      <c r="AD4" s="204"/>
-      <c r="AE4" s="205"/>
-      <c r="AF4" s="203" t="s">
+      <c r="AC4" s="197"/>
+      <c r="AD4" s="197"/>
+      <c r="AE4" s="198"/>
+      <c r="AF4" s="196" t="s">
         <v>377</v>
       </c>
-      <c r="AG4" s="204"/>
-      <c r="AH4" s="204"/>
-      <c r="AI4" s="205"/>
-      <c r="AJ4" s="203" t="s">
+      <c r="AG4" s="197"/>
+      <c r="AH4" s="197"/>
+      <c r="AI4" s="198"/>
+      <c r="AJ4" s="196" t="s">
         <v>378</v>
       </c>
-      <c r="AK4" s="204"/>
-      <c r="AL4" s="204"/>
-      <c r="AM4" s="205"/>
+      <c r="AK4" s="197"/>
+      <c r="AL4" s="197"/>
+      <c r="AM4" s="198"/>
     </row>
     <row r="5" spans="1:39" ht="45">
       <c r="D5" s="48" t="s">
@@ -35363,11 +35444,11 @@
       </c>
     </row>
     <row r="6" spans="1:39">
-      <c r="A6" s="195" t="s">
+      <c r="A6" s="199" t="s">
         <v>118</v>
       </c>
-      <c r="B6" s="195"/>
-      <c r="C6" s="195"/>
+      <c r="B6" s="199"/>
+      <c r="C6" s="199"/>
       <c r="E6" s="74" t="s">
         <v>333</v>
       </c>
@@ -35842,11 +35923,11 @@
       </c>
     </row>
     <row r="10" spans="1:39">
-      <c r="A10" s="195" t="s">
+      <c r="A10" s="199" t="s">
         <v>121</v>
       </c>
-      <c r="B10" s="195"/>
-      <c r="C10" s="195"/>
+      <c r="B10" s="199"/>
+      <c r="C10" s="199"/>
       <c r="I10" s="39"/>
       <c r="J10" t="s">
         <v>145</v>
@@ -36310,11 +36391,11 @@
       </c>
     </row>
     <row r="14" spans="1:39">
-      <c r="A14" s="195" t="s">
+      <c r="A14" s="199" t="s">
         <v>86</v>
       </c>
-      <c r="B14" s="195"/>
-      <c r="C14" s="195"/>
+      <c r="B14" s="199"/>
+      <c r="C14" s="199"/>
       <c r="N14">
         <v>8.0000000000000002E-3</v>
       </c>
@@ -37111,11 +37192,11 @@
       </c>
     </row>
     <row r="21" spans="1:39">
-      <c r="A21" s="196" t="s">
+      <c r="A21" s="200" t="s">
         <v>131</v>
       </c>
-      <c r="B21" s="197"/>
-      <c r="C21" s="198"/>
+      <c r="B21" s="201"/>
+      <c r="C21" s="202"/>
       <c r="N21">
         <v>1.4999999999999999E-2</v>
       </c>
@@ -39298,11 +39379,11 @@
       </c>
     </row>
     <row r="40" spans="1:39" ht="15" thickBot="1">
-      <c r="A40" s="199" t="s">
+      <c r="A40" s="203" t="s">
         <v>10</v>
       </c>
-      <c r="B40" s="200"/>
-      <c r="C40" s="201"/>
+      <c r="B40" s="204"/>
+      <c r="C40" s="205"/>
       <c r="E40" s="34" t="s">
         <v>154</v>
       </c>
@@ -41277,20 +41358,20 @@
       <c r="Y58" s="40"/>
       <c r="Z58" s="40"/>
       <c r="AA58" s="40"/>
-      <c r="AD58" s="202" t="s">
+      <c r="AD58" s="195" t="s">
         <v>79</v>
       </c>
-      <c r="AE58" s="202"/>
-      <c r="AF58" s="202"/>
-      <c r="AG58" s="202"/>
-      <c r="AH58" s="202"/>
-      <c r="AI58" s="202"/>
-      <c r="AJ58" s="202"/>
-      <c r="AK58" s="202"/>
-      <c r="AL58" s="202"/>
-      <c r="AM58" s="202"/>
-      <c r="AN58" s="202"/>
-      <c r="AO58" s="202"/>
+      <c r="AE58" s="195"/>
+      <c r="AF58" s="195"/>
+      <c r="AG58" s="195"/>
+      <c r="AH58" s="195"/>
+      <c r="AI58" s="195"/>
+      <c r="AJ58" s="195"/>
+      <c r="AK58" s="195"/>
+      <c r="AL58" s="195"/>
+      <c r="AM58" s="195"/>
+      <c r="AN58" s="195"/>
+      <c r="AO58" s="195"/>
     </row>
     <row r="59" spans="1:42" ht="15" thickBot="1">
       <c r="N59" s="40"/>
@@ -41641,11 +41722,11 @@
       </c>
     </row>
     <row r="63" spans="1:42">
-      <c r="A63" s="196" t="s">
+      <c r="A63" s="200" t="s">
         <v>73</v>
       </c>
-      <c r="B63" s="197"/>
-      <c r="C63" s="198"/>
+      <c r="B63" s="201"/>
+      <c r="C63" s="202"/>
       <c r="E63" s="65" t="s">
         <v>152</v>
       </c>
@@ -48554,6 +48635,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A63:C63"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A21:C21"/>
     <mergeCell ref="AD58:AO58"/>
     <mergeCell ref="AB4:AE4"/>
     <mergeCell ref="AF4:AI4"/>
@@ -48561,12 +48648,6 @@
     <mergeCell ref="P4:S4"/>
     <mergeCell ref="T4:W4"/>
     <mergeCell ref="X4:AA4"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A63:C63"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="A21:C21"/>
   </mergeCells>
   <phoneticPr fontId="30"/>
   <conditionalFormatting sqref="D70">
@@ -48613,38 +48694,38 @@
       </c>
     </row>
     <row r="5" spans="2:30">
-      <c r="B5" s="213" t="s">
+      <c r="B5" s="206" t="s">
         <v>33</v>
       </c>
-      <c r="C5" s="213"/>
-      <c r="D5" s="202" t="s">
+      <c r="C5" s="206"/>
+      <c r="D5" s="195" t="s">
         <v>272</v>
       </c>
-      <c r="E5" s="202"/>
-      <c r="F5" s="202"/>
-      <c r="G5" s="202" t="s">
+      <c r="E5" s="195"/>
+      <c r="F5" s="195"/>
+      <c r="G5" s="195" t="s">
         <v>276</v>
       </c>
-      <c r="H5" s="202"/>
-      <c r="I5" s="202"/>
-      <c r="J5" s="202" t="s">
+      <c r="H5" s="195"/>
+      <c r="I5" s="195"/>
+      <c r="J5" s="195" t="s">
         <v>277</v>
       </c>
-      <c r="K5" s="202"/>
-      <c r="L5" s="202"/>
+      <c r="K5" s="195"/>
+      <c r="L5" s="195"/>
     </row>
     <row r="6" spans="2:30">
-      <c r="B6" s="213"/>
-      <c r="C6" s="213"/>
-      <c r="D6" s="202"/>
-      <c r="E6" s="202"/>
-      <c r="F6" s="202"/>
-      <c r="G6" s="202"/>
-      <c r="H6" s="202"/>
-      <c r="I6" s="202"/>
-      <c r="J6" s="202"/>
-      <c r="K6" s="202"/>
-      <c r="L6" s="202"/>
+      <c r="B6" s="206"/>
+      <c r="C6" s="206"/>
+      <c r="D6" s="195"/>
+      <c r="E6" s="195"/>
+      <c r="F6" s="195"/>
+      <c r="G6" s="195"/>
+      <c r="H6" s="195"/>
+      <c r="I6" s="195"/>
+      <c r="J6" s="195"/>
+      <c r="K6" s="195"/>
+      <c r="L6" s="195"/>
     </row>
     <row r="7" spans="2:30" s="2" customFormat="1" ht="30">
       <c r="B7" s="71" t="s">
@@ -51245,67 +51326,67 @@
       <c r="E75" s="29"/>
     </row>
     <row r="76" spans="2:97" ht="15" thickBot="1">
-      <c r="B76" s="213" t="s">
+      <c r="B76" s="206" t="s">
         <v>33</v>
       </c>
-      <c r="C76" s="213"/>
-      <c r="D76" s="206" t="s">
+      <c r="C76" s="206"/>
+      <c r="D76" s="216" t="s">
         <v>31</v>
       </c>
-      <c r="E76" s="202"/>
-      <c r="F76" s="202"/>
-      <c r="G76" s="202"/>
-      <c r="H76" s="202"/>
-      <c r="I76" s="202"/>
-      <c r="J76" s="202"/>
-      <c r="K76" s="202"/>
-      <c r="L76" s="202"/>
-      <c r="M76" s="202"/>
-      <c r="N76" s="202"/>
-      <c r="O76" s="202"/>
-      <c r="P76" s="202"/>
-      <c r="Q76" s="202"/>
-      <c r="R76" s="202"/>
-      <c r="S76" s="202"/>
-      <c r="T76" s="202"/>
+      <c r="E76" s="195"/>
+      <c r="F76" s="195"/>
+      <c r="G76" s="195"/>
+      <c r="H76" s="195"/>
+      <c r="I76" s="195"/>
+      <c r="J76" s="195"/>
+      <c r="K76" s="195"/>
+      <c r="L76" s="195"/>
+      <c r="M76" s="195"/>
+      <c r="N76" s="195"/>
+      <c r="O76" s="195"/>
+      <c r="P76" s="195"/>
+      <c r="Q76" s="195"/>
+      <c r="R76" s="195"/>
+      <c r="S76" s="195"/>
+      <c r="T76" s="195"/>
     </row>
     <row r="77" spans="2:97" ht="15" thickBot="1">
-      <c r="B77" s="213"/>
-      <c r="C77" s="213"/>
-      <c r="D77" s="203" t="s">
+      <c r="B77" s="206"/>
+      <c r="C77" s="206"/>
+      <c r="D77" s="196" t="s">
         <v>0</v>
       </c>
-      <c r="E77" s="204"/>
-      <c r="F77" s="205"/>
-      <c r="G77" s="203" t="s">
+      <c r="E77" s="197"/>
+      <c r="F77" s="198"/>
+      <c r="G77" s="196" t="s">
         <v>386</v>
       </c>
-      <c r="H77" s="204"/>
-      <c r="I77" s="205"/>
-      <c r="J77" s="203" t="s">
+      <c r="H77" s="197"/>
+      <c r="I77" s="198"/>
+      <c r="J77" s="196" t="s">
         <v>387</v>
       </c>
-      <c r="K77" s="204"/>
-      <c r="L77" s="205"/>
-      <c r="M77" s="203" t="s">
+      <c r="K77" s="197"/>
+      <c r="L77" s="198"/>
+      <c r="M77" s="196" t="s">
         <v>390</v>
       </c>
-      <c r="N77" s="205"/>
+      <c r="N77" s="198"/>
       <c r="O77" s="207" t="s">
         <v>444</v>
       </c>
-      <c r="P77" s="208"/>
-      <c r="Q77" s="209"/>
-      <c r="R77" s="210" t="s">
+      <c r="P77" s="217"/>
+      <c r="Q77" s="208"/>
+      <c r="R77" s="218" t="s">
         <v>445</v>
       </c>
-      <c r="S77" s="211"/>
-      <c r="T77" s="211"/>
-      <c r="U77" s="202" t="s">
+      <c r="S77" s="219"/>
+      <c r="T77" s="219"/>
+      <c r="U77" s="195" t="s">
         <v>393</v>
       </c>
-      <c r="V77" s="202"/>
-      <c r="W77" s="202"/>
+      <c r="V77" s="195"/>
+      <c r="W77" s="195"/>
       <c r="X77" t="s">
         <v>387</v>
       </c>
@@ -57442,30 +57523,30 @@
       <c r="B166" s="207" t="s">
         <v>33</v>
       </c>
-      <c r="C166" s="209"/>
-      <c r="D166" s="219" t="s">
+      <c r="C166" s="208"/>
+      <c r="D166" s="214" t="s">
         <v>31</v>
       </c>
-      <c r="E166" s="212"/>
-      <c r="F166" s="212"/>
-      <c r="G166" s="212" t="s">
+      <c r="E166" s="215"/>
+      <c r="F166" s="215"/>
+      <c r="G166" s="215" t="s">
         <v>386</v>
       </c>
-      <c r="H166" s="212"/>
-      <c r="I166" s="212"/>
-      <c r="J166" s="212" t="s">
+      <c r="H166" s="215"/>
+      <c r="I166" s="215"/>
+      <c r="J166" s="215" t="s">
         <v>387</v>
       </c>
-      <c r="K166" s="212"/>
-      <c r="L166" s="212"/>
-      <c r="M166" s="212"/>
-      <c r="N166" s="212"/>
-      <c r="O166" s="212"/>
-      <c r="P166" s="212"/>
-      <c r="Q166" s="212"/>
-      <c r="R166" s="212"/>
-      <c r="S166" s="212"/>
-      <c r="T166" s="212"/>
+      <c r="K166" s="215"/>
+      <c r="L166" s="215"/>
+      <c r="M166" s="215"/>
+      <c r="N166" s="215"/>
+      <c r="O166" s="215"/>
+      <c r="P166" s="215"/>
+      <c r="Q166" s="215"/>
+      <c r="R166" s="215"/>
+      <c r="S166" s="215"/>
+      <c r="T166" s="215"/>
       <c r="U166" s="81"/>
       <c r="V166" s="81"/>
       <c r="W166" s="81"/>
@@ -57473,133 +57554,133 @@
       <c r="Y166" s="81"/>
       <c r="Z166" s="81"/>
       <c r="AA166" s="81"/>
-      <c r="AB166" s="213"/>
-      <c r="AC166" s="213"/>
-      <c r="AD166" s="213"/>
-      <c r="BC166" s="202"/>
-      <c r="BD166" s="202"/>
-      <c r="BE166" s="202"/>
-      <c r="BF166" s="202"/>
-      <c r="BG166" s="202"/>
-      <c r="BH166" s="202"/>
-      <c r="BI166" s="202"/>
-      <c r="BJ166" s="202"/>
-      <c r="BK166" s="202"/>
-      <c r="BL166" s="202"/>
-      <c r="BM166" s="202"/>
-      <c r="BN166" s="202"/>
-      <c r="BO166" s="202"/>
-      <c r="BP166" s="202"/>
-      <c r="BQ166" s="202"/>
-      <c r="BR166" s="202"/>
-      <c r="BS166" s="202"/>
-      <c r="BT166" s="202"/>
-      <c r="BU166" s="202"/>
-      <c r="BV166" s="202"/>
-      <c r="BW166" s="202"/>
-      <c r="BX166" s="202"/>
-      <c r="BY166" s="202"/>
-      <c r="BZ166" s="202"/>
-      <c r="CA166" s="202"/>
-      <c r="CB166" s="202"/>
-      <c r="CC166" s="202"/>
-      <c r="CD166" s="202"/>
-      <c r="CE166" s="202"/>
-      <c r="CF166" s="202"/>
-      <c r="CG166" s="202"/>
-      <c r="CH166" s="202"/>
-      <c r="CI166" s="202"/>
-      <c r="CJ166" s="202"/>
-      <c r="CK166" s="202"/>
-      <c r="CL166" s="202"/>
-      <c r="CM166" s="202"/>
-      <c r="CN166" s="202"/>
-      <c r="CO166" s="202"/>
+      <c r="AB166" s="206"/>
+      <c r="AC166" s="206"/>
+      <c r="AD166" s="206"/>
+      <c r="BC166" s="195"/>
+      <c r="BD166" s="195"/>
+      <c r="BE166" s="195"/>
+      <c r="BF166" s="195"/>
+      <c r="BG166" s="195"/>
+      <c r="BH166" s="195"/>
+      <c r="BI166" s="195"/>
+      <c r="BJ166" s="195"/>
+      <c r="BK166" s="195"/>
+      <c r="BL166" s="195"/>
+      <c r="BM166" s="195"/>
+      <c r="BN166" s="195"/>
+      <c r="BO166" s="195"/>
+      <c r="BP166" s="195"/>
+      <c r="BQ166" s="195"/>
+      <c r="BR166" s="195"/>
+      <c r="BS166" s="195"/>
+      <c r="BT166" s="195"/>
+      <c r="BU166" s="195"/>
+      <c r="BV166" s="195"/>
+      <c r="BW166" s="195"/>
+      <c r="BX166" s="195"/>
+      <c r="BY166" s="195"/>
+      <c r="BZ166" s="195"/>
+      <c r="CA166" s="195"/>
+      <c r="CB166" s="195"/>
+      <c r="CC166" s="195"/>
+      <c r="CD166" s="195"/>
+      <c r="CE166" s="195"/>
+      <c r="CF166" s="195"/>
+      <c r="CG166" s="195"/>
+      <c r="CH166" s="195"/>
+      <c r="CI166" s="195"/>
+      <c r="CJ166" s="195"/>
+      <c r="CK166" s="195"/>
+      <c r="CL166" s="195"/>
+      <c r="CM166" s="195"/>
+      <c r="CN166" s="195"/>
+      <c r="CO166" s="195"/>
     </row>
     <row r="167" spans="2:93" ht="15" thickBot="1">
-      <c r="B167" s="214"/>
-      <c r="C167" s="215"/>
-      <c r="D167" s="216" t="s">
+      <c r="B167" s="209"/>
+      <c r="C167" s="210"/>
+      <c r="D167" s="211" t="s">
         <v>385</v>
       </c>
-      <c r="E167" s="217"/>
-      <c r="F167" s="218"/>
-      <c r="G167" s="216" t="s">
+      <c r="E167" s="212"/>
+      <c r="F167" s="213"/>
+      <c r="G167" s="211" t="s">
         <v>385</v>
       </c>
-      <c r="H167" s="217"/>
-      <c r="I167" s="218"/>
-      <c r="J167" s="216" t="s">
+      <c r="H167" s="212"/>
+      <c r="I167" s="213"/>
+      <c r="J167" s="211" t="s">
         <v>385</v>
       </c>
-      <c r="K167" s="217"/>
-      <c r="L167" s="218"/>
-      <c r="M167" s="206" t="s">
+      <c r="K167" s="212"/>
+      <c r="L167" s="213"/>
+      <c r="M167" s="216" t="s">
         <v>390</v>
       </c>
-      <c r="N167" s="202"/>
-      <c r="O167" s="202" t="s">
+      <c r="N167" s="195"/>
+      <c r="O167" s="195" t="s">
         <v>394</v>
       </c>
-      <c r="P167" s="202"/>
-      <c r="Q167" s="202"/>
-      <c r="R167" s="202" t="s">
+      <c r="P167" s="195"/>
+      <c r="Q167" s="195"/>
+      <c r="R167" s="195" t="s">
         <v>391</v>
       </c>
-      <c r="S167" s="202"/>
-      <c r="T167" s="202"/>
-      <c r="U167" s="202" t="s">
+      <c r="S167" s="195"/>
+      <c r="T167" s="195"/>
+      <c r="U167" s="195" t="s">
         <v>393</v>
       </c>
-      <c r="V167" s="202"/>
-      <c r="W167" s="202"/>
-      <c r="X167" s="202" t="s">
+      <c r="V167" s="195"/>
+      <c r="W167" s="195"/>
+      <c r="X167" s="195" t="s">
         <v>395</v>
       </c>
-      <c r="Y167" s="202"/>
-      <c r="Z167" s="202"/>
-      <c r="AB167" s="213"/>
-      <c r="AC167" s="213"/>
-      <c r="AD167" s="213"/>
-      <c r="BC167" s="202"/>
-      <c r="BD167" s="202"/>
-      <c r="BE167" s="202"/>
-      <c r="BF167" s="202"/>
-      <c r="BG167" s="202"/>
-      <c r="BH167" s="202"/>
-      <c r="BI167" s="202"/>
-      <c r="BJ167" s="202"/>
-      <c r="BK167" s="202"/>
-      <c r="BL167" s="202"/>
-      <c r="BM167" s="202"/>
-      <c r="BN167" s="202"/>
-      <c r="BO167" s="202"/>
-      <c r="BP167" s="202"/>
-      <c r="BQ167" s="202"/>
-      <c r="BR167" s="202"/>
-      <c r="BS167" s="202"/>
-      <c r="BT167" s="202"/>
-      <c r="BU167" s="202"/>
-      <c r="BV167" s="202"/>
-      <c r="BW167" s="202"/>
-      <c r="BX167" s="202"/>
-      <c r="BY167" s="202"/>
-      <c r="BZ167" s="202"/>
-      <c r="CA167" s="202"/>
-      <c r="CB167" s="202"/>
-      <c r="CC167" s="202"/>
-      <c r="CD167" s="202"/>
-      <c r="CE167" s="202"/>
-      <c r="CF167" s="202"/>
-      <c r="CG167" s="202"/>
-      <c r="CH167" s="202"/>
-      <c r="CI167" s="202"/>
-      <c r="CJ167" s="202"/>
-      <c r="CK167" s="202"/>
-      <c r="CL167" s="202"/>
-      <c r="CM167" s="202"/>
-      <c r="CN167" s="202"/>
-      <c r="CO167" s="202"/>
+      <c r="Y167" s="195"/>
+      <c r="Z167" s="195"/>
+      <c r="AB167" s="206"/>
+      <c r="AC167" s="206"/>
+      <c r="AD167" s="206"/>
+      <c r="BC167" s="195"/>
+      <c r="BD167" s="195"/>
+      <c r="BE167" s="195"/>
+      <c r="BF167" s="195"/>
+      <c r="BG167" s="195"/>
+      <c r="BH167" s="195"/>
+      <c r="BI167" s="195"/>
+      <c r="BJ167" s="195"/>
+      <c r="BK167" s="195"/>
+      <c r="BL167" s="195"/>
+      <c r="BM167" s="195"/>
+      <c r="BN167" s="195"/>
+      <c r="BO167" s="195"/>
+      <c r="BP167" s="195"/>
+      <c r="BQ167" s="195"/>
+      <c r="BR167" s="195"/>
+      <c r="BS167" s="195"/>
+      <c r="BT167" s="195"/>
+      <c r="BU167" s="195"/>
+      <c r="BV167" s="195"/>
+      <c r="BW167" s="195"/>
+      <c r="BX167" s="195"/>
+      <c r="BY167" s="195"/>
+      <c r="BZ167" s="195"/>
+      <c r="CA167" s="195"/>
+      <c r="CB167" s="195"/>
+      <c r="CC167" s="195"/>
+      <c r="CD167" s="195"/>
+      <c r="CE167" s="195"/>
+      <c r="CF167" s="195"/>
+      <c r="CG167" s="195"/>
+      <c r="CH167" s="195"/>
+      <c r="CI167" s="195"/>
+      <c r="CJ167" s="195"/>
+      <c r="CK167" s="195"/>
+      <c r="CL167" s="195"/>
+      <c r="CM167" s="195"/>
+      <c r="CN167" s="195"/>
+      <c r="CO167" s="195"/>
     </row>
     <row r="168" spans="2:93" ht="45">
       <c r="B168" s="23" t="s">
@@ -63827,25 +63908,18 @@
     </row>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="B76:C77"/>
-    <mergeCell ref="D77:F77"/>
-    <mergeCell ref="J77:L77"/>
-    <mergeCell ref="BC166:BN166"/>
-    <mergeCell ref="BO166:BZ166"/>
-    <mergeCell ref="BC167:BE167"/>
-    <mergeCell ref="BF167:BH167"/>
-    <mergeCell ref="BI167:BK167"/>
-    <mergeCell ref="BL167:BN167"/>
-    <mergeCell ref="BO167:BQ167"/>
-    <mergeCell ref="BR167:BT167"/>
-    <mergeCell ref="BU167:BW167"/>
-    <mergeCell ref="BX167:BZ167"/>
-    <mergeCell ref="CD166:CO166"/>
-    <mergeCell ref="CA167:CC167"/>
-    <mergeCell ref="CD167:CF167"/>
-    <mergeCell ref="CG167:CI167"/>
-    <mergeCell ref="CJ167:CL167"/>
-    <mergeCell ref="CM167:CO167"/>
+    <mergeCell ref="X167:Z167"/>
+    <mergeCell ref="G77:I77"/>
+    <mergeCell ref="M77:N77"/>
+    <mergeCell ref="D76:T76"/>
+    <mergeCell ref="O77:Q77"/>
+    <mergeCell ref="R77:T77"/>
+    <mergeCell ref="U77:W77"/>
+    <mergeCell ref="R167:T167"/>
+    <mergeCell ref="M166:N166"/>
+    <mergeCell ref="O166:Q166"/>
+    <mergeCell ref="R166:T166"/>
+    <mergeCell ref="U167:W167"/>
     <mergeCell ref="D5:F6"/>
     <mergeCell ref="G5:I6"/>
     <mergeCell ref="J5:L6"/>
@@ -63862,18 +63936,25 @@
     <mergeCell ref="M167:N167"/>
     <mergeCell ref="O167:Q167"/>
     <mergeCell ref="AB167:AD167"/>
-    <mergeCell ref="X167:Z167"/>
-    <mergeCell ref="G77:I77"/>
-    <mergeCell ref="M77:N77"/>
-    <mergeCell ref="D76:T76"/>
-    <mergeCell ref="O77:Q77"/>
-    <mergeCell ref="R77:T77"/>
-    <mergeCell ref="U77:W77"/>
-    <mergeCell ref="R167:T167"/>
-    <mergeCell ref="M166:N166"/>
-    <mergeCell ref="O166:Q166"/>
-    <mergeCell ref="R166:T166"/>
-    <mergeCell ref="U167:W167"/>
+    <mergeCell ref="BR167:BT167"/>
+    <mergeCell ref="BU167:BW167"/>
+    <mergeCell ref="BX167:BZ167"/>
+    <mergeCell ref="CD166:CO166"/>
+    <mergeCell ref="CA167:CC167"/>
+    <mergeCell ref="CD167:CF167"/>
+    <mergeCell ref="CG167:CI167"/>
+    <mergeCell ref="CJ167:CL167"/>
+    <mergeCell ref="CM167:CO167"/>
+    <mergeCell ref="BC167:BE167"/>
+    <mergeCell ref="BF167:BH167"/>
+    <mergeCell ref="BI167:BK167"/>
+    <mergeCell ref="BL167:BN167"/>
+    <mergeCell ref="BO167:BQ167"/>
+    <mergeCell ref="B76:C77"/>
+    <mergeCell ref="D77:F77"/>
+    <mergeCell ref="J77:L77"/>
+    <mergeCell ref="BC166:BN166"/>
+    <mergeCell ref="BO166:BZ166"/>
   </mergeCells>
   <phoneticPr fontId="30"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -63928,9 +64009,9 @@
       <c r="A2" s="220" t="s">
         <v>91</v>
       </c>
-      <c r="B2" s="197"/>
-      <c r="C2" s="197"/>
-      <c r="D2" s="197"/>
+      <c r="B2" s="201"/>
+      <c r="C2" s="201"/>
+      <c r="D2" s="201"/>
       <c r="E2" s="221"/>
     </row>
     <row r="3" spans="1:9">

--- a/2026/PCB/WheelVoltageBooster/LM5170_DESIGN-CALC_V1.1.0.xlsx
+++ b/2026/PCB/WheelVoltageBooster/LM5170_DESIGN-CALC_V1.1.0.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tsukigake/Documents/GitHub/ssl-Circuit/2026/PCB/WheelVoltageBooster/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kamiokannde\Documents\GitHub\Ri-one\ssl-Circuit\2026\PCB\WheelVoltageBooster\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74D9A03C-247E-3248-A5B2-CA3BDE12BC39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{690B5035-FDC8-424A-86C6-1749DF2C47B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="FTbea0zNh/M4QFFIjkWMzUxKnz4OFezzA9/BRwWSIIMWDYlyn+LFccWDum1tXS3mgTwJKFr3ZBSW6d5DYWBVMg==" workbookSaltValue="UMfWwVJIqsWZTSD9g7ReYQ==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="1400" yWindow="880" windowWidth="32800" windowHeight="21360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25710" yWindow="-1320" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Design_Converter" sheetId="1" r:id="rId1"/>
@@ -10375,7 +10375,7 @@
     <numFmt numFmtId="179" formatCode="0.0000"/>
     <numFmt numFmtId="180" formatCode="0.00000"/>
   </numFmts>
-  <fonts count="36">
+  <fonts count="36" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -11683,6 +11683,26 @@
       <alignment horizontal="left"/>
       <protection hidden="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection hidden="1"/>
@@ -11694,6 +11714,14 @@
     <xf numFmtId="0" fontId="7" fillId="8" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0" hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
@@ -11715,34 +11743,6 @@
       <alignment horizontal="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -11760,6 +11760,18 @@
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -11783,39 +11795,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
@@ -11834,6 +11819,21 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
@@ -29071,7 +29071,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>2283071</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>5256</xdr:rowOff>
+      <xdr:rowOff>11606</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -29119,7 +29119,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>159046</xdr:colOff>
+      <xdr:colOff>165396</xdr:colOff>
       <xdr:row>103</xdr:row>
       <xdr:rowOff>114914</xdr:rowOff>
     </xdr:to>
@@ -29169,7 +29169,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>82848</xdr:colOff>
+      <xdr:colOff>89198</xdr:colOff>
       <xdr:row>103</xdr:row>
       <xdr:rowOff>114914</xdr:rowOff>
     </xdr:to>
@@ -29219,9 +29219,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>120397</xdr:colOff>
+      <xdr:colOff>126747</xdr:colOff>
       <xdr:row>103</xdr:row>
-      <xdr:rowOff>105389</xdr:rowOff>
+      <xdr:rowOff>111739</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -29269,9 +29269,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>239358</xdr:colOff>
+      <xdr:colOff>245708</xdr:colOff>
       <xdr:row>116</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
+      <xdr:rowOff>130175</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -29371,7 +29371,7 @@
       <xdr:col>10</xdr:col>
       <xdr:colOff>419103</xdr:colOff>
       <xdr:row>128</xdr:row>
-      <xdr:rowOff>66296</xdr:rowOff>
+      <xdr:rowOff>72646</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -29703,7 +29703,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>276239</xdr:colOff>
+      <xdr:colOff>282589</xdr:colOff>
       <xdr:row>55</xdr:row>
       <xdr:rowOff>19068</xdr:rowOff>
     </xdr:to>
@@ -29755,7 +29755,7 @@
       <xdr:col>6</xdr:col>
       <xdr:colOff>457201</xdr:colOff>
       <xdr:row>144</xdr:row>
-      <xdr:rowOff>10306</xdr:rowOff>
+      <xdr:rowOff>16656</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -29803,7 +29803,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>121812</xdr:colOff>
+      <xdr:colOff>128162</xdr:colOff>
       <xdr:row>180</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
@@ -31474,33 +31474,33 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:V184"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="50.1640625" style="127" customWidth="1"/>
+    <col min="1" max="1" width="50.125" style="127" customWidth="1"/>
     <col min="2" max="2" width="10" style="128" customWidth="1"/>
-    <col min="3" max="3" width="4.6640625" style="128" customWidth="1"/>
-    <col min="4" max="4" width="9.1640625" style="128"/>
+    <col min="3" max="3" width="4.625" style="128" customWidth="1"/>
+    <col min="4" max="4" width="9.125" style="128"/>
     <col min="5" max="5" width="10" style="128" bestFit="1" customWidth="1"/>
-    <col min="6" max="9" width="9.1640625" style="128"/>
-    <col min="10" max="10" width="9.1640625" style="128" customWidth="1"/>
-    <col min="11" max="17" width="9.1640625" style="128"/>
-    <col min="18" max="18" width="12.6640625" style="128" customWidth="1"/>
-    <col min="19" max="19" width="9.1640625" style="148"/>
-    <col min="20" max="16384" width="9.1640625" style="128"/>
+    <col min="6" max="9" width="9.125" style="128"/>
+    <col min="10" max="10" width="9.125" style="128" customWidth="1"/>
+    <col min="11" max="17" width="9.125" style="128"/>
+    <col min="18" max="18" width="12.625" style="128" customWidth="1"/>
+    <col min="19" max="19" width="9.125" style="148"/>
+    <col min="20" max="16384" width="9.125" style="128"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" s="178" customFormat="1">
-      <c r="A1" s="177" t="s">
+    <row r="1" spans="1:22" s="185" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="184" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="2" spans="1:22" s="180" customFormat="1">
-      <c r="A2" s="179"/>
+    <row r="2" spans="1:22" s="187" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="186"/>
     </row>
-    <row r="3" spans="1:22" s="180" customFormat="1" ht="12.75" customHeight="1">
-      <c r="A3" s="179"/>
+    <row r="3" spans="1:22" s="187" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="186"/>
     </row>
-    <row r="4" spans="1:22" s="116" customFormat="1" ht="15" thickBot="1">
+    <row r="4" spans="1:22" s="116" customFormat="1" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A4" s="115"/>
       <c r="F4" s="117"/>
       <c r="G4" s="117"/>
@@ -31520,7 +31520,7 @@
       <c r="U4" s="117"/>
       <c r="V4" s="117"/>
     </row>
-    <row r="5" spans="1:22" s="116" customFormat="1" ht="15" thickBot="1">
+    <row r="5" spans="1:22" s="116" customFormat="1" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A5" s="119"/>
       <c r="B5" s="120"/>
       <c r="C5" s="121" t="s">
@@ -31546,7 +31546,7 @@
       <c r="U5" s="117"/>
       <c r="V5" s="117"/>
     </row>
-    <row r="6" spans="1:22" s="124" customFormat="1" ht="15" thickBot="1">
+    <row r="6" spans="1:22" s="124" customFormat="1" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A6" s="123"/>
       <c r="F6" s="125"/>
       <c r="G6" s="125"/>
@@ -31566,7 +31566,7 @@
       <c r="U6" s="125"/>
       <c r="V6" s="125"/>
     </row>
-    <row r="7" spans="1:22">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.15">
       <c r="F7" s="129"/>
       <c r="G7" s="129"/>
       <c r="H7" s="129"/>
@@ -31585,7 +31585,7 @@
       <c r="U7" s="129"/>
       <c r="V7" s="129"/>
     </row>
-    <row r="8" spans="1:22" ht="17">
+    <row r="8" spans="1:22" ht="17.25" x14ac:dyDescent="0.2">
       <c r="A8" s="173" t="s">
         <v>469</v>
       </c>
@@ -31609,7 +31609,7 @@
       <c r="U8" s="129"/>
       <c r="V8" s="129"/>
     </row>
-    <row r="9" spans="1:22" ht="12.75" customHeight="1" thickBot="1">
+    <row r="9" spans="1:22" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="131"/>
       <c r="B9" s="131"/>
       <c r="C9" s="131"/>
@@ -31631,22 +31631,22 @@
       <c r="U9" s="129"/>
       <c r="V9" s="129"/>
     </row>
-    <row r="10" spans="1:22" ht="17.25" customHeight="1" thickBot="1">
-      <c r="A10" s="174" t="s">
+    <row r="10" spans="1:22" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="179" t="s">
         <v>321</v>
       </c>
-      <c r="B10" s="175"/>
-      <c r="C10" s="176"/>
+      <c r="B10" s="180"/>
+      <c r="C10" s="181"/>
       <c r="F10" s="129"/>
-      <c r="G10" s="184" t="s">
+      <c r="G10" s="174" t="s">
         <v>281</v>
       </c>
-      <c r="H10" s="184"/>
-      <c r="I10" s="184"/>
-      <c r="J10" s="184"/>
-      <c r="K10" s="184"/>
-      <c r="L10" s="184"/>
-      <c r="M10" s="184"/>
+      <c r="H10" s="174"/>
+      <c r="I10" s="174"/>
+      <c r="J10" s="174"/>
+      <c r="K10" s="174"/>
+      <c r="L10" s="174"/>
+      <c r="M10" s="174"/>
       <c r="N10" s="132"/>
       <c r="O10" s="132"/>
       <c r="P10" s="129"/>
@@ -31657,7 +31657,7 @@
       <c r="U10" s="129"/>
       <c r="V10" s="129"/>
     </row>
-    <row r="11" spans="1:22" ht="15" customHeight="1">
+    <row r="11" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="133" t="s">
         <v>330</v>
       </c>
@@ -31668,13 +31668,13 @@
         <v>1</v>
       </c>
       <c r="F11" s="129"/>
-      <c r="G11" s="184"/>
-      <c r="H11" s="184"/>
-      <c r="I11" s="184"/>
-      <c r="J11" s="184"/>
-      <c r="K11" s="184"/>
-      <c r="L11" s="184"/>
-      <c r="M11" s="184"/>
+      <c r="G11" s="174"/>
+      <c r="H11" s="174"/>
+      <c r="I11" s="174"/>
+      <c r="J11" s="174"/>
+      <c r="K11" s="174"/>
+      <c r="L11" s="174"/>
+      <c r="M11" s="174"/>
       <c r="N11" s="132"/>
       <c r="O11" s="132"/>
       <c r="Q11" s="129"/>
@@ -31684,7 +31684,7 @@
       <c r="U11" s="129"/>
       <c r="V11" s="129"/>
     </row>
-    <row r="12" spans="1:22" ht="15" customHeight="1">
+    <row r="12" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="133" t="s">
         <v>331</v>
       </c>
@@ -31703,7 +31703,7 @@
       <c r="U12" s="129"/>
       <c r="V12" s="129"/>
     </row>
-    <row r="13" spans="1:22" ht="15" thickBot="1">
+    <row r="13" spans="1:22" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A13" s="135" t="s">
         <v>332</v>
       </c>
@@ -31731,7 +31731,7 @@
       <c r="U13" s="129"/>
       <c r="V13" s="129"/>
     </row>
-    <row r="14" spans="1:22" ht="15" thickBot="1">
+    <row r="14" spans="1:22" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B14" s="137"/>
       <c r="F14" s="129"/>
       <c r="G14" s="129"/>
@@ -31751,12 +31751,12 @@
       <c r="U14" s="129"/>
       <c r="V14" s="129"/>
     </row>
-    <row r="15" spans="1:22" ht="15" thickBot="1">
-      <c r="A15" s="174" t="s">
+    <row r="15" spans="1:22" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="179" t="s">
         <v>320</v>
       </c>
-      <c r="B15" s="175"/>
-      <c r="C15" s="176"/>
+      <c r="B15" s="180"/>
+      <c r="C15" s="181"/>
       <c r="F15" s="129"/>
       <c r="G15" s="129"/>
       <c r="H15" s="129"/>
@@ -31775,7 +31775,7 @@
       <c r="U15" s="129"/>
       <c r="V15" s="129"/>
     </row>
-    <row r="16" spans="1:22">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A16" s="133" t="s">
         <v>327</v>
       </c>
@@ -31803,7 +31803,7 @@
       <c r="U16" s="129"/>
       <c r="V16" s="129"/>
     </row>
-    <row r="17" spans="1:22">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A17" s="133" t="s">
         <v>328</v>
       </c>
@@ -31831,7 +31831,7 @@
       <c r="U17" s="129"/>
       <c r="V17" s="129"/>
     </row>
-    <row r="18" spans="1:22" ht="15" thickBot="1">
+    <row r="18" spans="1:22" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A18" s="135" t="s">
         <v>329</v>
       </c>
@@ -31859,7 +31859,7 @@
       <c r="U18" s="129"/>
       <c r="V18" s="129"/>
     </row>
-    <row r="19" spans="1:22" ht="15" thickBot="1">
+    <row r="19" spans="1:22" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B19" s="137"/>
       <c r="F19" s="129"/>
       <c r="G19" s="129"/>
@@ -31879,12 +31879,12 @@
       <c r="U19" s="129"/>
       <c r="V19" s="129"/>
     </row>
-    <row r="20" spans="1:22" ht="15" thickBot="1">
-      <c r="A20" s="174" t="s">
+    <row r="20" spans="1:22" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="179" t="s">
         <v>2</v>
       </c>
-      <c r="B20" s="175"/>
-      <c r="C20" s="176"/>
+      <c r="B20" s="180"/>
+      <c r="C20" s="181"/>
       <c r="F20" s="129"/>
       <c r="G20" s="129"/>
       <c r="H20" s="129"/>
@@ -31903,7 +31903,7 @@
       <c r="U20" s="129"/>
       <c r="V20" s="129"/>
     </row>
-    <row r="21" spans="1:22">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A21" s="133" t="s">
         <v>326</v>
       </c>
@@ -31931,7 +31931,7 @@
       <c r="U21" s="129"/>
       <c r="V21" s="129"/>
     </row>
-    <row r="22" spans="1:22" ht="17" thickBot="1">
+    <row r="22" spans="1:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="135" t="s">
         <v>470</v>
       </c>
@@ -31960,7 +31960,7 @@
       <c r="U22" s="129"/>
       <c r="V22" s="129"/>
     </row>
-    <row r="23" spans="1:22" ht="15" thickBot="1">
+    <row r="23" spans="1:22" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="F23" s="129"/>
       <c r="G23" s="129"/>
       <c r="H23" s="129"/>
@@ -31979,12 +31979,12 @@
       <c r="U23" s="129"/>
       <c r="V23" s="129"/>
     </row>
-    <row r="24" spans="1:22" ht="15" thickBot="1">
-      <c r="A24" s="174" t="s">
+    <row r="24" spans="1:22" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="179" t="s">
         <v>282</v>
       </c>
-      <c r="B24" s="175"/>
-      <c r="C24" s="176"/>
+      <c r="B24" s="180"/>
+      <c r="C24" s="181"/>
       <c r="F24" s="129"/>
       <c r="G24" s="129"/>
       <c r="H24" s="129"/>
@@ -32003,7 +32003,7 @@
       <c r="U24" s="129"/>
       <c r="V24" s="129"/>
     </row>
-    <row r="25" spans="1:22">
+    <row r="25" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A25" s="133" t="s">
         <v>27</v>
       </c>
@@ -32029,7 +32029,7 @@
       <c r="U25" s="129"/>
       <c r="V25" s="129"/>
     </row>
-    <row r="26" spans="1:22">
+    <row r="26" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A26" s="133" t="s">
         <v>325</v>
       </c>
@@ -32057,7 +32057,7 @@
       <c r="U26" s="129"/>
       <c r="V26" s="129"/>
     </row>
-    <row r="27" spans="1:22" ht="16">
+    <row r="27" spans="1:22" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A27" s="133" t="s">
         <v>324</v>
       </c>
@@ -32086,7 +32086,7 @@
       <c r="U27" s="129"/>
       <c r="V27" s="129"/>
     </row>
-    <row r="28" spans="1:22" ht="16">
+    <row r="28" spans="1:22" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A28" s="133" t="s">
         <v>323</v>
       </c>
@@ -32114,7 +32114,7 @@
       <c r="U28" s="129"/>
       <c r="V28" s="129"/>
     </row>
-    <row r="29" spans="1:22">
+    <row r="29" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A29" s="133" t="s">
         <v>158</v>
       </c>
@@ -32143,7 +32143,7 @@
       <c r="U29" s="129"/>
       <c r="V29" s="129"/>
     </row>
-    <row r="30" spans="1:22" ht="15" thickBot="1">
+    <row r="30" spans="1:22" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A30" s="135" t="s">
         <v>322</v>
       </c>
@@ -32172,10 +32172,10 @@
       <c r="U30" s="129"/>
       <c r="V30" s="129"/>
     </row>
-    <row r="31" spans="1:22" ht="17">
-      <c r="A31" s="181"/>
-      <c r="B31" s="181"/>
-      <c r="C31" s="181"/>
+    <row r="31" spans="1:22" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="A31" s="188"/>
+      <c r="B31" s="188"/>
+      <c r="C31" s="188"/>
       <c r="F31" s="129"/>
       <c r="G31" s="129"/>
       <c r="H31" s="129"/>
@@ -32194,7 +32194,7 @@
       <c r="U31" s="129"/>
       <c r="V31" s="129"/>
     </row>
-    <row r="32" spans="1:22" ht="17">
+    <row r="32" spans="1:22" ht="17.25" x14ac:dyDescent="0.2">
       <c r="A32" s="173" t="s">
         <v>283</v>
       </c>
@@ -32218,7 +32218,7 @@
       <c r="U32" s="129"/>
       <c r="V32" s="129"/>
     </row>
-    <row r="33" spans="1:22" ht="9" customHeight="1" thickBot="1">
+    <row r="33" spans="1:22" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A33" s="140"/>
       <c r="B33" s="140"/>
       <c r="C33" s="140"/>
@@ -32240,12 +32240,12 @@
       <c r="U33" s="129"/>
       <c r="V33" s="129"/>
     </row>
-    <row r="34" spans="1:22" ht="15" thickBot="1">
-      <c r="A34" s="174" t="s">
+    <row r="34" spans="1:22" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="179" t="s">
         <v>9</v>
       </c>
-      <c r="B34" s="175"/>
-      <c r="C34" s="176"/>
+      <c r="B34" s="180"/>
+      <c r="C34" s="181"/>
       <c r="F34" s="129"/>
       <c r="G34" s="129"/>
       <c r="H34" s="129"/>
@@ -32264,7 +32264,7 @@
       <c r="U34" s="129"/>
       <c r="V34" s="129"/>
     </row>
-    <row r="35" spans="1:22">
+    <row r="35" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A35" s="133" t="s">
         <v>471</v>
       </c>
@@ -32292,7 +32292,7 @@
       <c r="U35" s="129"/>
       <c r="V35" s="129"/>
     </row>
-    <row r="36" spans="1:22">
+    <row r="36" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A36" s="133" t="s">
         <v>472</v>
       </c>
@@ -32321,7 +32321,7 @@
       <c r="U36" s="129"/>
       <c r="V36" s="129"/>
     </row>
-    <row r="37" spans="1:22" ht="16">
+    <row r="37" spans="1:22" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A37" s="133" t="s">
         <v>473</v>
       </c>
@@ -32350,7 +32350,7 @@
       <c r="U37" s="129"/>
       <c r="V37" s="129"/>
     </row>
-    <row r="38" spans="1:22" ht="15">
+    <row r="38" spans="1:22" ht="15" x14ac:dyDescent="0.25">
       <c r="A38" s="133" t="s">
         <v>29</v>
       </c>
@@ -32378,7 +32378,7 @@
       <c r="U38" s="129"/>
       <c r="V38" s="129"/>
     </row>
-    <row r="39" spans="1:22" ht="15" thickBot="1">
+    <row r="39" spans="1:22" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A39" s="135" t="s">
         <v>474</v>
       </c>
@@ -32407,7 +32407,7 @@
       <c r="U39" s="129"/>
       <c r="V39" s="129"/>
     </row>
-    <row r="40" spans="1:22">
+    <row r="40" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A40" s="133"/>
       <c r="B40" s="144"/>
       <c r="F40" s="129"/>
@@ -32428,7 +32428,7 @@
       <c r="U40" s="129"/>
       <c r="V40" s="129"/>
     </row>
-    <row r="41" spans="1:22" ht="17">
+    <row r="41" spans="1:22" ht="17.25" x14ac:dyDescent="0.2">
       <c r="A41" s="173" t="s">
         <v>286</v>
       </c>
@@ -32452,7 +32452,7 @@
       <c r="U41" s="129"/>
       <c r="V41" s="129"/>
     </row>
-    <row r="42" spans="1:22" ht="7.5" customHeight="1" thickBot="1">
+    <row r="42" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A42" s="133"/>
       <c r="B42" s="144"/>
       <c r="F42" s="129"/>
@@ -32473,12 +32473,12 @@
       <c r="U42" s="129"/>
       <c r="V42" s="129"/>
     </row>
-    <row r="43" spans="1:22" ht="15" thickBot="1">
-      <c r="A43" s="174" t="s">
+    <row r="43" spans="1:22" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="179" t="s">
         <v>287</v>
       </c>
-      <c r="B43" s="175"/>
-      <c r="C43" s="176"/>
+      <c r="B43" s="180"/>
+      <c r="C43" s="181"/>
       <c r="F43" s="129"/>
       <c r="G43" s="129"/>
       <c r="H43" s="129"/>
@@ -32497,7 +32497,7 @@
       <c r="U43" s="129"/>
       <c r="V43" s="129"/>
     </row>
-    <row r="44" spans="1:22">
+    <row r="44" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A44" s="133" t="s">
         <v>340</v>
       </c>
@@ -32525,7 +32525,7 @@
       <c r="U44" s="129"/>
       <c r="V44" s="129"/>
     </row>
-    <row r="45" spans="1:22">
+    <row r="45" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A45" s="133" t="s">
         <v>344</v>
       </c>
@@ -32554,7 +32554,7 @@
       <c r="U45" s="129"/>
       <c r="V45" s="129"/>
     </row>
-    <row r="46" spans="1:22" ht="16">
+    <row r="46" spans="1:22" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A46" s="133" t="s">
         <v>341</v>
       </c>
@@ -32583,7 +32583,7 @@
       <c r="U46" s="129"/>
       <c r="V46" s="129"/>
     </row>
-    <row r="47" spans="1:22" ht="16">
+    <row r="47" spans="1:22" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A47" s="133" t="s">
         <v>342</v>
       </c>
@@ -32611,7 +32611,7 @@
       <c r="U47" s="129"/>
       <c r="V47" s="129"/>
     </row>
-    <row r="48" spans="1:22" ht="15" thickBot="1">
+    <row r="48" spans="1:22" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A48" s="135" t="s">
         <v>343</v>
       </c>
@@ -32640,7 +32640,7 @@
       <c r="U48" s="129"/>
       <c r="V48" s="129"/>
     </row>
-    <row r="49" spans="1:22">
+    <row r="49" spans="1:22" x14ac:dyDescent="0.15">
       <c r="B49" s="144"/>
       <c r="F49" s="129"/>
       <c r="G49" s="129"/>
@@ -32660,7 +32660,7 @@
       <c r="U49" s="129"/>
       <c r="V49" s="129"/>
     </row>
-    <row r="50" spans="1:22" ht="17">
+    <row r="50" spans="1:22" ht="17.25" x14ac:dyDescent="0.2">
       <c r="A50" s="173" t="s">
         <v>289</v>
       </c>
@@ -32684,7 +32684,7 @@
       <c r="U50" s="129"/>
       <c r="V50" s="129"/>
     </row>
-    <row r="51" spans="1:22" ht="6.75" customHeight="1" thickBot="1">
+    <row r="51" spans="1:22" ht="6.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B51" s="144"/>
       <c r="F51" s="129"/>
       <c r="G51" s="129"/>
@@ -32704,12 +32704,12 @@
       <c r="U51" s="129"/>
       <c r="V51" s="129"/>
     </row>
-    <row r="52" spans="1:22" ht="15" thickBot="1">
-      <c r="A52" s="174" t="s">
+    <row r="52" spans="1:22" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="179" t="s">
         <v>338</v>
       </c>
-      <c r="B52" s="175"/>
-      <c r="C52" s="176"/>
+      <c r="B52" s="180"/>
+      <c r="C52" s="181"/>
       <c r="F52" s="129"/>
       <c r="G52" s="129"/>
       <c r="H52" s="129"/>
@@ -32728,7 +32728,7 @@
       <c r="U52" s="129"/>
       <c r="V52" s="129"/>
     </row>
-    <row r="53" spans="1:22" ht="16">
+    <row r="53" spans="1:22" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A53" s="133" t="s">
         <v>347</v>
       </c>
@@ -32756,7 +32756,7 @@
       <c r="U53" s="129"/>
       <c r="V53" s="129"/>
     </row>
-    <row r="54" spans="1:22" ht="16" thickBot="1">
+    <row r="54" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="135" t="s">
         <v>345</v>
       </c>
@@ -32784,12 +32784,12 @@
       <c r="U54" s="129"/>
       <c r="V54" s="129"/>
     </row>
-    <row r="55" spans="1:22" ht="15" thickBot="1">
-      <c r="A55" s="174" t="s">
+    <row r="55" spans="1:22" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="179" t="s">
         <v>339</v>
       </c>
-      <c r="B55" s="175"/>
-      <c r="C55" s="176"/>
+      <c r="B55" s="180"/>
+      <c r="C55" s="181"/>
       <c r="F55" s="129"/>
       <c r="G55" s="129"/>
       <c r="H55" s="129"/>
@@ -32808,7 +32808,7 @@
       <c r="U55" s="129"/>
       <c r="V55" s="129"/>
     </row>
-    <row r="56" spans="1:22" ht="16">
+    <row r="56" spans="1:22" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A56" s="133" t="s">
         <v>348</v>
       </c>
@@ -32836,7 +32836,7 @@
       <c r="U56" s="129"/>
       <c r="V56" s="129"/>
     </row>
-    <row r="57" spans="1:22" ht="16" thickBot="1">
+    <row r="57" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="135" t="s">
         <v>346</v>
       </c>
@@ -32864,7 +32864,7 @@
       <c r="U57" s="129"/>
       <c r="V57" s="129"/>
     </row>
-    <row r="58" spans="1:22">
+    <row r="58" spans="1:22" x14ac:dyDescent="0.15">
       <c r="F58" s="129"/>
       <c r="G58" s="129"/>
       <c r="H58" s="129"/>
@@ -32883,7 +32883,7 @@
       <c r="U58" s="129"/>
       <c r="V58" s="129"/>
     </row>
-    <row r="59" spans="1:22" ht="17">
+    <row r="59" spans="1:22" ht="17.25" x14ac:dyDescent="0.2">
       <c r="A59" s="173" t="s">
         <v>295</v>
       </c>
@@ -32907,7 +32907,7 @@
       <c r="U59" s="129"/>
       <c r="V59" s="129"/>
     </row>
-    <row r="60" spans="1:22" ht="6" customHeight="1" thickBot="1">
+    <row r="60" spans="1:22" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="F60" s="129"/>
       <c r="G60" s="129"/>
       <c r="H60" s="129"/>
@@ -32926,12 +32926,12 @@
       <c r="U60" s="129"/>
       <c r="V60" s="129"/>
     </row>
-    <row r="61" spans="1:22" ht="15" thickBot="1">
-      <c r="A61" s="174" t="s">
+    <row r="61" spans="1:22" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="179" t="s">
         <v>296</v>
       </c>
-      <c r="B61" s="175"/>
-      <c r="C61" s="176"/>
+      <c r="B61" s="180"/>
+      <c r="C61" s="181"/>
       <c r="F61" s="129"/>
       <c r="G61" s="129"/>
       <c r="H61" s="129"/>
@@ -32942,17 +32942,17 @@
       <c r="M61" s="129"/>
       <c r="N61" s="129"/>
       <c r="O61" s="129"/>
-      <c r="P61" s="187" t="s">
+      <c r="P61" s="177" t="s">
         <v>384</v>
       </c>
-      <c r="Q61" s="188"/>
+      <c r="Q61" s="178"/>
       <c r="R61" s="129"/>
       <c r="S61" s="130"/>
       <c r="T61" s="129"/>
       <c r="U61" s="129"/>
       <c r="V61" s="129"/>
     </row>
-    <row r="62" spans="1:22" ht="16">
+    <row r="62" spans="1:22" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A62" s="146" t="s">
         <v>349</v>
       </c>
@@ -32980,7 +32980,7 @@
       <c r="U62" s="129"/>
       <c r="V62" s="129"/>
     </row>
-    <row r="63" spans="1:22" ht="16">
+    <row r="63" spans="1:22" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A63" s="133" t="s">
         <v>350</v>
       </c>
@@ -33009,7 +33009,7 @@
       <c r="U63" s="129"/>
       <c r="V63" s="129"/>
     </row>
-    <row r="64" spans="1:22" ht="16">
+    <row r="64" spans="1:22" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A64" s="133" t="s">
         <v>351</v>
       </c>
@@ -33037,7 +33037,7 @@
       <c r="U64" s="129"/>
       <c r="V64" s="129"/>
     </row>
-    <row r="65" spans="1:22">
+    <row r="65" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A65" s="133" t="s">
         <v>475</v>
       </c>
@@ -33066,7 +33066,7 @@
       <c r="U65" s="129"/>
       <c r="V65" s="129"/>
     </row>
-    <row r="66" spans="1:22">
+    <row r="66" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A66" s="133" t="s">
         <v>476</v>
       </c>
@@ -33095,7 +33095,7 @@
       <c r="U66" s="129"/>
       <c r="V66" s="129"/>
     </row>
-    <row r="67" spans="1:22" ht="15" thickBot="1">
+    <row r="67" spans="1:22" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A67" s="135" t="s">
         <v>477</v>
       </c>
@@ -33124,7 +33124,7 @@
       <c r="U67" s="129"/>
       <c r="V67" s="129"/>
     </row>
-    <row r="68" spans="1:22">
+    <row r="68" spans="1:22" x14ac:dyDescent="0.15">
       <c r="F68" s="129"/>
       <c r="G68" s="129"/>
       <c r="H68" s="129"/>
@@ -33143,7 +33143,7 @@
       <c r="U68" s="129"/>
       <c r="V68" s="129"/>
     </row>
-    <row r="69" spans="1:22" ht="17">
+    <row r="69" spans="1:22" ht="17.25" x14ac:dyDescent="0.2">
       <c r="A69" s="173" t="s">
         <v>297</v>
       </c>
@@ -33167,7 +33167,7 @@
       <c r="U69" s="129"/>
       <c r="V69" s="129"/>
     </row>
-    <row r="70" spans="1:22" ht="6" customHeight="1" thickBot="1">
+    <row r="70" spans="1:22" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="F70" s="129"/>
       <c r="G70" s="129"/>
       <c r="H70" s="129"/>
@@ -33186,12 +33186,12 @@
       <c r="U70" s="129"/>
       <c r="V70" s="129"/>
     </row>
-    <row r="71" spans="1:22" ht="15" thickBot="1">
-      <c r="A71" s="174" t="s">
+    <row r="71" spans="1:22" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A71" s="179" t="s">
         <v>112</v>
       </c>
-      <c r="B71" s="175"/>
-      <c r="C71" s="176"/>
+      <c r="B71" s="180"/>
+      <c r="C71" s="181"/>
       <c r="F71" s="129"/>
       <c r="G71" s="129"/>
       <c r="H71" s="129"/>
@@ -33210,7 +33210,7 @@
       <c r="U71" s="129"/>
       <c r="V71" s="129"/>
     </row>
-    <row r="72" spans="1:22" ht="15" thickBot="1">
+    <row r="72" spans="1:22" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A72" s="133" t="s">
         <v>352</v>
       </c>
@@ -33238,7 +33238,7 @@
       <c r="U72" s="129"/>
       <c r="V72" s="129"/>
     </row>
-    <row r="73" spans="1:22" ht="17" thickBot="1">
+    <row r="73" spans="1:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="133" t="s">
         <v>353</v>
       </c>
@@ -33249,12 +33249,12 @@
       <c r="C73" s="134" t="s">
         <v>32</v>
       </c>
-      <c r="P73" s="187" t="s">
+      <c r="P73" s="177" t="s">
         <v>384</v>
       </c>
-      <c r="Q73" s="188"/>
+      <c r="Q73" s="178"/>
     </row>
-    <row r="74" spans="1:22" ht="16">
+    <row r="74" spans="1:22" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A74" s="133" t="s">
         <v>354</v>
       </c>
@@ -33265,7 +33265,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="75" spans="1:22" ht="15" thickBot="1">
+    <row r="75" spans="1:22" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A75" s="135" t="s">
         <v>182</v>
       </c>
@@ -33277,22 +33277,22 @@
         <v>114</v>
       </c>
     </row>
-    <row r="77" spans="1:22" ht="17">
+    <row r="77" spans="1:22" ht="17.25" x14ac:dyDescent="0.2">
       <c r="A77" s="173" t="s">
         <v>300</v>
       </c>
       <c r="B77" s="173"/>
       <c r="C77" s="173"/>
     </row>
-    <row r="78" spans="1:22" ht="7.5" customHeight="1" thickBot="1"/>
-    <row r="79" spans="1:22" ht="15" thickBot="1">
-      <c r="A79" s="174" t="s">
+    <row r="78" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2"/>
+    <row r="79" spans="1:22" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A79" s="179" t="s">
         <v>298</v>
       </c>
-      <c r="B79" s="175"/>
-      <c r="C79" s="176"/>
+      <c r="B79" s="180"/>
+      <c r="C79" s="181"/>
     </row>
-    <row r="80" spans="1:22">
+    <row r="80" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A80" s="133" t="s">
         <v>337</v>
       </c>
@@ -33303,7 +33303,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:19" ht="16">
+    <row r="81" spans="1:19" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A81" s="133" t="s">
         <v>355</v>
       </c>
@@ -33315,7 +33315,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="82" spans="1:19" ht="16">
+    <row r="82" spans="1:19" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A82" s="133" t="s">
         <v>356</v>
       </c>
@@ -33326,7 +33326,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="83" spans="1:19" ht="15" thickBot="1">
+    <row r="83" spans="1:19" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A83" s="135" t="s">
         <v>336</v>
       </c>
@@ -33338,14 +33338,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:19" ht="15" thickBot="1">
-      <c r="A84" s="174" t="s">
+    <row r="84" spans="1:19" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A84" s="179" t="s">
         <v>299</v>
       </c>
-      <c r="B84" s="175"/>
-      <c r="C84" s="176"/>
+      <c r="B84" s="180"/>
+      <c r="C84" s="181"/>
     </row>
-    <row r="85" spans="1:19">
+    <row r="85" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A85" s="133" t="s">
         <v>335</v>
       </c>
@@ -33356,7 +33356,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:19" ht="16">
+    <row r="86" spans="1:19" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A86" s="133" t="s">
         <v>357</v>
       </c>
@@ -33368,7 +33368,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="87" spans="1:19" ht="16">
+    <row r="87" spans="1:19" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A87" s="133" t="s">
         <v>358</v>
       </c>
@@ -33379,7 +33379,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="88" spans="1:19" ht="15" thickBot="1">
+    <row r="88" spans="1:19" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A88" s="135" t="s">
         <v>334</v>
       </c>
@@ -33391,14 +33391,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:19" ht="17">
+    <row r="90" spans="1:19" ht="17.25" x14ac:dyDescent="0.2">
       <c r="A90" s="173" t="s">
         <v>463</v>
       </c>
       <c r="B90" s="173"/>
       <c r="C90" s="173"/>
     </row>
-    <row r="91" spans="1:19" ht="6" customHeight="1" thickBot="1">
+    <row r="91" spans="1:19" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="E91" s="129"/>
       <c r="F91" s="129"/>
       <c r="G91" s="129"/>
@@ -33415,12 +33415,12 @@
       <c r="R91" s="129"/>
       <c r="S91" s="130"/>
     </row>
-    <row r="92" spans="1:19" ht="15" thickBot="1">
-      <c r="A92" s="174" t="s">
+    <row r="92" spans="1:19" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A92" s="179" t="s">
         <v>113</v>
       </c>
-      <c r="B92" s="175"/>
-      <c r="C92" s="176"/>
+      <c r="B92" s="180"/>
+      <c r="C92" s="181"/>
       <c r="E92" s="129"/>
       <c r="F92" s="129"/>
       <c r="G92" s="129"/>
@@ -33437,7 +33437,7 @@
       <c r="R92" s="129"/>
       <c r="S92" s="130"/>
     </row>
-    <row r="93" spans="1:19">
+    <row r="93" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A93" s="133" t="s">
         <v>117</v>
       </c>
@@ -33446,28 +33446,28 @@
       </c>
       <c r="C93" s="183"/>
       <c r="E93" s="129"/>
-      <c r="F93" s="185" t="s">
+      <c r="F93" s="175" t="s">
         <v>309</v>
       </c>
-      <c r="G93" s="185"/>
-      <c r="H93" s="185"/>
+      <c r="G93" s="175"/>
+      <c r="H93" s="175"/>
       <c r="I93" s="129"/>
       <c r="J93" s="129"/>
-      <c r="K93" s="185" t="s">
+      <c r="K93" s="175" t="s">
         <v>307</v>
       </c>
-      <c r="L93" s="185"/>
-      <c r="M93" s="185"/>
+      <c r="L93" s="175"/>
+      <c r="M93" s="175"/>
       <c r="N93" s="129"/>
       <c r="O93" s="129"/>
       <c r="P93" s="129"/>
-      <c r="Q93" s="185" t="s">
+      <c r="Q93" s="175" t="s">
         <v>308</v>
       </c>
-      <c r="R93" s="185"/>
+      <c r="R93" s="175"/>
       <c r="S93" s="130"/>
     </row>
-    <row r="94" spans="1:19">
+    <row r="94" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A94" s="133" t="s">
         <v>318</v>
       </c>
@@ -33493,7 +33493,7 @@
       <c r="R94" s="129"/>
       <c r="S94" s="130"/>
     </row>
-    <row r="95" spans="1:19" ht="16">
+    <row r="95" spans="1:19" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A95" s="133" t="s">
         <v>310</v>
       </c>
@@ -33519,7 +33519,7 @@
       <c r="R95" s="129"/>
       <c r="S95" s="130"/>
     </row>
-    <row r="96" spans="1:19" ht="16">
+    <row r="96" spans="1:19" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A96" s="133" t="s">
         <v>464</v>
       </c>
@@ -33546,7 +33546,7 @@
       <c r="R96" s="129"/>
       <c r="S96" s="130"/>
     </row>
-    <row r="97" spans="1:21" ht="16">
+    <row r="97" spans="1:21" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A97" s="133" t="s">
         <v>311</v>
       </c>
@@ -33572,7 +33572,7 @@
       <c r="R97" s="129"/>
       <c r="S97" s="130"/>
     </row>
-    <row r="98" spans="1:21">
+    <row r="98" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A98" s="133" t="s">
         <v>316</v>
       </c>
@@ -33598,7 +33598,7 @@
       <c r="T98" s="150"/>
       <c r="U98" s="150"/>
     </row>
-    <row r="99" spans="1:21">
+    <row r="99" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A99" s="133" t="s">
         <v>241</v>
       </c>
@@ -33624,7 +33624,7 @@
       <c r="R99" s="129"/>
       <c r="S99" s="130"/>
     </row>
-    <row r="100" spans="1:21" ht="16">
+    <row r="100" spans="1:21" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A100" s="133" t="s">
         <v>313</v>
       </c>
@@ -33651,7 +33651,7 @@
       <c r="R100" s="129"/>
       <c r="S100" s="130"/>
     </row>
-    <row r="101" spans="1:21" ht="16">
+    <row r="101" spans="1:21" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A101" s="133" t="s">
         <v>314</v>
       </c>
@@ -33677,7 +33677,7 @@
       <c r="R101" s="129"/>
       <c r="S101" s="130"/>
     </row>
-    <row r="102" spans="1:21">
+    <row r="102" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A102" s="133" t="s">
         <v>315</v>
       </c>
@@ -33704,7 +33704,7 @@
       <c r="R102" s="129"/>
       <c r="S102" s="130"/>
     </row>
-    <row r="103" spans="1:21">
+    <row r="103" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A103" s="133" t="s">
         <v>317</v>
       </c>
@@ -33731,7 +33731,7 @@
       <c r="R103" s="129"/>
       <c r="S103" s="130"/>
     </row>
-    <row r="104" spans="1:21">
+    <row r="104" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A104" s="133" t="s">
         <v>319</v>
       </c>
@@ -33758,7 +33758,7 @@
       <c r="R104" s="129"/>
       <c r="S104" s="130"/>
     </row>
-    <row r="105" spans="1:21" ht="15" thickBot="1">
+    <row r="105" spans="1:21" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A105" s="135" t="s">
         <v>178</v>
       </c>
@@ -33785,7 +33785,7 @@
       <c r="R105" s="129"/>
       <c r="S105" s="130"/>
     </row>
-    <row r="106" spans="1:21">
+    <row r="106" spans="1:21" x14ac:dyDescent="0.15">
       <c r="E106" s="129"/>
       <c r="F106" s="151"/>
       <c r="G106" s="151"/>
@@ -33802,7 +33802,7 @@
       <c r="R106" s="129"/>
       <c r="S106" s="130"/>
     </row>
-    <row r="107" spans="1:21" ht="17">
+    <row r="107" spans="1:21" ht="17.25" x14ac:dyDescent="0.2">
       <c r="A107" s="173" t="s">
         <v>301</v>
       </c>
@@ -33824,7 +33824,7 @@
       <c r="R107" s="129"/>
       <c r="S107" s="130"/>
     </row>
-    <row r="108" spans="1:21" ht="8.25" customHeight="1" thickBot="1">
+    <row r="108" spans="1:21" ht="8.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="E108" s="129"/>
       <c r="F108" s="151"/>
       <c r="G108" s="151"/>
@@ -33841,12 +33841,12 @@
       <c r="R108" s="129"/>
       <c r="S108" s="130"/>
     </row>
-    <row r="109" spans="1:21" ht="15" thickBot="1">
-      <c r="A109" s="174" t="s">
+    <row r="109" spans="1:21" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A109" s="179" t="s">
         <v>302</v>
       </c>
-      <c r="B109" s="175"/>
-      <c r="C109" s="176"/>
+      <c r="B109" s="180"/>
+      <c r="C109" s="181"/>
       <c r="E109" s="129"/>
       <c r="F109" s="129"/>
       <c r="G109" s="129"/>
@@ -33863,7 +33863,7 @@
       <c r="R109" s="129"/>
       <c r="S109" s="130"/>
     </row>
-    <row r="110" spans="1:21" ht="16">
+    <row r="110" spans="1:21" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A110" s="133" t="s">
         <v>478</v>
       </c>
@@ -33889,7 +33889,7 @@
       <c r="R110" s="129"/>
       <c r="S110" s="130"/>
     </row>
-    <row r="111" spans="1:21" ht="16">
+    <row r="111" spans="1:21" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A111" s="133" t="s">
         <v>465</v>
       </c>
@@ -33916,7 +33916,7 @@
       <c r="R111" s="129"/>
       <c r="S111" s="130"/>
     </row>
-    <row r="112" spans="1:21" ht="16">
+    <row r="112" spans="1:21" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A112" s="133" t="s">
         <v>364</v>
       </c>
@@ -33942,7 +33942,7 @@
       <c r="R112" s="129"/>
       <c r="S112" s="130"/>
     </row>
-    <row r="113" spans="1:19" ht="16">
+    <row r="113" spans="1:19" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A113" s="133" t="s">
         <v>480</v>
       </c>
@@ -33969,7 +33969,7 @@
       <c r="R113" s="129"/>
       <c r="S113" s="130"/>
     </row>
-    <row r="114" spans="1:19" ht="16">
+    <row r="114" spans="1:19" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A114" s="133" t="s">
         <v>479</v>
       </c>
@@ -33996,7 +33996,7 @@
       <c r="R114" s="129"/>
       <c r="S114" s="130"/>
     </row>
-    <row r="115" spans="1:19" ht="16">
+    <row r="115" spans="1:19" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A115" s="133" t="s">
         <v>365</v>
       </c>
@@ -34023,7 +34023,7 @@
       <c r="R115" s="129"/>
       <c r="S115" s="130"/>
     </row>
-    <row r="116" spans="1:19" ht="16">
+    <row r="116" spans="1:19" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A116" s="133" t="s">
         <v>366</v>
       </c>
@@ -34049,7 +34049,7 @@
       <c r="R116" s="129"/>
       <c r="S116" s="130"/>
     </row>
-    <row r="117" spans="1:19" ht="16">
+    <row r="117" spans="1:19" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A117" s="133" t="s">
         <v>481</v>
       </c>
@@ -34076,7 +34076,7 @@
       <c r="R117" s="129"/>
       <c r="S117" s="130"/>
     </row>
-    <row r="118" spans="1:19" ht="17" thickBot="1">
+    <row r="118" spans="1:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A118" s="135" t="s">
         <v>482</v>
       </c>
@@ -34103,7 +34103,7 @@
       <c r="R118" s="129"/>
       <c r="S118" s="130"/>
     </row>
-    <row r="119" spans="1:19">
+    <row r="119" spans="1:19" x14ac:dyDescent="0.15">
       <c r="E119" s="129"/>
       <c r="F119" s="129"/>
       <c r="G119" s="129"/>
@@ -34120,7 +34120,7 @@
       <c r="R119" s="129"/>
       <c r="S119" s="130"/>
     </row>
-    <row r="120" spans="1:19" ht="17">
+    <row r="120" spans="1:19" ht="17.25" x14ac:dyDescent="0.2">
       <c r="A120" s="173" t="s">
         <v>304</v>
       </c>
@@ -34142,7 +34142,7 @@
       <c r="R120" s="129"/>
       <c r="S120" s="130"/>
     </row>
-    <row r="121" spans="1:19" ht="6.75" customHeight="1" thickBot="1">
+    <row r="121" spans="1:19" ht="6.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="E121" s="129"/>
       <c r="F121" s="129"/>
       <c r="G121" s="129"/>
@@ -34159,24 +34159,24 @@
       <c r="R121" s="129"/>
       <c r="S121" s="130"/>
     </row>
-    <row r="122" spans="1:19" ht="15" thickBot="1">
-      <c r="A122" s="174" t="s">
+    <row r="122" spans="1:19" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A122" s="179" t="s">
         <v>303</v>
       </c>
-      <c r="B122" s="175"/>
-      <c r="C122" s="176"/>
-      <c r="E122" s="186" t="s">
+      <c r="B122" s="180"/>
+      <c r="C122" s="181"/>
+      <c r="E122" s="176" t="s">
         <v>361</v>
       </c>
-      <c r="F122" s="186"/>
-      <c r="G122" s="186"/>
-      <c r="I122" s="186" t="s">
+      <c r="F122" s="176"/>
+      <c r="G122" s="176"/>
+      <c r="I122" s="176" t="s">
         <v>362</v>
       </c>
-      <c r="J122" s="186"/>
-      <c r="K122" s="186"/>
+      <c r="J122" s="176"/>
+      <c r="K122" s="176"/>
     </row>
-    <row r="123" spans="1:19">
+    <row r="123" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A123" s="133" t="s">
         <v>224</v>
       </c>
@@ -34185,7 +34185,7 @@
       </c>
       <c r="C123" s="183"/>
     </row>
-    <row r="124" spans="1:19">
+    <row r="124" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A124" s="133" t="s">
         <v>359</v>
       </c>
@@ -34196,7 +34196,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="125" spans="1:19" ht="16">
+    <row r="125" spans="1:19" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A125" s="133" t="s">
         <v>466</v>
       </c>
@@ -34208,7 +34208,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="126" spans="1:19" ht="16">
+    <row r="126" spans="1:19" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A126" s="133" t="s">
         <v>360</v>
       </c>
@@ -34219,7 +34219,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="127" spans="1:19">
+    <row r="127" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A127" s="133" t="s">
         <v>237</v>
       </c>
@@ -34231,7 +34231,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="128" spans="1:19" ht="15" thickBot="1">
+    <row r="128" spans="1:19" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A128" s="135" t="s">
         <v>238</v>
       </c>
@@ -34243,22 +34243,22 @@
         <v>97</v>
       </c>
     </row>
-    <row r="131" spans="1:3" ht="17">
+    <row r="131" spans="1:3" ht="17.25" x14ac:dyDescent="0.2">
       <c r="A131" s="173" t="s">
         <v>305</v>
       </c>
       <c r="B131" s="173"/>
       <c r="C131" s="173"/>
     </row>
-    <row r="132" spans="1:3" ht="15" thickBot="1"/>
-    <row r="133" spans="1:3" ht="15" thickBot="1">
-      <c r="A133" s="174" t="s">
+    <row r="132" spans="1:3" ht="14.25" thickBot="1" x14ac:dyDescent="0.2"/>
+    <row r="133" spans="1:3" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A133" s="179" t="s">
         <v>306</v>
       </c>
-      <c r="B133" s="175"/>
-      <c r="C133" s="176"/>
+      <c r="B133" s="180"/>
+      <c r="C133" s="181"/>
     </row>
-    <row r="134" spans="1:3">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A134" s="133" t="s">
         <v>250</v>
       </c>
@@ -34269,7 +34269,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="135" spans="1:3" ht="16">
+    <row r="135" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A135" s="133" t="s">
         <v>363</v>
       </c>
@@ -34281,7 +34281,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="136" spans="1:3" ht="16">
+    <row r="136" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A136" s="133" t="s">
         <v>467</v>
       </c>
@@ -34293,7 +34293,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="137" spans="1:3" ht="16">
+    <row r="137" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A137" s="133" t="s">
         <v>468</v>
       </c>
@@ -34304,7 +34304,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="138" spans="1:3" ht="16">
+    <row r="138" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A138" s="133" t="s">
         <v>367</v>
       </c>
@@ -34316,7 +34316,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="139" spans="1:3" ht="16">
+    <row r="139" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A139" s="133" t="s">
         <v>368</v>
       </c>
@@ -34327,7 +34327,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="140" spans="1:3" ht="16">
+    <row r="140" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A140" s="133" t="s">
         <v>370</v>
       </c>
@@ -34339,7 +34339,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="141" spans="1:3" ht="16">
+    <row r="141" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A141" s="133" t="s">
         <v>369</v>
       </c>
@@ -34350,7 +34350,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="142" spans="1:3" ht="16">
+    <row r="142" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A142" s="133" t="s">
         <v>372</v>
       </c>
@@ -34362,7 +34362,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="143" spans="1:3" ht="16">
+    <row r="143" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A143" s="133" t="s">
         <v>371</v>
       </c>
@@ -34373,7 +34373,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="144" spans="1:3" ht="16">
+    <row r="144" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A144" s="133" t="s">
         <v>374</v>
       </c>
@@ -34385,7 +34385,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="145" spans="1:3" ht="17" thickBot="1">
+    <row r="145" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A145" s="135" t="s">
         <v>373</v>
       </c>
@@ -34397,22 +34397,22 @@
         <v>3</v>
       </c>
     </row>
-    <row r="149" spans="1:3" ht="17">
+    <row r="149" spans="1:3" ht="17.25" x14ac:dyDescent="0.2">
       <c r="A149" s="173" t="s">
         <v>460</v>
       </c>
       <c r="B149" s="173"/>
       <c r="C149" s="173"/>
     </row>
-    <row r="150" spans="1:3" ht="8.25" customHeight="1" thickBot="1"/>
-    <row r="151" spans="1:3" ht="15" thickBot="1">
-      <c r="A151" s="174" t="s">
+    <row r="150" spans="1:3" ht="8.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2"/>
+    <row r="151" spans="1:3" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A151" s="179" t="s">
         <v>459</v>
       </c>
-      <c r="B151" s="175"/>
-      <c r="C151" s="176"/>
+      <c r="B151" s="180"/>
+      <c r="C151" s="181"/>
     </row>
-    <row r="152" spans="1:3" ht="16">
+    <row r="152" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A152" s="146" t="s">
         <v>484</v>
       </c>
@@ -34423,7 +34423,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:3" ht="16">
+    <row r="153" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A153" s="133" t="s">
         <v>485</v>
       </c>
@@ -34434,7 +34434,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="154" spans="1:3" ht="16">
+    <row r="154" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A154" s="133" t="s">
         <v>487</v>
       </c>
@@ -34446,7 +34446,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="155" spans="1:3" ht="16">
+    <row r="155" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A155" s="133" t="s">
         <v>486</v>
       </c>
@@ -34457,7 +34457,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="156" spans="1:3">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A156" s="133" t="s">
         <v>432</v>
       </c>
@@ -34469,7 +34469,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="157" spans="1:3">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A157" s="133" t="s">
         <v>258</v>
       </c>
@@ -34480,7 +34480,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="158" spans="1:3" ht="16">
+    <row r="158" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A158" s="133" t="s">
         <v>455</v>
       </c>
@@ -34492,7 +34492,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="159" spans="1:3" ht="16">
+    <row r="159" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A159" s="133" t="s">
         <v>456</v>
       </c>
@@ -34503,7 +34503,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="160" spans="1:3" ht="16">
+    <row r="160" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A160" s="133" t="s">
         <v>457</v>
       </c>
@@ -34515,7 +34515,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="161" spans="1:3" ht="16">
+    <row r="161" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A161" s="133" t="s">
         <v>458</v>
       </c>
@@ -34526,7 +34526,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="162" spans="1:3" ht="16">
+    <row r="162" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A162" s="133" t="s">
         <v>454</v>
       </c>
@@ -34538,7 +34538,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="163" spans="1:3" ht="16">
+    <row r="163" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A163" s="133" t="s">
         <v>453</v>
       </c>
@@ -34549,7 +34549,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="164" spans="1:3" ht="16">
+    <row r="164" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A164" s="133" t="s">
         <v>374</v>
       </c>
@@ -34561,7 +34561,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="165" spans="1:3" ht="17" thickBot="1">
+    <row r="165" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A165" s="135" t="s">
         <v>373</v>
       </c>
@@ -34573,22 +34573,22 @@
         <v>3</v>
       </c>
     </row>
-    <row r="168" spans="1:3" ht="17">
+    <row r="168" spans="1:3" ht="17.25" x14ac:dyDescent="0.2">
       <c r="A168" s="173" t="s">
         <v>483</v>
       </c>
       <c r="B168" s="173"/>
       <c r="C168" s="173"/>
     </row>
-    <row r="169" spans="1:3" ht="15" thickBot="1"/>
-    <row r="170" spans="1:3" ht="15" thickBot="1">
-      <c r="A170" s="174" t="s">
+    <row r="169" spans="1:3" ht="14.25" thickBot="1" x14ac:dyDescent="0.2"/>
+    <row r="170" spans="1:3" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A170" s="179" t="s">
         <v>461</v>
       </c>
-      <c r="B170" s="175"/>
-      <c r="C170" s="176"/>
+      <c r="B170" s="180"/>
+      <c r="C170" s="181"/>
     </row>
-    <row r="171" spans="1:3" ht="16">
+    <row r="171" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A171" s="146" t="s">
         <v>484</v>
       </c>
@@ -34599,7 +34599,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="172" spans="1:3" ht="16">
+    <row r="172" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A172" s="133" t="s">
         <v>485</v>
       </c>
@@ -34610,7 +34610,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="173" spans="1:3" ht="16">
+    <row r="173" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A173" s="133" t="s">
         <v>487</v>
       </c>
@@ -34622,7 +34622,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="174" spans="1:3" ht="16">
+    <row r="174" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A174" s="133" t="s">
         <v>486</v>
       </c>
@@ -34633,7 +34633,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="175" spans="1:3">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A175" s="133" t="s">
         <v>432</v>
       </c>
@@ -34645,7 +34645,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="176" spans="1:3">
+    <row r="176" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A176" s="133" t="s">
         <v>258</v>
       </c>
@@ -34656,7 +34656,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="177" spans="1:3" ht="16">
+    <row r="177" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A177" s="133" t="s">
         <v>428</v>
       </c>
@@ -34668,7 +34668,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="178" spans="1:3" ht="16">
+    <row r="178" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A178" s="133" t="s">
         <v>427</v>
       </c>
@@ -34679,7 +34679,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="179" spans="1:3" ht="16">
+    <row r="179" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A179" s="133" t="s">
         <v>426</v>
       </c>
@@ -34691,7 +34691,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="180" spans="1:3" ht="16">
+    <row r="180" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A180" s="133" t="s">
         <v>429</v>
       </c>
@@ -34702,7 +34702,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="181" spans="1:3" ht="16">
+    <row r="181" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A181" s="133" t="s">
         <v>430</v>
       </c>
@@ -34714,7 +34714,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="182" spans="1:3" ht="16">
+    <row r="182" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A182" s="133" t="s">
         <v>431</v>
       </c>
@@ -34725,7 +34725,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="183" spans="1:3" ht="16">
+    <row r="183" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A183" s="133" t="s">
         <v>374</v>
       </c>
@@ -34737,7 +34737,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="184" spans="1:3" ht="17" thickBot="1">
+    <row r="184" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A184" s="135" t="s">
         <v>373</v>
       </c>
@@ -34752,6 +34752,34 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="fdU52W4crYajbraSt7Ih5pmYR8gmHjUDwlpQIF4YYH9Fakzt1D1AAwKy17nH/MLXUijSXtaMyzWZLUNwvQ0pfg==" saltValue="U5ME1tcmw0TPKCAZJxVidQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="44">
+    <mergeCell ref="A149:C149"/>
+    <mergeCell ref="A151:C151"/>
+    <mergeCell ref="A168:C168"/>
+    <mergeCell ref="A170:C170"/>
+    <mergeCell ref="A1:XFD3"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A133:C133"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="A52:C52"/>
+    <mergeCell ref="A55:C55"/>
+    <mergeCell ref="A59:C59"/>
+    <mergeCell ref="A69:C69"/>
+    <mergeCell ref="A84:C84"/>
+    <mergeCell ref="A77:C77"/>
+    <mergeCell ref="A90:C90"/>
+    <mergeCell ref="A109:C109"/>
+    <mergeCell ref="A107:C107"/>
+    <mergeCell ref="A122:C122"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="B98:C98"/>
     <mergeCell ref="A131:C131"/>
     <mergeCell ref="G10:M11"/>
     <mergeCell ref="F93:H93"/>
@@ -34768,34 +34796,6 @@
     <mergeCell ref="A71:C71"/>
     <mergeCell ref="A43:C43"/>
     <mergeCell ref="A61:C61"/>
-    <mergeCell ref="A90:C90"/>
-    <mergeCell ref="A109:C109"/>
-    <mergeCell ref="A107:C107"/>
-    <mergeCell ref="A122:C122"/>
-    <mergeCell ref="B123:C123"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="A52:C52"/>
-    <mergeCell ref="A55:C55"/>
-    <mergeCell ref="A59:C59"/>
-    <mergeCell ref="A69:C69"/>
-    <mergeCell ref="A84:C84"/>
-    <mergeCell ref="A77:C77"/>
-    <mergeCell ref="A149:C149"/>
-    <mergeCell ref="A151:C151"/>
-    <mergeCell ref="A168:C168"/>
-    <mergeCell ref="A170:C170"/>
-    <mergeCell ref="A1:XFD3"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="A133:C133"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="A50:C50"/>
   </mergeCells>
   <phoneticPr fontId="30"/>
   <hyperlinks>
@@ -35050,16 +35050,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C938147A-1FCB-422A-9F91-062C401E57FB}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:AM47"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="25.6640625" style="166" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.625" style="166" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="56.5" style="167" customWidth="1"/>
-    <col min="3" max="11" width="9.1640625" style="160"/>
+    <col min="3" max="11" width="9.125" style="160"/>
     <col min="12" max="12" width="20.5" style="160" customWidth="1"/>
-    <col min="13" max="16384" width="9.1640625" style="160"/>
+    <col min="13" max="16384" width="9.125" style="160"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="190"/>
       <c r="B1" s="190"/>
       <c r="C1" s="190"/>
@@ -35073,7 +35073,7 @@
       <c r="K1" s="190"/>
       <c r="L1" s="190"/>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="190"/>
       <c r="B2" s="190"/>
       <c r="C2" s="190"/>
@@ -35087,7 +35087,7 @@
       <c r="K2" s="190"/>
       <c r="L2" s="190"/>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" s="190"/>
       <c r="B3" s="190"/>
       <c r="C3" s="190"/>
@@ -35101,7 +35101,7 @@
       <c r="K3" s="190"/>
       <c r="L3" s="190"/>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="191"/>
       <c r="B4" s="191"/>
       <c r="C4" s="191"/>
@@ -35115,7 +35115,7 @@
       <c r="K4" s="191"/>
       <c r="L4" s="191"/>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="161" t="s">
         <v>489</v>
       </c>
@@ -35134,7 +35134,7 @@
       <c r="K5" s="164"/>
       <c r="L5" s="165"/>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="161"/>
       <c r="B6" s="162"/>
       <c r="C6" s="163"/>
@@ -35148,7 +35148,7 @@
       <c r="K6" s="165"/>
       <c r="L6" s="165"/>
     </row>
-    <row r="35" spans="1:39">
+    <row r="35" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A35" s="168" t="s">
         <v>491</v>
       </c>
@@ -35163,7 +35163,7 @@
       <c r="J35" s="163"/>
       <c r="K35" s="163"/>
     </row>
-    <row r="36" spans="1:39">
+    <row r="36" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A36" s="170" t="s">
         <v>492</v>
       </c>
@@ -35180,7 +35180,7 @@
       <c r="J36" s="192"/>
       <c r="K36" s="192"/>
     </row>
-    <row r="37" spans="1:39">
+    <row r="37" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A37" s="168" t="s">
         <v>490</v>
       </c>
@@ -35197,7 +35197,7 @@
       <c r="J37" s="193"/>
       <c r="K37" s="193"/>
     </row>
-    <row r="38" spans="1:39" ht="14.25" customHeight="1">
+    <row r="38" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="168" t="s">
         <v>495</v>
       </c>
@@ -35214,7 +35214,7 @@
       <c r="J38" s="193"/>
       <c r="K38" s="193"/>
     </row>
-    <row r="39" spans="1:39" ht="14.25" customHeight="1">
+    <row r="39" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="168"/>
       <c r="B39" s="189"/>
       <c r="C39" s="189"/>
@@ -35227,7 +35227,7 @@
       <c r="J39" s="189"/>
       <c r="K39" s="189"/>
     </row>
-    <row r="40" spans="1:39" ht="14.25" customHeight="1">
+    <row r="40" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="168"/>
       <c r="B40" s="189"/>
       <c r="C40" s="189"/>
@@ -35240,7 +35240,7 @@
       <c r="J40" s="189"/>
       <c r="K40" s="189"/>
     </row>
-    <row r="41" spans="1:39" ht="14.25" customHeight="1">
+    <row r="41" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="168"/>
       <c r="B41" s="189"/>
       <c r="C41" s="189"/>
@@ -35253,7 +35253,7 @@
       <c r="J41" s="189"/>
       <c r="K41" s="189"/>
     </row>
-    <row r="42" spans="1:39">
+    <row r="42" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A42" s="168"/>
       <c r="B42" s="189"/>
       <c r="C42" s="189"/>
@@ -35266,7 +35266,7 @@
       <c r="J42" s="189"/>
       <c r="K42" s="189"/>
     </row>
-    <row r="43" spans="1:39">
+    <row r="43" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A43" s="168"/>
       <c r="B43" s="189"/>
       <c r="C43" s="189"/>
@@ -35279,7 +35279,7 @@
       <c r="J43" s="189"/>
       <c r="K43" s="189"/>
     </row>
-    <row r="44" spans="1:39">
+    <row r="44" spans="1:39" ht="15" x14ac:dyDescent="0.2">
       <c r="A44" s="168"/>
       <c r="B44" s="189"/>
       <c r="C44" s="189"/>
@@ -35320,7 +35320,7 @@
       <c r="AL44" s="171"/>
       <c r="AM44" s="171"/>
     </row>
-    <row r="45" spans="1:39">
+    <row r="45" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A45" s="168"/>
       <c r="B45" s="189"/>
       <c r="C45" s="189"/>
@@ -35333,7 +35333,7 @@
       <c r="J45" s="189"/>
       <c r="K45" s="189"/>
     </row>
-    <row r="46" spans="1:39">
+    <row r="46" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A46" s="168"/>
       <c r="B46" s="189"/>
       <c r="C46" s="189"/>
@@ -35346,7 +35346,7 @@
       <c r="J46" s="189"/>
       <c r="K46" s="189"/>
     </row>
-    <row r="47" spans="1:39">
+    <row r="47" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A47" s="168"/>
       <c r="B47" s="189"/>
       <c r="C47" s="189"/>
@@ -35362,12 +35362,6 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="5qE34U5q/yBhg7STOFPUv88vScnDIX6LSJXkXZZoEDGlf2xyJ9tb1iRHmvB8K7kFYfV2kEAhxpH5QBakawGgAg==" saltValue="eUds3aBXmyc9/xlWEDMFXg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1" selectUnlockedCells="1"/>
   <mergeCells count="14">
-    <mergeCell ref="B39:K39"/>
-    <mergeCell ref="A1:L3"/>
-    <mergeCell ref="A4:L4"/>
-    <mergeCell ref="B36:K36"/>
-    <mergeCell ref="B37:K37"/>
-    <mergeCell ref="B38:K38"/>
     <mergeCell ref="B46:K46"/>
     <mergeCell ref="B47:K47"/>
     <mergeCell ref="B40:K40"/>
@@ -35376,6 +35370,12 @@
     <mergeCell ref="B43:K43"/>
     <mergeCell ref="B44:K44"/>
     <mergeCell ref="B45:K45"/>
+    <mergeCell ref="B39:K39"/>
+    <mergeCell ref="A1:L3"/>
+    <mergeCell ref="A4:L4"/>
+    <mergeCell ref="B36:K36"/>
+    <mergeCell ref="B37:K37"/>
+    <mergeCell ref="B38:K38"/>
   </mergeCells>
   <phoneticPr fontId="30"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -35388,71 +35388,71 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A2:AP201"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="46.5" style="34" customWidth="1"/>
-    <col min="2" max="2" width="12.6640625" style="33" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.625" style="33" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" style="34" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.33203125" style="34" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.33203125" style="34" customWidth="1"/>
-    <col min="6" max="11" width="10.33203125" customWidth="1"/>
-    <col min="12" max="12" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.375" style="34" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.375" style="34" customWidth="1"/>
+    <col min="6" max="11" width="10.375" customWidth="1"/>
+    <col min="12" max="12" width="10.875" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="10.5" customWidth="1"/>
     <col min="16" max="16" width="12" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="9.5" customWidth="1"/>
     <col min="18" max="19" width="12" customWidth="1"/>
     <col min="20" max="20" width="11.5" customWidth="1"/>
     <col min="29" max="29" width="11" customWidth="1"/>
-    <col min="32" max="32" width="12.33203125" customWidth="1"/>
-    <col min="56" max="56" width="9.1640625" customWidth="1"/>
-    <col min="59" max="59" width="9.1640625" customWidth="1"/>
+    <col min="32" max="32" width="12.375" customWidth="1"/>
+    <col min="56" max="56" width="9.125" customWidth="1"/>
+    <col min="59" max="59" width="9.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:39">
+    <row r="2" spans="1:39" x14ac:dyDescent="0.15">
       <c r="N2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:39" ht="15" thickBot="1"/>
-    <row r="4" spans="1:39">
-      <c r="P4" s="203" t="s">
+    <row r="3" spans="1:39" ht="14.25" thickBot="1" x14ac:dyDescent="0.2"/>
+    <row r="4" spans="1:39" x14ac:dyDescent="0.15">
+      <c r="P4" s="196" t="s">
         <v>375</v>
       </c>
-      <c r="Q4" s="204"/>
-      <c r="R4" s="204"/>
-      <c r="S4" s="205"/>
-      <c r="T4" s="203" t="s">
+      <c r="Q4" s="197"/>
+      <c r="R4" s="197"/>
+      <c r="S4" s="198"/>
+      <c r="T4" s="196" t="s">
         <v>24</v>
       </c>
-      <c r="U4" s="204"/>
-      <c r="V4" s="204"/>
-      <c r="W4" s="205"/>
-      <c r="X4" s="203" t="s">
+      <c r="U4" s="197"/>
+      <c r="V4" s="197"/>
+      <c r="W4" s="198"/>
+      <c r="X4" s="196" t="s">
         <v>75</v>
       </c>
-      <c r="Y4" s="204"/>
-      <c r="Z4" s="204"/>
-      <c r="AA4" s="205"/>
-      <c r="AB4" s="203" t="s">
+      <c r="Y4" s="197"/>
+      <c r="Z4" s="197"/>
+      <c r="AA4" s="198"/>
+      <c r="AB4" s="196" t="s">
         <v>376</v>
       </c>
-      <c r="AC4" s="204"/>
-      <c r="AD4" s="204"/>
-      <c r="AE4" s="205"/>
-      <c r="AF4" s="203" t="s">
+      <c r="AC4" s="197"/>
+      <c r="AD4" s="197"/>
+      <c r="AE4" s="198"/>
+      <c r="AF4" s="196" t="s">
         <v>377</v>
       </c>
-      <c r="AG4" s="204"/>
-      <c r="AH4" s="204"/>
-      <c r="AI4" s="205"/>
-      <c r="AJ4" s="203" t="s">
+      <c r="AG4" s="197"/>
+      <c r="AH4" s="197"/>
+      <c r="AI4" s="198"/>
+      <c r="AJ4" s="196" t="s">
         <v>378</v>
       </c>
-      <c r="AK4" s="204"/>
-      <c r="AL4" s="204"/>
-      <c r="AM4" s="205"/>
+      <c r="AK4" s="197"/>
+      <c r="AL4" s="197"/>
+      <c r="AM4" s="198"/>
     </row>
-    <row r="5" spans="1:39" ht="45">
+    <row r="5" spans="1:39" ht="40.5" x14ac:dyDescent="0.15">
       <c r="D5" s="48" t="s">
         <v>90</v>
       </c>
@@ -35541,12 +35541,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:39">
-      <c r="A6" s="195" t="s">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.15">
+      <c r="A6" s="199" t="s">
         <v>118</v>
       </c>
-      <c r="B6" s="195"/>
-      <c r="C6" s="195"/>
+      <c r="B6" s="199"/>
+      <c r="C6" s="199"/>
       <c r="E6" s="74" t="s">
         <v>333</v>
       </c>
@@ -35654,7 +35654,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:39">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.15">
       <c r="A7" s="31" t="s">
         <v>108</v>
       </c>
@@ -35776,7 +35776,7 @@
         <v>3.6437063197630035</v>
       </c>
     </row>
-    <row r="8" spans="1:39">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.15">
       <c r="A8" s="31" t="s">
         <v>109</v>
       </c>
@@ -35898,7 +35898,7 @@
         <v>5.1529788947133968</v>
       </c>
     </row>
-    <row r="9" spans="1:39">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.15">
       <c r="A9" s="31" t="s">
         <v>110</v>
       </c>
@@ -36020,12 +36020,12 @@
         <v>6.3110844736893332</v>
       </c>
     </row>
-    <row r="10" spans="1:39">
-      <c r="A10" s="195" t="s">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.15">
+      <c r="A10" s="199" t="s">
         <v>121</v>
       </c>
-      <c r="B10" s="195"/>
-      <c r="C10" s="195"/>
+      <c r="B10" s="199"/>
+      <c r="C10" s="199"/>
       <c r="I10" s="39"/>
       <c r="J10" t="s">
         <v>145</v>
@@ -36134,7 +36134,7 @@
         <v>7.3191489361702127</v>
       </c>
     </row>
-    <row r="11" spans="1:39">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.15">
       <c r="A11" s="31" t="s">
         <v>76</v>
       </c>
@@ -36252,7 +36252,7 @@
         <v>8.3191489361702118</v>
       </c>
     </row>
-    <row r="12" spans="1:39">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.15">
       <c r="A12" s="31" t="s">
         <v>77</v>
       </c>
@@ -36370,7 +36370,7 @@
         <v>9.3191489361702118</v>
       </c>
     </row>
-    <row r="13" spans="1:39">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.15">
       <c r="A13" s="31" t="s">
         <v>78</v>
       </c>
@@ -36488,12 +36488,12 @@
         <v>10.319148936170212</v>
       </c>
     </row>
-    <row r="14" spans="1:39">
-      <c r="A14" s="195" t="s">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.15">
+      <c r="A14" s="199" t="s">
         <v>86</v>
       </c>
-      <c r="B14" s="195"/>
-      <c r="C14" s="195"/>
+      <c r="B14" s="199"/>
+      <c r="C14" s="199"/>
       <c r="N14">
         <v>8.0000000000000002E-3</v>
       </c>
@@ -36598,7 +36598,7 @@
         <v>11.319148936170212</v>
       </c>
     </row>
-    <row r="15" spans="1:39">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.15">
       <c r="A15" s="31" t="s">
         <v>129</v>
       </c>
@@ -36720,7 +36720,7 @@
         <v>12.319148936170212</v>
       </c>
     </row>
-    <row r="16" spans="1:39">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.15">
       <c r="A16" s="31" t="s">
         <v>149</v>
       </c>
@@ -36841,7 +36841,7 @@
         <v>13.319148936170212</v>
       </c>
     </row>
-    <row r="17" spans="1:39">
+    <row r="17" spans="1:39" x14ac:dyDescent="0.15">
       <c r="A17" s="31" t="s">
         <v>88</v>
       </c>
@@ -36960,7 +36960,7 @@
         <v>14.319148936170212</v>
       </c>
     </row>
-    <row r="18" spans="1:39">
+    <row r="18" spans="1:39" x14ac:dyDescent="0.15">
       <c r="A18" s="31" t="s">
         <v>89</v>
       </c>
@@ -37079,7 +37079,7 @@
         <v>15.319148936170212</v>
       </c>
     </row>
-    <row r="19" spans="1:39">
+    <row r="19" spans="1:39" x14ac:dyDescent="0.15">
       <c r="N19">
         <v>1.2999999999999999E-2</v>
       </c>
@@ -37184,7 +37184,7 @@
         <v>16.319148936170212</v>
       </c>
     </row>
-    <row r="20" spans="1:39">
+    <row r="20" spans="1:39" x14ac:dyDescent="0.15">
       <c r="N20">
         <v>1.4E-2</v>
       </c>
@@ -37289,12 +37289,12 @@
         <v>17.319148936170212</v>
       </c>
     </row>
-    <row r="21" spans="1:39">
-      <c r="A21" s="196" t="s">
+    <row r="21" spans="1:39" x14ac:dyDescent="0.15">
+      <c r="A21" s="200" t="s">
         <v>131</v>
       </c>
-      <c r="B21" s="197"/>
-      <c r="C21" s="198"/>
+      <c r="B21" s="201"/>
+      <c r="C21" s="202"/>
       <c r="N21">
         <v>1.4999999999999999E-2</v>
       </c>
@@ -37399,7 +37399,7 @@
         <v>18.319148936170212</v>
       </c>
     </row>
-    <row r="22" spans="1:39">
+    <row r="22" spans="1:39" x14ac:dyDescent="0.15">
       <c r="A22" s="31" t="s">
         <v>44</v>
       </c>
@@ -37514,7 +37514,7 @@
         <v>19.319148936170212</v>
       </c>
     </row>
-    <row r="23" spans="1:39">
+    <row r="23" spans="1:39" x14ac:dyDescent="0.15">
       <c r="A23" s="31" t="s">
         <v>132</v>
       </c>
@@ -37632,7 +37632,7 @@
         <v>20.319148936170212</v>
       </c>
     </row>
-    <row r="24" spans="1:39">
+    <row r="24" spans="1:39" x14ac:dyDescent="0.15">
       <c r="A24" s="31" t="s">
         <v>134</v>
       </c>
@@ -37748,7 +37748,7 @@
         <v>21.319148936170212</v>
       </c>
     </row>
-    <row r="25" spans="1:39">
+    <row r="25" spans="1:39" x14ac:dyDescent="0.15">
       <c r="A25" s="31" t="s">
         <v>143</v>
       </c>
@@ -37866,7 +37866,7 @@
         <v>22.319148936170212</v>
       </c>
     </row>
-    <row r="26" spans="1:39">
+    <row r="26" spans="1:39" x14ac:dyDescent="0.15">
       <c r="A26" s="31" t="s">
         <v>197</v>
       </c>
@@ -37984,7 +37984,7 @@
         <v>23.319148936170212</v>
       </c>
     </row>
-    <row r="27" spans="1:39">
+    <row r="27" spans="1:39" x14ac:dyDescent="0.15">
       <c r="A27" s="31" t="s">
         <v>139</v>
       </c>
@@ -38102,7 +38102,7 @@
         <v>24.319148936170212</v>
       </c>
     </row>
-    <row r="28" spans="1:39">
+    <row r="28" spans="1:39" x14ac:dyDescent="0.15">
       <c r="A28" s="31" t="s">
         <v>141</v>
       </c>
@@ -38220,7 +38220,7 @@
         <v>25.319148936170212</v>
       </c>
     </row>
-    <row r="29" spans="1:39">
+    <row r="29" spans="1:39" x14ac:dyDescent="0.15">
       <c r="A29" s="31" t="s">
         <v>144</v>
       </c>
@@ -38338,7 +38338,7 @@
         <v>26.319148936170212</v>
       </c>
     </row>
-    <row r="30" spans="1:39">
+    <row r="30" spans="1:39" x14ac:dyDescent="0.15">
       <c r="A30" s="31" t="s">
         <v>142</v>
       </c>
@@ -38456,7 +38456,7 @@
         <v>27.319148936170212</v>
       </c>
     </row>
-    <row r="31" spans="1:39">
+    <row r="31" spans="1:39" x14ac:dyDescent="0.15">
       <c r="A31" s="31" t="s">
         <v>146</v>
       </c>
@@ -38574,7 +38574,7 @@
         <v>28.319148936170212</v>
       </c>
     </row>
-    <row r="32" spans="1:39">
+    <row r="32" spans="1:39" x14ac:dyDescent="0.15">
       <c r="A32" s="31" t="s">
         <v>147</v>
       </c>
@@ -38692,7 +38692,7 @@
         <v>29.319148936170212</v>
       </c>
     </row>
-    <row r="33" spans="1:39">
+    <row r="33" spans="1:39" x14ac:dyDescent="0.15">
       <c r="N33">
         <v>2.7E-2</v>
       </c>
@@ -38797,7 +38797,7 @@
         <v>30.319148936170212</v>
       </c>
     </row>
-    <row r="34" spans="1:39">
+    <row r="34" spans="1:39" x14ac:dyDescent="0.15">
       <c r="N34">
         <v>2.8000000000000001E-2</v>
       </c>
@@ -38902,7 +38902,7 @@
         <v>31.319148936170212</v>
       </c>
     </row>
-    <row r="35" spans="1:39">
+    <row r="35" spans="1:39" x14ac:dyDescent="0.15">
       <c r="A35" s="32" t="s">
         <v>148</v>
       </c>
@@ -39012,7 +39012,7 @@
         <v>32.319148936170215</v>
       </c>
     </row>
-    <row r="36" spans="1:39">
+    <row r="36" spans="1:39" x14ac:dyDescent="0.15">
       <c r="A36" s="31" t="s">
         <v>151</v>
       </c>
@@ -39128,7 +39128,7 @@
         <v>33.319148936170215</v>
       </c>
     </row>
-    <row r="37" spans="1:39">
+    <row r="37" spans="1:39" x14ac:dyDescent="0.15">
       <c r="A37" s="31" t="s">
         <v>111</v>
       </c>
@@ -39246,7 +39246,7 @@
         <v>34.319148936170215</v>
       </c>
     </row>
-    <row r="38" spans="1:39">
+    <row r="38" spans="1:39" x14ac:dyDescent="0.15">
       <c r="A38" s="31" t="s">
         <v>5</v>
       </c>
@@ -39361,7 +39361,7 @@
         <v>35.319148936170215</v>
       </c>
     </row>
-    <row r="39" spans="1:39" ht="15">
+    <row r="39" spans="1:39" ht="15" x14ac:dyDescent="0.25">
       <c r="A39" s="31" t="s">
         <v>29</v>
       </c>
@@ -39476,12 +39476,12 @@
         <v>36.319148936170215</v>
       </c>
     </row>
-    <row r="40" spans="1:39" ht="15" thickBot="1">
-      <c r="A40" s="199" t="s">
+    <row r="40" spans="1:39" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="203" t="s">
         <v>10</v>
       </c>
-      <c r="B40" s="200"/>
-      <c r="C40" s="201"/>
+      <c r="B40" s="204"/>
+      <c r="C40" s="205"/>
       <c r="E40" s="34" t="s">
         <v>154</v>
       </c>
@@ -39589,7 +39589,7 @@
         <v>37.319148936170215</v>
       </c>
     </row>
-    <row r="41" spans="1:39">
+    <row r="41" spans="1:39" x14ac:dyDescent="0.15">
       <c r="A41" s="75" t="s">
         <v>82</v>
       </c>
@@ -39704,7 +39704,7 @@
         <v>38.319148936170215</v>
       </c>
     </row>
-    <row r="42" spans="1:39">
+    <row r="42" spans="1:39" x14ac:dyDescent="0.15">
       <c r="A42" s="78" t="s">
         <v>83</v>
       </c>
@@ -39819,7 +39819,7 @@
         <v>39.319148936170215</v>
       </c>
     </row>
-    <row r="43" spans="1:39">
+    <row r="43" spans="1:39" x14ac:dyDescent="0.15">
       <c r="A43" s="78" t="s">
         <v>383</v>
       </c>
@@ -39932,7 +39932,7 @@
         <v>40.319148936170215</v>
       </c>
     </row>
-    <row r="44" spans="1:39">
+    <row r="44" spans="1:39" x14ac:dyDescent="0.15">
       <c r="A44" s="78" t="s">
         <v>74</v>
       </c>
@@ -40047,7 +40047,7 @@
         <v>41.319148936170215</v>
       </c>
     </row>
-    <row r="45" spans="1:39">
+    <row r="45" spans="1:39" x14ac:dyDescent="0.15">
       <c r="A45" s="78" t="s">
         <v>81</v>
       </c>
@@ -40162,7 +40162,7 @@
         <v>42.319148936170215</v>
       </c>
     </row>
-    <row r="46" spans="1:39">
+    <row r="46" spans="1:39" x14ac:dyDescent="0.15">
       <c r="A46" s="78" t="s">
         <v>383</v>
       </c>
@@ -40275,7 +40275,7 @@
         <v>43.319148936170215</v>
       </c>
     </row>
-    <row r="47" spans="1:39">
+    <row r="47" spans="1:39" x14ac:dyDescent="0.15">
       <c r="A47" s="78" t="s">
         <v>84</v>
       </c>
@@ -40390,7 +40390,7 @@
         <v>44.319148936170215</v>
       </c>
     </row>
-    <row r="48" spans="1:39">
+    <row r="48" spans="1:39" x14ac:dyDescent="0.15">
       <c r="A48" s="78" t="s">
         <v>85</v>
       </c>
@@ -40505,7 +40505,7 @@
         <v>45.319148936170215</v>
       </c>
     </row>
-    <row r="49" spans="1:42" ht="15" thickBot="1">
+    <row r="49" spans="1:42" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A49" s="79" t="s">
         <v>383</v>
       </c>
@@ -40618,7 +40618,7 @@
         <v>46.319148936170208</v>
       </c>
     </row>
-    <row r="50" spans="1:42">
+    <row r="50" spans="1:42" x14ac:dyDescent="0.15">
       <c r="A50" s="75" t="s">
         <v>382</v>
       </c>
@@ -40733,7 +40733,7 @@
         <v>47.319148936170215</v>
       </c>
     </row>
-    <row r="51" spans="1:42">
+    <row r="51" spans="1:42" x14ac:dyDescent="0.15">
       <c r="A51" s="78" t="s">
         <v>381</v>
       </c>
@@ -40848,7 +40848,7 @@
         <v>48.319148936170215</v>
       </c>
     </row>
-    <row r="52" spans="1:42">
+    <row r="52" spans="1:42" x14ac:dyDescent="0.15">
       <c r="A52" s="78" t="s">
         <v>383</v>
       </c>
@@ -40961,7 +40961,7 @@
         <v>49.319148936170215</v>
       </c>
     </row>
-    <row r="53" spans="1:42">
+    <row r="53" spans="1:42" x14ac:dyDescent="0.15">
       <c r="A53" s="78" t="s">
         <v>74</v>
       </c>
@@ -41076,7 +41076,7 @@
         <v>50.319148936170215</v>
       </c>
     </row>
-    <row r="54" spans="1:42">
+    <row r="54" spans="1:42" x14ac:dyDescent="0.15">
       <c r="A54" s="78" t="s">
         <v>81</v>
       </c>
@@ -41191,7 +41191,7 @@
         <v>51.319148936170215</v>
       </c>
     </row>
-    <row r="55" spans="1:42">
+    <row r="55" spans="1:42" x14ac:dyDescent="0.15">
       <c r="A55" s="78" t="s">
         <v>383</v>
       </c>
@@ -41304,7 +41304,7 @@
         <v>52.319148936170215</v>
       </c>
     </row>
-    <row r="56" spans="1:42">
+    <row r="56" spans="1:42" x14ac:dyDescent="0.15">
       <c r="A56" s="78" t="s">
         <v>380</v>
       </c>
@@ -41419,7 +41419,7 @@
         <v>53.319148936170215</v>
       </c>
     </row>
-    <row r="57" spans="1:42">
+    <row r="57" spans="1:42" x14ac:dyDescent="0.15">
       <c r="A57" s="78" t="s">
         <v>379</v>
       </c>
@@ -41431,7 +41431,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="58" spans="1:42" ht="15" thickBot="1">
+    <row r="58" spans="1:42" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A58" s="79" t="s">
         <v>383</v>
       </c>
@@ -41456,22 +41456,22 @@
       <c r="Y58" s="40"/>
       <c r="Z58" s="40"/>
       <c r="AA58" s="40"/>
-      <c r="AD58" s="202" t="s">
+      <c r="AD58" s="195" t="s">
         <v>79</v>
       </c>
-      <c r="AE58" s="202"/>
-      <c r="AF58" s="202"/>
-      <c r="AG58" s="202"/>
-      <c r="AH58" s="202"/>
-      <c r="AI58" s="202"/>
-      <c r="AJ58" s="202"/>
-      <c r="AK58" s="202"/>
-      <c r="AL58" s="202"/>
-      <c r="AM58" s="202"/>
-      <c r="AN58" s="202"/>
-      <c r="AO58" s="202"/>
+      <c r="AE58" s="195"/>
+      <c r="AF58" s="195"/>
+      <c r="AG58" s="195"/>
+      <c r="AH58" s="195"/>
+      <c r="AI58" s="195"/>
+      <c r="AJ58" s="195"/>
+      <c r="AK58" s="195"/>
+      <c r="AL58" s="195"/>
+      <c r="AM58" s="195"/>
+      <c r="AN58" s="195"/>
+      <c r="AO58" s="195"/>
     </row>
-    <row r="59" spans="1:42" ht="15" thickBot="1">
+    <row r="59" spans="1:42" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="N59" s="40"/>
       <c r="O59" s="40"/>
       <c r="P59" s="41" t="s">
@@ -41513,7 +41513,7 @@
       <c r="AO59" s="41"/>
       <c r="AP59" s="41"/>
     </row>
-    <row r="60" spans="1:42" ht="31" thickBot="1">
+    <row r="60" spans="1:42" ht="27.75" thickBot="1" x14ac:dyDescent="0.2">
       <c r="N60" s="40"/>
       <c r="O60" s="40" t="s">
         <v>30</v>
@@ -41595,7 +41595,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="61" spans="1:42">
+    <row r="61" spans="1:42" x14ac:dyDescent="0.15">
       <c r="N61">
         <v>0</v>
       </c>
@@ -41707,7 +41707,7 @@
         <v>53.849342928660825</v>
       </c>
     </row>
-    <row r="62" spans="1:42">
+    <row r="62" spans="1:42" x14ac:dyDescent="0.15">
       <c r="N62">
         <v>1</v>
       </c>
@@ -41819,12 +41819,12 @@
         <v>53.871800688360452</v>
       </c>
     </row>
-    <row r="63" spans="1:42">
-      <c r="A63" s="196" t="s">
+    <row r="63" spans="1:42" x14ac:dyDescent="0.15">
+      <c r="A63" s="200" t="s">
         <v>73</v>
       </c>
-      <c r="B63" s="197"/>
-      <c r="C63" s="198"/>
+      <c r="B63" s="201"/>
+      <c r="C63" s="202"/>
       <c r="E63" s="65" t="s">
         <v>152</v>
       </c>
@@ -41939,7 +41939,7 @@
         <v>53.89411764705882</v>
       </c>
     </row>
-    <row r="64" spans="1:42">
+    <row r="64" spans="1:42" x14ac:dyDescent="0.15">
       <c r="A64" s="31" t="s">
         <v>71</v>
       </c>
@@ -42064,7 +42064,7 @@
         <v>53.916293804755945</v>
       </c>
     </row>
-    <row r="65" spans="1:42">
+    <row r="65" spans="1:42" x14ac:dyDescent="0.15">
       <c r="A65" s="31" t="s">
         <v>204</v>
       </c>
@@ -42189,7 +42189,7 @@
         <v>53.938329161451819</v>
       </c>
     </row>
-    <row r="66" spans="1:42">
+    <row r="66" spans="1:42" x14ac:dyDescent="0.15">
       <c r="A66" s="34" t="s">
         <v>288</v>
       </c>
@@ -42311,7 +42311,7 @@
         <v>53.960223717146434</v>
       </c>
     </row>
-    <row r="67" spans="1:42">
+    <row r="67" spans="1:42" x14ac:dyDescent="0.15">
       <c r="A67" s="31" t="s">
         <v>205</v>
       </c>
@@ -42436,7 +42436,7 @@
         <v>53.981977471839798</v>
       </c>
     </row>
-    <row r="68" spans="1:42" ht="15">
+    <row r="68" spans="1:42" ht="15" x14ac:dyDescent="0.25">
       <c r="A68" s="31" t="s">
         <v>206</v>
       </c>
@@ -42561,7 +42561,7 @@
         <v>54.003590425531918</v>
       </c>
     </row>
-    <row r="69" spans="1:42" ht="15">
+    <row r="69" spans="1:42" ht="15" x14ac:dyDescent="0.25">
       <c r="A69" s="31" t="s">
         <v>190</v>
       </c>
@@ -42683,7 +42683,7 @@
         <v>54.02506257822278</v>
       </c>
     </row>
-    <row r="70" spans="1:42" ht="15">
+    <row r="70" spans="1:42" ht="15" x14ac:dyDescent="0.25">
       <c r="A70" s="31" t="s">
         <v>191</v>
       </c>
@@ -42812,7 +42812,7 @@
         <v>54.046393929912391</v>
       </c>
     </row>
-    <row r="71" spans="1:42">
+    <row r="71" spans="1:42" x14ac:dyDescent="0.15">
       <c r="N71">
         <v>10</v>
       </c>
@@ -42924,7 +42924,7 @@
         <v>54.06758448060075</v>
       </c>
     </row>
-    <row r="72" spans="1:42">
+    <row r="72" spans="1:42" x14ac:dyDescent="0.15">
       <c r="N72">
         <v>11</v>
       </c>
@@ -43036,7 +43036,7 @@
         <v>54.088634230287859</v>
       </c>
     </row>
-    <row r="73" spans="1:42">
+    <row r="73" spans="1:42" x14ac:dyDescent="0.15">
       <c r="N73">
         <v>12</v>
       </c>
@@ -43148,7 +43148,7 @@
         <v>54.109543178973716</v>
       </c>
     </row>
-    <row r="74" spans="1:42">
+    <row r="74" spans="1:42" x14ac:dyDescent="0.15">
       <c r="A74" s="47" t="s">
         <v>99</v>
       </c>
@@ -43265,7 +43265,7 @@
         <v>54.130311326658322</v>
       </c>
     </row>
-    <row r="75" spans="1:42">
+    <row r="75" spans="1:42" x14ac:dyDescent="0.15">
       <c r="A75" s="31" t="s">
         <v>207</v>
       </c>
@@ -43387,7 +43387,7 @@
         <v>54.150938673341678</v>
       </c>
     </row>
-    <row r="76" spans="1:42" ht="15">
+    <row r="76" spans="1:42" ht="15" x14ac:dyDescent="0.25">
       <c r="A76" s="31" t="s">
         <v>157</v>
       </c>
@@ -43512,7 +43512,7 @@
         <v>54.171425219023781</v>
       </c>
     </row>
-    <row r="77" spans="1:42" ht="15">
+    <row r="77" spans="1:42" ht="15" x14ac:dyDescent="0.25">
       <c r="A77" s="34" t="s">
         <v>208</v>
       </c>
@@ -43636,7 +43636,7 @@
         <v>54.191770963704627</v>
       </c>
     </row>
-    <row r="78" spans="1:42">
+    <row r="78" spans="1:42" x14ac:dyDescent="0.15">
       <c r="A78" s="31" t="s">
         <v>101</v>
       </c>
@@ -43765,7 +43765,7 @@
         <v>54.211975907384229</v>
       </c>
     </row>
-    <row r="79" spans="1:42">
+    <row r="79" spans="1:42" x14ac:dyDescent="0.15">
       <c r="A79" s="31" t="s">
         <v>102</v>
       </c>
@@ -43894,7 +43894,7 @@
         <v>54.232040050062579</v>
       </c>
     </row>
-    <row r="80" spans="1:42">
+    <row r="80" spans="1:42" x14ac:dyDescent="0.15">
       <c r="A80" s="31" t="s">
         <v>103</v>
       </c>
@@ -44023,7 +44023,7 @@
         <v>54.251963391739679</v>
       </c>
     </row>
-    <row r="81" spans="1:42">
+    <row r="81" spans="1:42" x14ac:dyDescent="0.15">
       <c r="N81">
         <v>20</v>
       </c>
@@ -44135,7 +44135,7 @@
         <v>54.27174593241552</v>
       </c>
     </row>
-    <row r="82" spans="1:42">
+    <row r="82" spans="1:42" x14ac:dyDescent="0.15">
       <c r="A82" s="44" t="s">
         <v>112</v>
       </c>
@@ -44252,7 +44252,7 @@
         <v>54.29138767209011</v>
       </c>
     </row>
-    <row r="83" spans="1:42">
+    <row r="83" spans="1:42" x14ac:dyDescent="0.15">
       <c r="A83" s="31" t="s">
         <v>210</v>
       </c>
@@ -44374,7 +44374,7 @@
         <v>54.310888610763456</v>
       </c>
     </row>
-    <row r="84" spans="1:42">
+    <row r="84" spans="1:42" x14ac:dyDescent="0.15">
       <c r="A84" s="31" t="s">
         <v>115</v>
       </c>
@@ -44496,7 +44496,7 @@
         <v>54.330248748435544</v>
       </c>
     </row>
-    <row r="85" spans="1:42">
+    <row r="85" spans="1:42" x14ac:dyDescent="0.15">
       <c r="A85" s="31" t="s">
         <v>181</v>
       </c>
@@ -44618,7 +44618,7 @@
         <v>54.34946808510638</v>
       </c>
     </row>
-    <row r="86" spans="1:42">
+    <row r="86" spans="1:42" x14ac:dyDescent="0.15">
       <c r="A86" s="31" t="s">
         <v>183</v>
       </c>
@@ -44740,7 +44740,7 @@
         <v>54.368546620775973</v>
       </c>
     </row>
-    <row r="87" spans="1:42">
+    <row r="87" spans="1:42" x14ac:dyDescent="0.15">
       <c r="N87">
         <v>26</v>
       </c>
@@ -44852,7 +44852,7 @@
         <v>54.387484355444307</v>
       </c>
     </row>
-    <row r="88" spans="1:42">
+    <row r="88" spans="1:42" x14ac:dyDescent="0.15">
       <c r="A88" s="31" t="s">
         <v>160</v>
       </c>
@@ -44969,7 +44969,7 @@
         <v>54.406281289111391</v>
       </c>
     </row>
-    <row r="89" spans="1:42">
+    <row r="89" spans="1:42" x14ac:dyDescent="0.15">
       <c r="A89" s="31" t="s">
         <v>161</v>
       </c>
@@ -45091,7 +45091,7 @@
         <v>54.424937421777223</v>
       </c>
     </row>
-    <row r="90" spans="1:42" ht="15">
+    <row r="90" spans="1:42" ht="15" x14ac:dyDescent="0.25">
       <c r="A90" s="31" t="s">
         <v>162</v>
       </c>
@@ -45213,7 +45213,7 @@
         <v>54.443452753441804</v>
       </c>
     </row>
-    <row r="91" spans="1:42" ht="15">
+    <row r="91" spans="1:42" ht="15" x14ac:dyDescent="0.25">
       <c r="A91" s="31" t="s">
         <v>164</v>
       </c>
@@ -45335,7 +45335,7 @@
         <v>54.461827284105134</v>
       </c>
     </row>
-    <row r="92" spans="1:42" ht="15">
+    <row r="92" spans="1:42" ht="15" x14ac:dyDescent="0.25">
       <c r="A92" s="31" t="s">
         <v>163</v>
       </c>
@@ -45457,7 +45457,7 @@
         <v>54.480061013767212</v>
       </c>
     </row>
-    <row r="93" spans="1:42">
+    <row r="93" spans="1:42" x14ac:dyDescent="0.15">
       <c r="A93" s="31" t="s">
         <v>165</v>
       </c>
@@ -45579,7 +45579,7 @@
         <v>54.498153942428033</v>
       </c>
     </row>
-    <row r="94" spans="1:42" ht="15">
+    <row r="94" spans="1:42" ht="15" x14ac:dyDescent="0.25">
       <c r="A94" s="31" t="s">
         <v>166</v>
       </c>
@@ -45701,7 +45701,7 @@
         <v>54.516106070087609</v>
       </c>
     </row>
-    <row r="95" spans="1:42" ht="15">
+    <row r="95" spans="1:42" ht="15" x14ac:dyDescent="0.25">
       <c r="A95" s="31" t="s">
         <v>167</v>
       </c>
@@ -45823,7 +45823,7 @@
         <v>54.533917396745935</v>
       </c>
     </row>
-    <row r="96" spans="1:42" ht="15">
+    <row r="96" spans="1:42" ht="15" x14ac:dyDescent="0.25">
       <c r="A96" s="31" t="s">
         <v>168</v>
       </c>
@@ -45945,7 +45945,7 @@
         <v>54.551587922403002</v>
       </c>
     </row>
-    <row r="97" spans="1:42">
+    <row r="97" spans="1:42" x14ac:dyDescent="0.15">
       <c r="N97">
         <v>36</v>
       </c>
@@ -46057,7 +46057,7 @@
         <v>54.569117647058825</v>
       </c>
     </row>
-    <row r="98" spans="1:42">
+    <row r="98" spans="1:42" x14ac:dyDescent="0.15">
       <c r="A98" s="32" t="s">
         <v>169</v>
       </c>
@@ -46174,7 +46174,7 @@
         <v>54.586506570713397</v>
       </c>
     </row>
-    <row r="99" spans="1:42">
+    <row r="99" spans="1:42" x14ac:dyDescent="0.15">
       <c r="A99" s="31" t="s">
         <v>170</v>
       </c>
@@ -46297,7 +46297,7 @@
         <v>54.60375469336671</v>
       </c>
     </row>
-    <row r="100" spans="1:42">
+    <row r="100" spans="1:42" x14ac:dyDescent="0.15">
       <c r="A100" s="31" t="s">
         <v>174</v>
       </c>
@@ -46419,7 +46419,7 @@
         <v>54.620862015018773</v>
       </c>
     </row>
-    <row r="101" spans="1:42" ht="15">
+    <row r="101" spans="1:42" ht="15" x14ac:dyDescent="0.25">
       <c r="A101" s="31" t="s">
         <v>175</v>
       </c>
@@ -46541,7 +46541,7 @@
         <v>54.637828535669584</v>
       </c>
     </row>
-    <row r="102" spans="1:42" ht="15">
+    <row r="102" spans="1:42" ht="15" x14ac:dyDescent="0.25">
       <c r="A102" s="31" t="s">
         <v>176</v>
       </c>
@@ -46663,7 +46663,7 @@
         <v>54.654654255319151</v>
       </c>
     </row>
-    <row r="103" spans="1:42" ht="15">
+    <row r="103" spans="1:42" ht="15" x14ac:dyDescent="0.25">
       <c r="A103" s="31" t="s">
         <v>177</v>
       </c>
@@ -46785,7 +46785,7 @@
         <v>54.671339173967461</v>
       </c>
     </row>
-    <row r="104" spans="1:42">
+    <row r="104" spans="1:42" x14ac:dyDescent="0.15">
       <c r="A104" s="31" t="s">
         <v>240</v>
       </c>
@@ -46908,7 +46908,7 @@
         <v>54.687883291614519</v>
       </c>
     </row>
-    <row r="105" spans="1:42">
+    <row r="105" spans="1:42" x14ac:dyDescent="0.15">
       <c r="A105" s="31" t="s">
         <v>242</v>
       </c>
@@ -47030,7 +47030,7 @@
         <v>54.704286608260325</v>
       </c>
     </row>
-    <row r="106" spans="1:42" ht="15">
+    <row r="106" spans="1:42" ht="15" x14ac:dyDescent="0.25">
       <c r="A106" s="31" t="s">
         <v>243</v>
       </c>
@@ -47152,7 +47152,7 @@
         <v>54.720549123904881</v>
       </c>
     </row>
-    <row r="107" spans="1:42" ht="15">
+    <row r="107" spans="1:42" ht="15" x14ac:dyDescent="0.25">
       <c r="A107" s="31" t="s">
         <v>244</v>
       </c>
@@ -47274,7 +47274,7 @@
         <v>54.736670838548186</v>
       </c>
     </row>
-    <row r="108" spans="1:42" ht="15">
+    <row r="108" spans="1:42" ht="15" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>179</v>
       </c>
@@ -47396,7 +47396,7 @@
         <v>54.752651752190239</v>
       </c>
     </row>
-    <row r="109" spans="1:42" ht="15">
+    <row r="109" spans="1:42" ht="15" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>245</v>
       </c>
@@ -47518,7 +47518,7 @@
         <v>54.768491864831041</v>
       </c>
     </row>
-    <row r="110" spans="1:42" ht="15">
+    <row r="110" spans="1:42" ht="15" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>246</v>
       </c>
@@ -47640,7 +47640,7 @@
         <v>54.784191176470586</v>
       </c>
     </row>
-    <row r="111" spans="1:42" ht="15">
+    <row r="111" spans="1:42" ht="15" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
         <v>178</v>
       </c>
@@ -47762,12 +47762,12 @@
         <v>54.799749687108886</v>
       </c>
     </row>
-    <row r="114" spans="1:28" ht="15.75" customHeight="1">
+    <row r="114" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A114" s="40" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="115" spans="1:28">
+    <row r="115" spans="1:28" x14ac:dyDescent="0.15">
       <c r="A115" s="31" t="s">
         <v>211</v>
       </c>
@@ -47786,7 +47786,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="116" spans="1:28" ht="15">
+    <row r="116" spans="1:28" ht="15" x14ac:dyDescent="0.25">
       <c r="A116" s="31" t="s">
         <v>212</v>
       </c>
@@ -47798,7 +47798,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="117" spans="1:28" s="21" customFormat="1" ht="15">
+    <row r="117" spans="1:28" s="21" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A117" s="31" t="s">
         <v>186</v>
       </c>
@@ -47816,7 +47816,7 @@
       <c r="H117"/>
       <c r="AB117"/>
     </row>
-    <row r="118" spans="1:28">
+    <row r="118" spans="1:28" x14ac:dyDescent="0.15">
       <c r="A118" s="31" t="s">
         <v>213</v>
       </c>
@@ -47835,7 +47835,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="119" spans="1:28">
+    <row r="119" spans="1:28" x14ac:dyDescent="0.15">
       <c r="A119" s="31" t="s">
         <v>214</v>
       </c>
@@ -47847,7 +47847,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:28">
+    <row r="120" spans="1:28" x14ac:dyDescent="0.15">
       <c r="A120" s="31" t="s">
         <v>215</v>
       </c>
@@ -47862,7 +47862,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="121" spans="1:28">
+    <row r="121" spans="1:28" x14ac:dyDescent="0.15">
       <c r="A121" s="31" t="s">
         <v>216</v>
       </c>
@@ -47874,7 +47874,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="122" spans="1:28">
+    <row r="122" spans="1:28" x14ac:dyDescent="0.15">
       <c r="A122" s="31" t="s">
         <v>218</v>
       </c>
@@ -47886,7 +47886,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="123" spans="1:28">
+    <row r="123" spans="1:28" x14ac:dyDescent="0.15">
       <c r="A123" s="31" t="s">
         <v>219</v>
       </c>
@@ -47898,12 +47898,12 @@
         <v>72</v>
       </c>
     </row>
-    <row r="126" spans="1:28">
+    <row r="126" spans="1:28" x14ac:dyDescent="0.15">
       <c r="A126" s="34" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="127" spans="1:28">
+    <row r="127" spans="1:28" x14ac:dyDescent="0.15">
       <c r="A127" s="31" t="s">
         <v>227</v>
       </c>
@@ -47916,7 +47916,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="128" spans="1:28">
+    <row r="128" spans="1:28" x14ac:dyDescent="0.15">
       <c r="A128" s="31" t="s">
         <v>229</v>
       </c>
@@ -47935,7 +47935,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="129" spans="1:8" ht="15">
+    <row r="129" spans="1:8" ht="15" x14ac:dyDescent="0.25">
       <c r="A129" s="31" t="s">
         <v>231</v>
       </c>
@@ -47947,7 +47947,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="130" spans="1:8" ht="15">
+    <row r="130" spans="1:8" ht="15" x14ac:dyDescent="0.25">
       <c r="A130" s="31" t="s">
         <v>232</v>
       </c>
@@ -47959,7 +47959,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="131" spans="1:8">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A131" s="31" t="s">
         <v>233</v>
       </c>
@@ -47971,7 +47971,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="132" spans="1:8">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A132" s="31" t="s">
         <v>234</v>
       </c>
@@ -47983,17 +47983,17 @@
         <v>97</v>
       </c>
     </row>
-    <row r="133" spans="1:8">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.15">
       <c r="H133" s="21"/>
     </row>
-    <row r="134" spans="1:8">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A134" s="47" t="s">
         <v>252</v>
       </c>
       <c r="B134" s="47"/>
       <c r="C134" s="47"/>
     </row>
-    <row r="135" spans="1:8">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A135" s="31" t="s">
         <v>250</v>
       </c>
@@ -48005,7 +48005,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="136" spans="1:8">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A136" s="31" t="s">
         <v>254</v>
       </c>
@@ -48017,7 +48017,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="137" spans="1:8">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A137" s="31" t="s">
         <v>253</v>
       </c>
@@ -48029,7 +48029,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="138" spans="1:8">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A138" s="31" t="s">
         <v>256</v>
       </c>
@@ -48041,7 +48041,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="139" spans="1:8">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A139" s="31" t="s">
         <v>257</v>
       </c>
@@ -48053,7 +48053,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="140" spans="1:8">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A140" s="31" t="s">
         <v>258</v>
       </c>
@@ -48065,7 +48065,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="141" spans="1:8">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A141" s="31" t="s">
         <v>265</v>
       </c>
@@ -48077,7 +48077,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="142" spans="1:8">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A142" s="31" t="s">
         <v>266</v>
       </c>
@@ -48089,7 +48089,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="143" spans="1:8" ht="15">
+    <row r="143" spans="1:8" ht="15" x14ac:dyDescent="0.25">
       <c r="A143" s="31" t="s">
         <v>259</v>
       </c>
@@ -48101,7 +48101,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="144" spans="1:8" ht="15">
+    <row r="144" spans="1:8" ht="15" x14ac:dyDescent="0.25">
       <c r="A144" s="31" t="s">
         <v>260</v>
       </c>
@@ -48113,7 +48113,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="145" spans="1:7">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A145" s="31" t="s">
         <v>261</v>
       </c>
@@ -48125,7 +48125,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="146" spans="1:7">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A146" s="31" t="s">
         <v>262</v>
       </c>
@@ -48137,7 +48137,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="147" spans="1:7" ht="15">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A147" s="31" t="s">
         <v>263</v>
       </c>
@@ -48155,7 +48155,7 @@
       <c r="F147" s="21"/>
       <c r="G147" s="21"/>
     </row>
-    <row r="148" spans="1:7">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A148" s="31" t="s">
         <v>264</v>
       </c>
@@ -48167,7 +48167,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="149" spans="1:7">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A149" s="31" t="s">
         <v>268</v>
       </c>
@@ -48179,7 +48179,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="150" spans="1:7">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A150" s="31" t="s">
         <v>269</v>
       </c>
@@ -48191,7 +48191,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="151" spans="1:7">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A151" s="34" t="s">
         <v>278</v>
       </c>
@@ -48199,7 +48199,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="152" spans="1:7">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A152" s="34" t="s">
         <v>279</v>
       </c>
@@ -48207,12 +48207,12 @@
         <v>280</v>
       </c>
     </row>
-    <row r="156" spans="1:7">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A156" s="34" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="157" spans="1:7">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A157" s="31" t="s">
         <v>433</v>
       </c>
@@ -48224,7 +48224,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:7">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A158" s="31" t="s">
         <v>419</v>
       </c>
@@ -48236,7 +48236,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="159" spans="1:7">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A159" s="31" t="s">
         <v>434</v>
       </c>
@@ -48248,7 +48248,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="160" spans="1:7">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A160" s="31" t="s">
         <v>418</v>
       </c>
@@ -48260,7 +48260,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="161" spans="1:5">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A161" s="31" t="s">
         <v>410</v>
       </c>
@@ -48272,7 +48272,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="162" spans="1:5">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A162" s="31" t="s">
         <v>411</v>
       </c>
@@ -48287,7 +48287,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="163" spans="1:5">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A163" s="31" t="s">
         <v>438</v>
       </c>
@@ -48302,7 +48302,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="164" spans="1:5">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A164" s="31" t="s">
         <v>439</v>
       </c>
@@ -48317,7 +48317,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="165" spans="1:5">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A165" s="31" t="s">
         <v>440</v>
       </c>
@@ -48329,14 +48329,14 @@
         <v>87</v>
       </c>
     </row>
-    <row r="166" spans="1:5">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A166" s="32" t="s">
         <v>404</v>
       </c>
       <c r="B166" s="53"/>
       <c r="C166" s="31"/>
     </row>
-    <row r="167" spans="1:5">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A167" s="31" t="s">
         <v>408</v>
       </c>
@@ -48348,7 +48348,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="168" spans="1:5">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A168" s="31" t="s">
         <v>414</v>
       </c>
@@ -48360,7 +48360,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="169" spans="1:5">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A169" s="31" t="s">
         <v>417</v>
       </c>
@@ -48372,7 +48372,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="170" spans="1:5">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A170" s="31" t="s">
         <v>413</v>
       </c>
@@ -48384,7 +48384,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="171" spans="1:5">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A171" s="31" t="s">
         <v>420</v>
       </c>
@@ -48396,7 +48396,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="172" spans="1:5">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A172" s="31" t="s">
         <v>422</v>
       </c>
@@ -48408,7 +48408,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="173" spans="1:5">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A173" s="31" t="s">
         <v>421</v>
       </c>
@@ -48420,7 +48420,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="174" spans="1:5">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A174" s="31" t="s">
         <v>423</v>
       </c>
@@ -48430,7 +48430,7 @@
       </c>
       <c r="C174" s="31"/>
     </row>
-    <row r="175" spans="1:5">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A175" s="31" t="s">
         <v>424</v>
       </c>
@@ -48440,7 +48440,7 @@
       </c>
       <c r="C175" s="31"/>
     </row>
-    <row r="176" spans="1:5">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A176" s="31" t="s">
         <v>435</v>
       </c>
@@ -48452,7 +48452,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="177" spans="1:5">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A177" s="31" t="s">
         <v>436</v>
       </c>
@@ -48464,12 +48464,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="180" spans="1:5">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A180" s="34" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="181" spans="1:5">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A181" s="31" t="s">
         <v>433</v>
       </c>
@@ -48481,7 +48481,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="1:5">
+    <row r="182" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A182" s="31" t="s">
         <v>419</v>
       </c>
@@ -48493,7 +48493,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="183" spans="1:5">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A183" s="31" t="s">
         <v>434</v>
       </c>
@@ -48505,7 +48505,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="184" spans="1:5">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A184" s="31" t="s">
         <v>418</v>
       </c>
@@ -48517,7 +48517,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="185" spans="1:5">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A185" s="31" t="s">
         <v>410</v>
       </c>
@@ -48532,7 +48532,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="186" spans="1:5">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A186" s="31" t="s">
         <v>400</v>
       </c>
@@ -48547,7 +48547,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="187" spans="1:5">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A187" s="31" t="s">
         <v>397</v>
       </c>
@@ -48562,7 +48562,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="188" spans="1:5">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A188" s="31" t="s">
         <v>402</v>
       </c>
@@ -48577,7 +48577,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="189" spans="1:5">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A189" s="31" t="s">
         <v>401</v>
       </c>
@@ -48589,14 +48589,14 @@
         <v>87</v>
       </c>
     </row>
-    <row r="190" spans="1:5">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A190" s="32" t="s">
         <v>404</v>
       </c>
       <c r="B190" s="32"/>
       <c r="C190" s="32"/>
     </row>
-    <row r="191" spans="1:5">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A191" s="31" t="s">
         <v>408</v>
       </c>
@@ -48608,7 +48608,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="192" spans="1:5">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A192" s="31" t="s">
         <v>414</v>
       </c>
@@ -48620,7 +48620,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="193" spans="1:5">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A193" s="31" t="s">
         <v>417</v>
       </c>
@@ -48635,7 +48635,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="194" spans="1:5">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A194" s="31" t="s">
         <v>413</v>
       </c>
@@ -48647,7 +48647,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="195" spans="1:5">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A195" s="31" t="s">
         <v>420</v>
       </c>
@@ -48659,7 +48659,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="196" spans="1:5">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A196" s="31" t="s">
         <v>422</v>
       </c>
@@ -48671,7 +48671,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="197" spans="1:5">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A197" s="31" t="s">
         <v>421</v>
       </c>
@@ -48683,7 +48683,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="198" spans="1:5">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A198" s="31" t="s">
         <v>423</v>
       </c>
@@ -48695,7 +48695,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="199" spans="1:5">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A199" s="31" t="s">
         <v>424</v>
       </c>
@@ -48707,7 +48707,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="200" spans="1:5">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A200" s="31" t="s">
         <v>435</v>
       </c>
@@ -48719,7 +48719,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="201" spans="1:5">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A201" s="31" t="s">
         <v>436</v>
       </c>
@@ -48733,6 +48733,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A63:C63"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A21:C21"/>
     <mergeCell ref="AD58:AO58"/>
     <mergeCell ref="AB4:AE4"/>
     <mergeCell ref="AF4:AI4"/>
@@ -48740,12 +48746,6 @@
     <mergeCell ref="P4:S4"/>
     <mergeCell ref="T4:W4"/>
     <mergeCell ref="X4:AA4"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A63:C63"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="A21:C21"/>
   </mergeCells>
   <phoneticPr fontId="30"/>
   <conditionalFormatting sqref="D70">
@@ -48764,68 +48764,68 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A3:CS228"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="27.5" customWidth="1"/>
-    <col min="2" max="2" width="11.6640625" customWidth="1"/>
+    <col min="2" max="2" width="11.625" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="11.83203125" customWidth="1"/>
+    <col min="4" max="4" width="11.875" customWidth="1"/>
     <col min="7" max="7" width="10.5" customWidth="1"/>
     <col min="8" max="8" width="9.5" customWidth="1"/>
     <col min="10" max="10" width="17.5" customWidth="1"/>
-    <col min="13" max="13" width="16.33203125" customWidth="1"/>
+    <col min="13" max="13" width="16.375" customWidth="1"/>
     <col min="14" max="14" width="16" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.83203125" customWidth="1"/>
+    <col min="15" max="15" width="13.875" customWidth="1"/>
     <col min="18" max="18" width="17.5" customWidth="1"/>
     <col min="21" max="21" width="12" customWidth="1"/>
     <col min="32" max="32" width="13.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:30">
+    <row r="3" spans="2:30" x14ac:dyDescent="0.15">
       <c r="B3" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="4" spans="2:30">
+    <row r="4" spans="2:30" x14ac:dyDescent="0.15">
       <c r="B4" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="5" spans="2:30">
-      <c r="B5" s="213" t="s">
+    <row r="5" spans="2:30" x14ac:dyDescent="0.15">
+      <c r="B5" s="206" t="s">
         <v>33</v>
       </c>
-      <c r="C5" s="213"/>
-      <c r="D5" s="202" t="s">
+      <c r="C5" s="206"/>
+      <c r="D5" s="195" t="s">
         <v>272</v>
       </c>
-      <c r="E5" s="202"/>
-      <c r="F5" s="202"/>
-      <c r="G5" s="202" t="s">
+      <c r="E5" s="195"/>
+      <c r="F5" s="195"/>
+      <c r="G5" s="195" t="s">
         <v>276</v>
       </c>
-      <c r="H5" s="202"/>
-      <c r="I5" s="202"/>
-      <c r="J5" s="202" t="s">
+      <c r="H5" s="195"/>
+      <c r="I5" s="195"/>
+      <c r="J5" s="195" t="s">
         <v>277</v>
       </c>
-      <c r="K5" s="202"/>
-      <c r="L5" s="202"/>
+      <c r="K5" s="195"/>
+      <c r="L5" s="195"/>
     </row>
-    <row r="6" spans="2:30">
-      <c r="B6" s="213"/>
-      <c r="C6" s="213"/>
-      <c r="D6" s="202"/>
-      <c r="E6" s="202"/>
-      <c r="F6" s="202"/>
-      <c r="G6" s="202"/>
-      <c r="H6" s="202"/>
-      <c r="I6" s="202"/>
-      <c r="J6" s="202"/>
-      <c r="K6" s="202"/>
-      <c r="L6" s="202"/>
+    <row r="6" spans="2:30" x14ac:dyDescent="0.15">
+      <c r="B6" s="206"/>
+      <c r="C6" s="206"/>
+      <c r="D6" s="195"/>
+      <c r="E6" s="195"/>
+      <c r="F6" s="195"/>
+      <c r="G6" s="195"/>
+      <c r="H6" s="195"/>
+      <c r="I6" s="195"/>
+      <c r="J6" s="195"/>
+      <c r="K6" s="195"/>
+      <c r="L6" s="195"/>
     </row>
-    <row r="7" spans="2:30" s="2" customFormat="1" ht="30">
+    <row r="7" spans="2:30" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.15">
       <c r="B7" s="71" t="s">
         <v>35</v>
       </c>
@@ -48860,7 +48860,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="8" spans="2:30">
+    <row r="8" spans="2:30" x14ac:dyDescent="0.15">
       <c r="B8" s="1">
         <v>1</v>
       </c>
@@ -48917,7 +48917,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="9" spans="2:30">
+    <row r="9" spans="2:30" x14ac:dyDescent="0.15">
       <c r="B9" s="1">
         <v>2</v>
       </c>
@@ -48981,7 +48981,7 @@
         <v>33.172582805277543</v>
       </c>
     </row>
-    <row r="10" spans="2:30">
+    <row r="10" spans="2:30" x14ac:dyDescent="0.15">
       <c r="B10" s="1">
         <v>3</v>
       </c>
@@ -49045,7 +49045,7 @@
         <v>32.512934072541391</v>
       </c>
     </row>
-    <row r="11" spans="2:30">
+    <row r="11" spans="2:30" x14ac:dyDescent="0.15">
       <c r="B11" s="1">
         <v>4</v>
       </c>
@@ -49109,7 +49109,7 @@
         <v>-10.760391445764517</v>
       </c>
     </row>
-    <row r="12" spans="2:30">
+    <row r="12" spans="2:30" x14ac:dyDescent="0.15">
       <c r="B12" s="1">
         <v>5</v>
       </c>
@@ -49154,7 +49154,7 @@
         <v>89.974022015347515</v>
       </c>
     </row>
-    <row r="13" spans="2:30">
+    <row r="13" spans="2:30" x14ac:dyDescent="0.15">
       <c r="B13" s="1">
         <v>6</v>
       </c>
@@ -49199,7 +49199,7 @@
         <v>89.968826782794125</v>
       </c>
     </row>
-    <row r="14" spans="2:30">
+    <row r="14" spans="2:30" x14ac:dyDescent="0.15">
       <c r="B14" s="1">
         <v>7</v>
       </c>
@@ -49244,7 +49244,7 @@
         <v>89.963631748977392</v>
       </c>
     </row>
-    <row r="15" spans="2:30">
+    <row r="15" spans="2:30" x14ac:dyDescent="0.15">
       <c r="B15" s="1">
         <v>8</v>
       </c>
@@ -49289,7 +49289,7 @@
         <v>89.958436947007982</v>
       </c>
     </row>
-    <row r="16" spans="2:30">
+    <row r="16" spans="2:30" x14ac:dyDescent="0.15">
       <c r="B16" s="1">
         <v>9</v>
       </c>
@@ -49334,7 +49334,7 @@
         <v>89.95324240999102</v>
       </c>
     </row>
-    <row r="17" spans="2:12">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.15">
       <c r="B17" s="1">
         <v>10</v>
       </c>
@@ -49379,7 +49379,7 @@
         <v>89.948048171025221</v>
       </c>
     </row>
-    <row r="18" spans="2:12">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.15">
       <c r="B18" s="1">
         <v>20</v>
       </c>
@@ -49424,7 +49424,7 @@
         <v>89.896129449754241</v>
       </c>
     </row>
-    <row r="19" spans="2:12">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.15">
       <c r="B19" s="1">
         <v>30</v>
       </c>
@@ -49469,7 +49469,7 @@
         <v>89.84427686430584</v>
       </c>
     </row>
-    <row r="20" spans="2:12">
+    <row r="20" spans="2:12" x14ac:dyDescent="0.15">
       <c r="B20" s="1">
         <v>40</v>
       </c>
@@ -49514,7 +49514,7 @@
         <v>89.792523284031105</v>
       </c>
     </row>
-    <row r="21" spans="2:12">
+    <row r="21" spans="2:12" x14ac:dyDescent="0.15">
       <c r="B21" s="1">
         <v>50</v>
       </c>
@@ -49559,7 +49559,7 @@
         <v>89.740901341131149</v>
       </c>
     </row>
-    <row r="22" spans="2:12">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.15">
       <c r="B22" s="1">
         <v>60</v>
       </c>
@@ -49604,7 +49604,7 @@
         <v>89.689443353467766</v>
       </c>
     </row>
-    <row r="23" spans="2:12">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.15">
       <c r="B23" s="1">
         <v>70</v>
       </c>
@@ -49649,7 +49649,7 @@
         <v>89.638181248947447</v>
       </c>
     </row>
-    <row r="24" spans="2:12">
+    <row r="24" spans="2:12" x14ac:dyDescent="0.15">
       <c r="B24" s="1">
         <v>80</v>
       </c>
@@ -49694,7 +49694,7 @@
         <v>89.587146491847719</v>
       </c>
     </row>
-    <row r="25" spans="2:12">
+    <row r="25" spans="2:12" x14ac:dyDescent="0.15">
       <c r="B25" s="1">
         <v>90</v>
       </c>
@@ -49739,7 +49739,7 @@
         <v>89.536370011436603</v>
       </c>
     </row>
-    <row r="26" spans="2:12">
+    <row r="26" spans="2:12" x14ac:dyDescent="0.15">
       <c r="B26" s="1">
         <v>100</v>
       </c>
@@ -49784,7 +49784,7 @@
         <v>89.485882133217316</v>
       </c>
     </row>
-    <row r="27" spans="2:12">
+    <row r="27" spans="2:12" x14ac:dyDescent="0.15">
       <c r="B27" s="1">
         <v>200</v>
       </c>
@@ -49829,7 +49829,7 @@
         <v>89.002995099169837</v>
       </c>
     </row>
-    <row r="28" spans="2:12">
+    <row r="28" spans="2:12" x14ac:dyDescent="0.15">
       <c r="B28" s="1">
         <v>300</v>
       </c>
@@ -49874,7 +49874,7 @@
         <v>88.575790272430652</v>
       </c>
     </row>
-    <row r="29" spans="2:12">
+    <row r="29" spans="2:12" x14ac:dyDescent="0.15">
       <c r="B29" s="1">
         <v>400</v>
       </c>
@@ -49919,7 +49919,7 @@
         <v>88.218035971914659</v>
       </c>
     </row>
-    <row r="30" spans="2:12">
+    <row r="30" spans="2:12" x14ac:dyDescent="0.15">
       <c r="B30" s="1">
         <v>500</v>
       </c>
@@ -49964,7 +49964,7 @@
         <v>87.932746504864227</v>
       </c>
     </row>
-    <row r="31" spans="2:12">
+    <row r="31" spans="2:12" x14ac:dyDescent="0.15">
       <c r="B31" s="1">
         <v>600</v>
       </c>
@@ -50009,7 +50009,7 @@
         <v>87.714839478592395</v>
       </c>
     </row>
-    <row r="32" spans="2:12">
+    <row r="32" spans="2:12" x14ac:dyDescent="0.15">
       <c r="B32" s="1">
         <v>700</v>
       </c>
@@ -50054,7 +50054,7 @@
         <v>87.554662963763519</v>
       </c>
     </row>
-    <row r="33" spans="2:12">
+    <row r="33" spans="2:12" x14ac:dyDescent="0.15">
       <c r="B33" s="1">
         <v>800</v>
       </c>
@@ -50099,7 +50099,7 @@
         <v>87.441013519063787</v>
       </c>
     </row>
-    <row r="34" spans="2:12">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.15">
       <c r="B34" s="1">
         <v>900</v>
       </c>
@@ -50144,7 +50144,7 @@
         <v>87.363112941225396</v>
       </c>
     </row>
-    <row r="35" spans="2:12">
+    <row r="35" spans="2:12" x14ac:dyDescent="0.15">
       <c r="B35" s="1">
         <v>1000</v>
       </c>
@@ -50189,7 +50189,7 @@
         <v>87.311608835870189</v>
       </c>
     </row>
-    <row r="36" spans="2:12">
+    <row r="36" spans="2:12" x14ac:dyDescent="0.15">
       <c r="B36" s="1">
         <v>2000</v>
       </c>
@@ -50234,7 +50234,7 @@
         <v>87.216638365890404</v>
       </c>
     </row>
-    <row r="37" spans="2:12">
+    <row r="37" spans="2:12" x14ac:dyDescent="0.15">
       <c r="B37" s="1">
         <v>3000</v>
       </c>
@@ -50279,7 +50279,7 @@
         <v>87.034650562364931</v>
       </c>
     </row>
-    <row r="38" spans="2:12">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.15">
       <c r="B38" s="1">
         <v>4000</v>
       </c>
@@ -50324,7 +50324,7 @@
         <v>86.695168606144193</v>
       </c>
     </row>
-    <row r="39" spans="2:12">
+    <row r="39" spans="2:12" x14ac:dyDescent="0.15">
       <c r="B39" s="1">
         <v>5000</v>
       </c>
@@ -50369,7 +50369,7 @@
         <v>86.266622886779146</v>
       </c>
     </row>
-    <row r="40" spans="2:12">
+    <row r="40" spans="2:12" x14ac:dyDescent="0.15">
       <c r="B40" s="1">
         <v>6000</v>
       </c>
@@ -50414,7 +50414,7 @@
         <v>85.787290263632102</v>
       </c>
     </row>
-    <row r="41" spans="2:12">
+    <row r="41" spans="2:12" x14ac:dyDescent="0.15">
       <c r="B41" s="1">
         <v>7000</v>
       </c>
@@ -50459,7 +50459,7 @@
         <v>85.277213074284191</v>
       </c>
     </row>
-    <row r="42" spans="2:12">
+    <row r="42" spans="2:12" x14ac:dyDescent="0.15">
       <c r="B42" s="1">
         <v>8000</v>
       </c>
@@ -50504,7 +50504,7 @@
         <v>84.747523880706055</v>
       </c>
     </row>
-    <row r="43" spans="2:12">
+    <row r="43" spans="2:12" x14ac:dyDescent="0.15">
       <c r="B43" s="1">
         <v>9000</v>
       </c>
@@ -50549,7 +50549,7 @@
         <v>84.20483175230595</v>
       </c>
     </row>
-    <row r="44" spans="2:12">
+    <row r="44" spans="2:12" x14ac:dyDescent="0.15">
       <c r="B44" s="1">
         <v>10000</v>
       </c>
@@ -50594,7 +50594,7 @@
         <v>83.653299900189396</v>
       </c>
     </row>
-    <row r="45" spans="2:12">
+    <row r="45" spans="2:12" x14ac:dyDescent="0.15">
       <c r="B45" s="1">
         <v>20000</v>
       </c>
@@ -50639,7 +50639,7 @@
         <v>78.002437476448151</v>
       </c>
     </row>
-    <row r="46" spans="2:12">
+    <row r="46" spans="2:12" x14ac:dyDescent="0.15">
       <c r="B46" s="1">
         <v>30000</v>
       </c>
@@ -50684,7 +50684,7 @@
         <v>72.464165165376599</v>
       </c>
     </row>
-    <row r="47" spans="2:12">
+    <row r="47" spans="2:12" x14ac:dyDescent="0.15">
       <c r="B47" s="1">
         <v>40000</v>
       </c>
@@ -50729,7 +50729,7 @@
         <v>67.216850668642977</v>
       </c>
     </row>
-    <row r="48" spans="2:12">
+    <row r="48" spans="2:12" x14ac:dyDescent="0.15">
       <c r="B48" s="1">
         <v>50000</v>
       </c>
@@ -50774,7 +50774,7 @@
         <v>62.333486106428929</v>
       </c>
     </row>
-    <row r="49" spans="2:12">
+    <row r="49" spans="2:12" x14ac:dyDescent="0.15">
       <c r="B49" s="1">
         <v>60000</v>
       </c>
@@ -50819,7 +50819,7 @@
         <v>57.845342455477052</v>
       </c>
     </row>
-    <row r="50" spans="2:12">
+    <row r="50" spans="2:12" x14ac:dyDescent="0.15">
       <c r="B50" s="1">
         <v>70000</v>
       </c>
@@ -50864,7 +50864,7 @@
         <v>53.756528232756132</v>
       </c>
     </row>
-    <row r="51" spans="2:12">
+    <row r="51" spans="2:12" x14ac:dyDescent="0.15">
       <c r="B51" s="1">
         <v>80000</v>
       </c>
@@ -50909,7 +50909,7 @@
         <v>50.05311305771766</v>
       </c>
     </row>
-    <row r="52" spans="2:12">
+    <row r="52" spans="2:12" x14ac:dyDescent="0.15">
       <c r="B52" s="1">
         <v>90000</v>
       </c>
@@ -50954,7 +50954,7 @@
         <v>46.710276838920862</v>
       </c>
     </row>
-    <row r="53" spans="2:12">
+    <row r="53" spans="2:12" x14ac:dyDescent="0.15">
       <c r="B53" s="1">
         <v>100000</v>
       </c>
@@ -50999,7 +50999,7 @@
         <v>43.697684483572949</v>
       </c>
     </row>
-    <row r="54" spans="2:12">
+    <row r="54" spans="2:12" x14ac:dyDescent="0.15">
       <c r="B54" s="1">
         <v>200000</v>
       </c>
@@ -51044,7 +51044,7 @@
         <v>25.547849807211566</v>
       </c>
     </row>
-    <row r="55" spans="2:12">
+    <row r="55" spans="2:12" x14ac:dyDescent="0.15">
       <c r="B55" s="1">
         <v>300000</v>
       </c>
@@ -51089,7 +51089,7 @@
         <v>17.676857658658555</v>
       </c>
     </row>
-    <row r="56" spans="2:12">
+    <row r="56" spans="2:12" x14ac:dyDescent="0.15">
       <c r="B56" s="1">
         <v>400000</v>
       </c>
@@ -51134,7 +51134,7 @@
         <v>13.443129816404278</v>
       </c>
     </row>
-    <row r="57" spans="2:12">
+    <row r="57" spans="2:12" x14ac:dyDescent="0.15">
       <c r="B57" s="1">
         <v>500000</v>
       </c>
@@ -51179,7 +51179,7 @@
         <v>10.825756501918624</v>
       </c>
     </row>
-    <row r="58" spans="2:12">
+    <row r="58" spans="2:12" x14ac:dyDescent="0.15">
       <c r="B58" s="1">
         <v>600000</v>
       </c>
@@ -51224,7 +51224,7 @@
         <v>9.0543159984642294</v>
       </c>
     </row>
-    <row r="59" spans="2:12">
+    <row r="59" spans="2:12" x14ac:dyDescent="0.15">
       <c r="B59" s="1">
         <v>700000</v>
       </c>
@@ -51269,7 +51269,7 @@
         <v>7.7780003877153518</v>
       </c>
     </row>
-    <row r="60" spans="2:12">
+    <row r="60" spans="2:12" x14ac:dyDescent="0.15">
       <c r="B60" s="1">
         <v>800000</v>
       </c>
@@ -51314,7 +51314,7 @@
         <v>6.8155586465821836</v>
       </c>
     </row>
-    <row r="61" spans="2:12">
+    <row r="61" spans="2:12" x14ac:dyDescent="0.15">
       <c r="B61" s="1">
         <v>900000</v>
       </c>
@@ -51359,7 +51359,7 @@
         <v>6.0642778871037422</v>
       </c>
     </row>
-    <row r="62" spans="2:12">
+    <row r="62" spans="2:12" x14ac:dyDescent="0.15">
       <c r="B62" s="1">
         <v>1000000</v>
       </c>
@@ -51404,12 +51404,12 @@
         <v>5.4617267920158881</v>
       </c>
     </row>
-    <row r="69" spans="2:97">
+    <row r="69" spans="2:97" x14ac:dyDescent="0.15">
       <c r="Q69" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="74" spans="2:97" ht="28">
+    <row r="74" spans="2:97" ht="28.5" x14ac:dyDescent="0.3">
       <c r="B74" s="30" t="s">
         <v>192</v>
       </c>
@@ -51417,79 +51417,79 @@
       <c r="D74" s="29"/>
       <c r="E74" s="29"/>
     </row>
-    <row r="75" spans="2:97" ht="28">
+    <row r="75" spans="2:97" ht="28.5" x14ac:dyDescent="0.3">
       <c r="B75" s="29"/>
       <c r="C75" s="29"/>
       <c r="D75" s="29"/>
       <c r="E75" s="29"/>
     </row>
-    <row r="76" spans="2:97" ht="15" thickBot="1">
-      <c r="B76" s="213" t="s">
+    <row r="76" spans="2:97" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="B76" s="206" t="s">
         <v>33</v>
       </c>
-      <c r="C76" s="213"/>
-      <c r="D76" s="206" t="s">
+      <c r="C76" s="206"/>
+      <c r="D76" s="216" t="s">
         <v>31</v>
       </c>
-      <c r="E76" s="202"/>
-      <c r="F76" s="202"/>
-      <c r="G76" s="202"/>
-      <c r="H76" s="202"/>
-      <c r="I76" s="202"/>
-      <c r="J76" s="202"/>
-      <c r="K76" s="202"/>
-      <c r="L76" s="202"/>
-      <c r="M76" s="202"/>
-      <c r="N76" s="202"/>
-      <c r="O76" s="202"/>
-      <c r="P76" s="202"/>
-      <c r="Q76" s="202"/>
-      <c r="R76" s="202"/>
-      <c r="S76" s="202"/>
-      <c r="T76" s="202"/>
+      <c r="E76" s="195"/>
+      <c r="F76" s="195"/>
+      <c r="G76" s="195"/>
+      <c r="H76" s="195"/>
+      <c r="I76" s="195"/>
+      <c r="J76" s="195"/>
+      <c r="K76" s="195"/>
+      <c r="L76" s="195"/>
+      <c r="M76" s="195"/>
+      <c r="N76" s="195"/>
+      <c r="O76" s="195"/>
+      <c r="P76" s="195"/>
+      <c r="Q76" s="195"/>
+      <c r="R76" s="195"/>
+      <c r="S76" s="195"/>
+      <c r="T76" s="195"/>
     </row>
-    <row r="77" spans="2:97" ht="15" thickBot="1">
-      <c r="B77" s="213"/>
-      <c r="C77" s="213"/>
-      <c r="D77" s="203" t="s">
+    <row r="77" spans="2:97" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="B77" s="206"/>
+      <c r="C77" s="206"/>
+      <c r="D77" s="196" t="s">
         <v>0</v>
       </c>
-      <c r="E77" s="204"/>
-      <c r="F77" s="205"/>
-      <c r="G77" s="203" t="s">
+      <c r="E77" s="197"/>
+      <c r="F77" s="198"/>
+      <c r="G77" s="196" t="s">
         <v>386</v>
       </c>
-      <c r="H77" s="204"/>
-      <c r="I77" s="205"/>
-      <c r="J77" s="203" t="s">
+      <c r="H77" s="197"/>
+      <c r="I77" s="198"/>
+      <c r="J77" s="196" t="s">
         <v>387</v>
       </c>
-      <c r="K77" s="204"/>
-      <c r="L77" s="205"/>
-      <c r="M77" s="203" t="s">
+      <c r="K77" s="197"/>
+      <c r="L77" s="198"/>
+      <c r="M77" s="196" t="s">
         <v>390</v>
       </c>
-      <c r="N77" s="205"/>
+      <c r="N77" s="198"/>
       <c r="O77" s="207" t="s">
         <v>444</v>
       </c>
-      <c r="P77" s="208"/>
-      <c r="Q77" s="209"/>
-      <c r="R77" s="210" t="s">
+      <c r="P77" s="217"/>
+      <c r="Q77" s="208"/>
+      <c r="R77" s="218" t="s">
         <v>445</v>
       </c>
-      <c r="S77" s="211"/>
-      <c r="T77" s="211"/>
-      <c r="U77" s="202" t="s">
+      <c r="S77" s="219"/>
+      <c r="T77" s="219"/>
+      <c r="U77" s="195" t="s">
         <v>393</v>
       </c>
-      <c r="V77" s="202"/>
-      <c r="W77" s="202"/>
+      <c r="V77" s="195"/>
+      <c r="W77" s="195"/>
       <c r="X77" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="78" spans="2:97" ht="45">
+    <row r="78" spans="2:97" ht="40.5" x14ac:dyDescent="0.15">
       <c r="B78" s="71" t="s">
         <v>35</v>
       </c>
@@ -51637,7 +51637,7 @@
       <c r="CR78" s="21"/>
       <c r="CS78" s="21"/>
     </row>
-    <row r="79" spans="2:97">
+    <row r="79" spans="2:97" x14ac:dyDescent="0.15">
       <c r="B79" s="1">
         <v>1</v>
       </c>
@@ -51738,7 +51738,7 @@
         <v>89.926766347412126</v>
       </c>
     </row>
-    <row r="80" spans="2:97">
+    <row r="80" spans="2:97" x14ac:dyDescent="0.15">
       <c r="B80" s="1">
         <v>2</v>
       </c>
@@ -51839,7 +51839,7 @@
         <v>89.853536929145662</v>
       </c>
     </row>
-    <row r="81" spans="2:26">
+    <row r="81" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B81" s="1">
         <v>3</v>
       </c>
@@ -51940,7 +51940,7 @@
         <v>89.780315978765515</v>
       </c>
     </row>
-    <row r="82" spans="2:26">
+    <row r="82" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B82" s="1">
         <v>4</v>
       </c>
@@ -52041,7 +52041,7 @@
         <v>89.707107728323891</v>
       </c>
     </row>
-    <row r="83" spans="2:26">
+    <row r="83" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B83" s="1">
         <v>5</v>
       </c>
@@ -52142,7 +52142,7 @@
         <v>89.63391640760463</v>
       </c>
     </row>
-    <row r="84" spans="2:26">
+    <row r="84" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B84" s="1">
         <v>6</v>
       </c>
@@ -52243,7 +52243,7 @@
         <v>89.560746243368627</v>
       </c>
     </row>
-    <row r="85" spans="2:26">
+    <row r="85" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B85" s="1">
         <v>7</v>
       </c>
@@ -52344,7 +52344,7 @@
         <v>89.487601458600253</v>
       </c>
     </row>
-    <row r="86" spans="2:26">
+    <row r="86" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B86" s="1">
         <v>8</v>
       </c>
@@ -52445,7 +52445,7 @@
         <v>89.414486271755365</v>
       </c>
     </row>
-    <row r="87" spans="2:26">
+    <row r="87" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B87" s="1">
         <v>9</v>
       </c>
@@ -52546,7 +52546,7 @@
         <v>89.341404896011198</v>
       </c>
     </row>
-    <row r="88" spans="2:26">
+    <row r="88" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B88" s="1">
         <v>10</v>
       </c>
@@ -52647,7 +52647,7 @@
         <v>89.268361538518221</v>
       </c>
     </row>
-    <row r="89" spans="2:26">
+    <row r="89" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B89" s="1">
         <v>20</v>
       </c>
@@ -52748,7 +52748,7 @@
         <v>88.540938747651325</v>
       </c>
     </row>
-    <row r="90" spans="2:26">
+    <row r="90" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B90" s="1">
         <v>30</v>
       </c>
@@ -52849,7 +52849,7 @@
         <v>87.821872634395959</v>
       </c>
     </row>
-    <row r="91" spans="2:26">
+    <row r="91" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B91" s="1">
         <v>40</v>
       </c>
@@ -52950,7 +52950,7 @@
         <v>87.115157812645307</v>
       </c>
     </row>
-    <row r="92" spans="2:26">
+    <row r="92" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B92" s="1">
         <v>50</v>
       </c>
@@ -53051,7 +53051,7 @@
         <v>86.424576435033643</v>
       </c>
     </row>
-    <row r="93" spans="2:26">
+    <row r="93" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B93" s="1">
         <v>60</v>
       </c>
@@ -53152,7 +53152,7 @@
         <v>85.75364012240054</v>
       </c>
     </row>
-    <row r="94" spans="2:26">
+    <row r="94" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B94" s="1">
         <v>70</v>
       </c>
@@ -53253,7 +53253,7 @@
         <v>85.105541694525783</v>
       </c>
     </row>
-    <row r="95" spans="2:26">
+    <row r="95" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B95" s="1">
         <v>80</v>
       </c>
@@ -53354,7 +53354,7 @@
         <v>84.483117886413268</v>
       </c>
     </row>
-    <row r="96" spans="2:26">
+    <row r="96" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B96" s="1">
         <v>90</v>
       </c>
@@ -53455,7 +53455,7 @@
         <v>83.888823587969043</v>
       </c>
     </row>
-    <row r="97" spans="2:26">
+    <row r="97" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B97" s="1">
         <v>100</v>
       </c>
@@ -53556,7 +53556,7 @@
         <v>83.324717527794718</v>
       </c>
     </row>
-    <row r="98" spans="2:26">
+    <row r="98" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B98" s="1">
         <v>200</v>
       </c>
@@ -53657,7 +53657,7 @@
         <v>79.531025615109073</v>
       </c>
     </row>
-    <row r="99" spans="2:26">
+    <row r="99" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B99" s="1">
         <v>300</v>
       </c>
@@ -53758,7 +53758,7 @@
         <v>78.721686059687926</v>
       </c>
     </row>
-    <row r="100" spans="2:26">
+    <row r="100" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B100" s="1">
         <v>400</v>
       </c>
@@ -53859,7 +53859,7 @@
         <v>79.675700498215647</v>
       </c>
     </row>
-    <row r="101" spans="2:26">
+    <row r="101" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B101" s="1">
         <v>500</v>
       </c>
@@ -53960,7 +53960,7 @@
         <v>81.371584674705829</v>
       </c>
     </row>
-    <row r="102" spans="2:26">
+    <row r="102" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B102" s="1">
         <v>600</v>
       </c>
@@ -54061,7 +54061,7 @@
         <v>83.241090352192913</v>
       </c>
     </row>
-    <row r="103" spans="2:26">
+    <row r="103" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B103" s="1">
         <v>700</v>
       </c>
@@ -54162,7 +54162,7 @@
         <v>85.020222172060556</v>
       </c>
     </row>
-    <row r="104" spans="2:26">
+    <row r="104" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B104" s="1">
         <v>800</v>
       </c>
@@ -54263,7 +54263,7 @@
         <v>86.605319810983687</v>
       </c>
     </row>
-    <row r="105" spans="2:26">
+    <row r="105" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B105" s="1">
         <v>900</v>
       </c>
@@ -54364,7 +54364,7 @@
         <v>87.969232991183503</v>
       </c>
     </row>
-    <row r="106" spans="2:26">
+    <row r="106" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B106" s="1">
         <v>1000</v>
       </c>
@@ -54465,7 +54465,7 @@
         <v>89.118671769523814</v>
       </c>
     </row>
-    <row r="107" spans="2:26">
+    <row r="107" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B107" s="1">
         <v>2000</v>
       </c>
@@ -54566,7 +54566,7 @@
         <v>93.284000467819908</v>
       </c>
     </row>
-    <row r="108" spans="2:26">
+    <row r="108" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B108" s="1">
         <v>3000</v>
       </c>
@@ -54667,7 +54667,7 @@
         <v>92.352723371958092</v>
       </c>
     </row>
-    <row r="109" spans="2:26">
+    <row r="109" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B109" s="1">
         <v>4000</v>
       </c>
@@ -54768,7 +54768,7 @@
         <v>90.403892885434345</v>
       </c>
     </row>
-    <row r="110" spans="2:26">
+    <row r="110" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B110" s="1">
         <v>5000</v>
       </c>
@@ -54869,7 +54869,7 @@
         <v>88.331017884181037</v>
       </c>
     </row>
-    <row r="111" spans="2:26">
+    <row r="111" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B111" s="1">
         <v>6000</v>
       </c>
@@ -54970,7 +54970,7 @@
         <v>86.327885696740324</v>
       </c>
     </row>
-    <row r="112" spans="2:26">
+    <row r="112" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B112" s="1">
         <v>7000</v>
       </c>
@@ -55071,7 +55071,7 @@
         <v>84.422115808897814</v>
       </c>
     </row>
-    <row r="113" spans="2:26">
+    <row r="113" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B113" s="1">
         <v>8000</v>
       </c>
@@ -55172,7 +55172,7 @@
         <v>82.603047195048831</v>
       </c>
     </row>
-    <row r="114" spans="2:26">
+    <row r="114" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B114" s="1">
         <v>9000</v>
       </c>
@@ -55273,7 +55273,7 @@
         <v>80.853843507599549</v>
       </c>
     </row>
-    <row r="115" spans="2:26">
+    <row r="115" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B115" s="1">
         <v>10000</v>
       </c>
@@ -55374,7 +55374,7 @@
         <v>79.159269055191814</v>
       </c>
     </row>
-    <row r="116" spans="2:26">
+    <row r="116" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B116" s="1">
         <v>20000</v>
       </c>
@@ -55475,7 +55475,7 @@
         <v>63.496440886789635</v>
       </c>
     </row>
-    <row r="117" spans="2:26">
+    <row r="117" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B117" s="1">
         <v>30000</v>
       </c>
@@ -55576,7 +55576,7 @@
         <v>48.330172240535568</v>
       </c>
     </row>
-    <row r="118" spans="2:26">
+    <row r="118" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B118" s="1">
         <v>40000</v>
       </c>
@@ -55677,7 +55677,7 @@
         <v>33.275849306823332</v>
       </c>
     </row>
-    <row r="119" spans="2:26">
+    <row r="119" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B119" s="1">
         <v>50000</v>
       </c>
@@ -55778,7 +55778,7 @@
         <v>18.841538248489307</v>
       </c>
     </row>
-    <row r="120" spans="2:26">
+    <row r="120" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B120" s="1">
         <v>60000</v>
       </c>
@@ -55879,7 +55879,7 @@
         <v>5.6918330486549413</v>
       </c>
     </row>
-    <row r="121" spans="2:26">
+    <row r="121" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B121" s="1">
         <v>70000</v>
       </c>
@@ -55980,7 +55980,7 @@
         <v>-5.7492456084780432</v>
       </c>
     </row>
-    <row r="122" spans="2:26">
+    <row r="122" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B122" s="1">
         <v>80000</v>
       </c>
@@ -56081,7 +56081,7 @@
         <v>-15.405464841748149</v>
       </c>
     </row>
-    <row r="123" spans="2:26">
+    <row r="123" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B123" s="1">
         <v>90000</v>
       </c>
@@ -56182,7 +56182,7 @@
         <v>-23.438827440646254</v>
       </c>
     </row>
-    <row r="124" spans="2:26">
+    <row r="124" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B124" s="1">
         <v>100000</v>
       </c>
@@ -56283,7 +56283,7 @@
         <v>-30.10443168897956</v>
       </c>
     </row>
-    <row r="125" spans="2:26">
+    <row r="125" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B125" s="1">
         <v>200000</v>
       </c>
@@ -56384,7 +56384,7 @@
         <v>-60.745072872271734</v>
       </c>
     </row>
-    <row r="126" spans="2:26">
+    <row r="126" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B126" s="1">
         <v>300000</v>
       </c>
@@ -56485,7 +56485,7 @@
         <v>-70.673691274893059</v>
       </c>
     </row>
-    <row r="127" spans="2:26">
+    <row r="127" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B127" s="1">
         <v>400000</v>
       </c>
@@ -56586,7 +56586,7 @@
         <v>-75.557252300108473</v>
       </c>
     </row>
-    <row r="128" spans="2:26">
+    <row r="128" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B128" s="1">
         <v>500000</v>
       </c>
@@ -56687,7 +56687,7 @@
         <v>-78.465830429899214</v>
       </c>
     </row>
-    <row r="129" spans="1:26">
+    <row r="129" spans="1:26" x14ac:dyDescent="0.15">
       <c r="B129" s="1">
         <v>600000</v>
       </c>
@@ -56788,7 +56788,7 @@
         <v>-80.397430818615803</v>
       </c>
     </row>
-    <row r="130" spans="1:26">
+    <row r="130" spans="1:26" x14ac:dyDescent="0.15">
       <c r="B130" s="1">
         <v>700000</v>
       </c>
@@ -56889,7 +56889,7 @@
         <v>-81.774051547831618</v>
       </c>
     </row>
-    <row r="131" spans="1:26">
+    <row r="131" spans="1:26" x14ac:dyDescent="0.15">
       <c r="B131" s="1">
         <v>800000</v>
       </c>
@@ -56990,7 +56990,7 @@
         <v>-82.805053033174602</v>
       </c>
     </row>
-    <row r="132" spans="1:26">
+    <row r="132" spans="1:26" x14ac:dyDescent="0.15">
       <c r="B132" s="1">
         <v>900000</v>
       </c>
@@ -57091,7 +57091,7 @@
         <v>-83.60617947248295</v>
       </c>
     </row>
-    <row r="133" spans="1:26" ht="15" thickBot="1">
+    <row r="133" spans="1:26" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B133" s="98">
         <v>1000000</v>
       </c>
@@ -57192,7 +57192,7 @@
         <v>-84.246651339457912</v>
       </c>
     </row>
-    <row r="134" spans="1:26">
+    <row r="134" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A134" s="82" t="s">
         <v>443</v>
       </c>
@@ -57297,7 +57297,7 @@
         <v>90.403892885434345</v>
       </c>
     </row>
-    <row r="135" spans="1:26">
+    <row r="135" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A135" t="s">
         <v>446</v>
       </c>
@@ -57402,7 +57402,7 @@
         <v>81.322883285048576</v>
       </c>
     </row>
-    <row r="136" spans="1:26" ht="15" thickBot="1">
+    <row r="136" spans="1:26" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>447</v>
       </c>
@@ -57507,7 +57507,7 @@
         <v>93.279780147589946</v>
       </c>
     </row>
-    <row r="137" spans="1:26" ht="15" thickBot="1">
+    <row r="137" spans="1:26" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>448</v>
       </c>
@@ -57612,39 +57612,39 @@
         <v>81.091143053752447</v>
       </c>
     </row>
-    <row r="165" spans="2:93" ht="29" thickBot="1">
+    <row r="165" spans="2:93" ht="29.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B165" s="30" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="166" spans="2:93">
+    <row r="166" spans="2:93" x14ac:dyDescent="0.15">
       <c r="B166" s="207" t="s">
         <v>33</v>
       </c>
-      <c r="C166" s="209"/>
-      <c r="D166" s="219" t="s">
+      <c r="C166" s="208"/>
+      <c r="D166" s="214" t="s">
         <v>31</v>
       </c>
-      <c r="E166" s="212"/>
-      <c r="F166" s="212"/>
-      <c r="G166" s="212" t="s">
+      <c r="E166" s="215"/>
+      <c r="F166" s="215"/>
+      <c r="G166" s="215" t="s">
         <v>386</v>
       </c>
-      <c r="H166" s="212"/>
-      <c r="I166" s="212"/>
-      <c r="J166" s="212" t="s">
+      <c r="H166" s="215"/>
+      <c r="I166" s="215"/>
+      <c r="J166" s="215" t="s">
         <v>387</v>
       </c>
-      <c r="K166" s="212"/>
-      <c r="L166" s="212"/>
-      <c r="M166" s="212"/>
-      <c r="N166" s="212"/>
-      <c r="O166" s="212"/>
-      <c r="P166" s="212"/>
-      <c r="Q166" s="212"/>
-      <c r="R166" s="212"/>
-      <c r="S166" s="212"/>
-      <c r="T166" s="212"/>
+      <c r="K166" s="215"/>
+      <c r="L166" s="215"/>
+      <c r="M166" s="215"/>
+      <c r="N166" s="215"/>
+      <c r="O166" s="215"/>
+      <c r="P166" s="215"/>
+      <c r="Q166" s="215"/>
+      <c r="R166" s="215"/>
+      <c r="S166" s="215"/>
+      <c r="T166" s="215"/>
       <c r="U166" s="81"/>
       <c r="V166" s="81"/>
       <c r="W166" s="81"/>
@@ -57652,135 +57652,135 @@
       <c r="Y166" s="81"/>
       <c r="Z166" s="81"/>
       <c r="AA166" s="81"/>
-      <c r="AB166" s="213"/>
-      <c r="AC166" s="213"/>
-      <c r="AD166" s="213"/>
-      <c r="BC166" s="202"/>
-      <c r="BD166" s="202"/>
-      <c r="BE166" s="202"/>
-      <c r="BF166" s="202"/>
-      <c r="BG166" s="202"/>
-      <c r="BH166" s="202"/>
-      <c r="BI166" s="202"/>
-      <c r="BJ166" s="202"/>
-      <c r="BK166" s="202"/>
-      <c r="BL166" s="202"/>
-      <c r="BM166" s="202"/>
-      <c r="BN166" s="202"/>
-      <c r="BO166" s="202"/>
-      <c r="BP166" s="202"/>
-      <c r="BQ166" s="202"/>
-      <c r="BR166" s="202"/>
-      <c r="BS166" s="202"/>
-      <c r="BT166" s="202"/>
-      <c r="BU166" s="202"/>
-      <c r="BV166" s="202"/>
-      <c r="BW166" s="202"/>
-      <c r="BX166" s="202"/>
-      <c r="BY166" s="202"/>
-      <c r="BZ166" s="202"/>
-      <c r="CA166" s="202"/>
-      <c r="CB166" s="202"/>
-      <c r="CC166" s="202"/>
-      <c r="CD166" s="202"/>
-      <c r="CE166" s="202"/>
-      <c r="CF166" s="202"/>
-      <c r="CG166" s="202"/>
-      <c r="CH166" s="202"/>
-      <c r="CI166" s="202"/>
-      <c r="CJ166" s="202"/>
-      <c r="CK166" s="202"/>
-      <c r="CL166" s="202"/>
-      <c r="CM166" s="202"/>
-      <c r="CN166" s="202"/>
-      <c r="CO166" s="202"/>
+      <c r="AB166" s="206"/>
+      <c r="AC166" s="206"/>
+      <c r="AD166" s="206"/>
+      <c r="BC166" s="195"/>
+      <c r="BD166" s="195"/>
+      <c r="BE166" s="195"/>
+      <c r="BF166" s="195"/>
+      <c r="BG166" s="195"/>
+      <c r="BH166" s="195"/>
+      <c r="BI166" s="195"/>
+      <c r="BJ166" s="195"/>
+      <c r="BK166" s="195"/>
+      <c r="BL166" s="195"/>
+      <c r="BM166" s="195"/>
+      <c r="BN166" s="195"/>
+      <c r="BO166" s="195"/>
+      <c r="BP166" s="195"/>
+      <c r="BQ166" s="195"/>
+      <c r="BR166" s="195"/>
+      <c r="BS166" s="195"/>
+      <c r="BT166" s="195"/>
+      <c r="BU166" s="195"/>
+      <c r="BV166" s="195"/>
+      <c r="BW166" s="195"/>
+      <c r="BX166" s="195"/>
+      <c r="BY166" s="195"/>
+      <c r="BZ166" s="195"/>
+      <c r="CA166" s="195"/>
+      <c r="CB166" s="195"/>
+      <c r="CC166" s="195"/>
+      <c r="CD166" s="195"/>
+      <c r="CE166" s="195"/>
+      <c r="CF166" s="195"/>
+      <c r="CG166" s="195"/>
+      <c r="CH166" s="195"/>
+      <c r="CI166" s="195"/>
+      <c r="CJ166" s="195"/>
+      <c r="CK166" s="195"/>
+      <c r="CL166" s="195"/>
+      <c r="CM166" s="195"/>
+      <c r="CN166" s="195"/>
+      <c r="CO166" s="195"/>
     </row>
-    <row r="167" spans="2:93" ht="15" thickBot="1">
-      <c r="B167" s="214"/>
-      <c r="C167" s="215"/>
-      <c r="D167" s="216" t="s">
+    <row r="167" spans="2:93" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="B167" s="209"/>
+      <c r="C167" s="210"/>
+      <c r="D167" s="211" t="s">
         <v>385</v>
       </c>
-      <c r="E167" s="217"/>
-      <c r="F167" s="218"/>
-      <c r="G167" s="216" t="s">
+      <c r="E167" s="212"/>
+      <c r="F167" s="213"/>
+      <c r="G167" s="211" t="s">
         <v>385</v>
       </c>
-      <c r="H167" s="217"/>
-      <c r="I167" s="218"/>
-      <c r="J167" s="216" t="s">
+      <c r="H167" s="212"/>
+      <c r="I167" s="213"/>
+      <c r="J167" s="211" t="s">
         <v>385</v>
       </c>
-      <c r="K167" s="217"/>
-      <c r="L167" s="218"/>
-      <c r="M167" s="206" t="s">
+      <c r="K167" s="212"/>
+      <c r="L167" s="213"/>
+      <c r="M167" s="216" t="s">
         <v>390</v>
       </c>
-      <c r="N167" s="202"/>
-      <c r="O167" s="202" t="s">
+      <c r="N167" s="195"/>
+      <c r="O167" s="195" t="s">
         <v>394</v>
       </c>
-      <c r="P167" s="202"/>
-      <c r="Q167" s="202"/>
-      <c r="R167" s="202" t="s">
+      <c r="P167" s="195"/>
+      <c r="Q167" s="195"/>
+      <c r="R167" s="195" t="s">
         <v>391</v>
       </c>
-      <c r="S167" s="202"/>
-      <c r="T167" s="202"/>
-      <c r="U167" s="202" t="s">
+      <c r="S167" s="195"/>
+      <c r="T167" s="195"/>
+      <c r="U167" s="195" t="s">
         <v>393</v>
       </c>
-      <c r="V167" s="202"/>
-      <c r="W167" s="202"/>
-      <c r="X167" s="202" t="s">
+      <c r="V167" s="195"/>
+      <c r="W167" s="195"/>
+      <c r="X167" s="195" t="s">
         <v>395</v>
       </c>
-      <c r="Y167" s="202"/>
-      <c r="Z167" s="202"/>
-      <c r="AB167" s="213"/>
-      <c r="AC167" s="213"/>
-      <c r="AD167" s="213"/>
-      <c r="BC167" s="202"/>
-      <c r="BD167" s="202"/>
-      <c r="BE167" s="202"/>
-      <c r="BF167" s="202"/>
-      <c r="BG167" s="202"/>
-      <c r="BH167" s="202"/>
-      <c r="BI167" s="202"/>
-      <c r="BJ167" s="202"/>
-      <c r="BK167" s="202"/>
-      <c r="BL167" s="202"/>
-      <c r="BM167" s="202"/>
-      <c r="BN167" s="202"/>
-      <c r="BO167" s="202"/>
-      <c r="BP167" s="202"/>
-      <c r="BQ167" s="202"/>
-      <c r="BR167" s="202"/>
-      <c r="BS167" s="202"/>
-      <c r="BT167" s="202"/>
-      <c r="BU167" s="202"/>
-      <c r="BV167" s="202"/>
-      <c r="BW167" s="202"/>
-      <c r="BX167" s="202"/>
-      <c r="BY167" s="202"/>
-      <c r="BZ167" s="202"/>
-      <c r="CA167" s="202"/>
-      <c r="CB167" s="202"/>
-      <c r="CC167" s="202"/>
-      <c r="CD167" s="202"/>
-      <c r="CE167" s="202"/>
-      <c r="CF167" s="202"/>
-      <c r="CG167" s="202"/>
-      <c r="CH167" s="202"/>
-      <c r="CI167" s="202"/>
-      <c r="CJ167" s="202"/>
-      <c r="CK167" s="202"/>
-      <c r="CL167" s="202"/>
-      <c r="CM167" s="202"/>
-      <c r="CN167" s="202"/>
-      <c r="CO167" s="202"/>
+      <c r="Y167" s="195"/>
+      <c r="Z167" s="195"/>
+      <c r="AB167" s="206"/>
+      <c r="AC167" s="206"/>
+      <c r="AD167" s="206"/>
+      <c r="BC167" s="195"/>
+      <c r="BD167" s="195"/>
+      <c r="BE167" s="195"/>
+      <c r="BF167" s="195"/>
+      <c r="BG167" s="195"/>
+      <c r="BH167" s="195"/>
+      <c r="BI167" s="195"/>
+      <c r="BJ167" s="195"/>
+      <c r="BK167" s="195"/>
+      <c r="BL167" s="195"/>
+      <c r="BM167" s="195"/>
+      <c r="BN167" s="195"/>
+      <c r="BO167" s="195"/>
+      <c r="BP167" s="195"/>
+      <c r="BQ167" s="195"/>
+      <c r="BR167" s="195"/>
+      <c r="BS167" s="195"/>
+      <c r="BT167" s="195"/>
+      <c r="BU167" s="195"/>
+      <c r="BV167" s="195"/>
+      <c r="BW167" s="195"/>
+      <c r="BX167" s="195"/>
+      <c r="BY167" s="195"/>
+      <c r="BZ167" s="195"/>
+      <c r="CA167" s="195"/>
+      <c r="CB167" s="195"/>
+      <c r="CC167" s="195"/>
+      <c r="CD167" s="195"/>
+      <c r="CE167" s="195"/>
+      <c r="CF167" s="195"/>
+      <c r="CG167" s="195"/>
+      <c r="CH167" s="195"/>
+      <c r="CI167" s="195"/>
+      <c r="CJ167" s="195"/>
+      <c r="CK167" s="195"/>
+      <c r="CL167" s="195"/>
+      <c r="CM167" s="195"/>
+      <c r="CN167" s="195"/>
+      <c r="CO167" s="195"/>
     </row>
-    <row r="168" spans="2:93" ht="45">
+    <row r="168" spans="2:93" ht="40.5" x14ac:dyDescent="0.15">
       <c r="B168" s="23" t="s">
         <v>35</v>
       </c>
@@ -57924,7 +57924,7 @@
       <c r="CN168" s="21"/>
       <c r="CO168" s="21"/>
     </row>
-    <row r="169" spans="2:93">
+    <row r="169" spans="2:93" x14ac:dyDescent="0.15">
       <c r="B169" s="1">
         <v>1</v>
       </c>
@@ -58025,7 +58025,7 @@
         <v>89.969977545251339</v>
       </c>
     </row>
-    <row r="170" spans="2:93">
+    <row r="170" spans="2:93" x14ac:dyDescent="0.15">
       <c r="B170" s="1">
         <v>2</v>
       </c>
@@ -58126,7 +58126,7 @@
         <v>89.939962582119293</v>
       </c>
     </row>
-    <row r="171" spans="2:93">
+    <row r="171" spans="2:93" x14ac:dyDescent="0.15">
       <c r="B171" s="1">
         <v>3</v>
       </c>
@@ -58227,7 +58227,7 @@
         <v>89.909962596432095</v>
       </c>
     </row>
-    <row r="172" spans="2:93">
+    <row r="172" spans="2:93" x14ac:dyDescent="0.15">
       <c r="B172" s="1">
         <v>4</v>
       </c>
@@ -58328,7 +58328,7 @@
         <v>89.879985062450814</v>
       </c>
     </row>
-    <row r="173" spans="2:93">
+    <row r="173" spans="2:93" x14ac:dyDescent="0.15">
       <c r="B173" s="1">
         <v>5</v>
       </c>
@@ -58429,7 +58429,7 @@
         <v>89.850037437109137</v>
       </c>
     </row>
-    <row r="174" spans="2:93">
+    <row r="174" spans="2:93" x14ac:dyDescent="0.15">
       <c r="B174" s="1">
         <v>6</v>
       </c>
@@ -58530,7 +58530,7 @@
         <v>89.820127154280868</v>
       </c>
     </row>
-    <row r="175" spans="2:93">
+    <row r="175" spans="2:93" x14ac:dyDescent="0.15">
       <c r="B175" s="1">
         <v>7</v>
       </c>
@@ -58631,7 +58631,7 @@
         <v>89.790261619085399</v>
       </c>
     </row>
-    <row r="176" spans="2:93">
+    <row r="176" spans="2:93" x14ac:dyDescent="0.15">
       <c r="B176" s="1">
         <v>8</v>
       </c>
@@ -58732,7 +58732,7 @@
         <v>89.760448202238891</v>
       </c>
     </row>
-    <row r="177" spans="2:26">
+    <row r="177" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B177" s="1">
         <v>9</v>
       </c>
@@ -58833,7 +58833,7 @@
         <v>89.730694234461225</v>
       </c>
     </row>
-    <row r="178" spans="2:26">
+    <row r="178" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B178" s="1">
         <v>10</v>
       </c>
@@ -58934,7 +58934,7 @@
         <v>89.701007000946262</v>
       </c>
     </row>
-    <row r="179" spans="2:26">
+    <row r="179" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B179" s="1">
         <v>20</v>
       </c>
@@ -59035,7 +59035,7 @@
         <v>89.40936459037205</v>
       </c>
     </row>
-    <row r="180" spans="2:26">
+    <row r="180" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B180" s="1">
         <v>30</v>
       </c>
@@ -59136,7 +59136,7 @@
         <v>89.131874272167366</v>
       </c>
     </row>
-    <row r="181" spans="2:26">
+    <row r="181" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B181" s="1">
         <v>40</v>
       </c>
@@ -59237,7 +59237,7 @@
         <v>88.874323165184506</v>
       </c>
     </row>
-    <row r="182" spans="2:26">
+    <row r="182" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B182" s="1">
         <v>50</v>
       </c>
@@ -59338,7 +59338,7 @@
         <v>88.641165001978734</v>
       </c>
     </row>
-    <row r="183" spans="2:26">
+    <row r="183" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B183" s="1">
         <v>60</v>
       </c>
@@ -59439,7 +59439,7 @@
         <v>88.435375361366056</v>
       </c>
     </row>
-    <row r="184" spans="2:26">
+    <row r="184" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B184" s="1">
         <v>70</v>
       </c>
@@ -59540,7 +59540,7 @@
         <v>88.258473041769761</v>
       </c>
     </row>
-    <row r="185" spans="2:26">
+    <row r="185" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B185" s="1">
         <v>80</v>
       </c>
@@ -59641,7 +59641,7 @@
         <v>88.110672326653926</v>
       </c>
     </row>
-    <row r="186" spans="2:26">
+    <row r="186" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B186" s="1">
         <v>90</v>
       </c>
@@ -59742,7 +59742,7 @@
         <v>87.991117698140641</v>
       </c>
     </row>
-    <row r="187" spans="2:26">
+    <row r="187" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B187" s="1">
         <v>100</v>
       </c>
@@ -59843,7 +59843,7 @@
         <v>87.898152715169473</v>
       </c>
     </row>
-    <row r="188" spans="2:26">
+    <row r="188" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B188" s="1">
         <v>200</v>
       </c>
@@ -59944,7 +59944,7 @@
         <v>87.908198506323842</v>
       </c>
     </row>
-    <row r="189" spans="2:26">
+    <row r="189" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B189" s="1">
         <v>300</v>
       </c>
@@ -60045,7 +60045,7 @@
         <v>88.453642124189798</v>
       </c>
     </row>
-    <row r="190" spans="2:26">
+    <row r="190" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B190" s="1">
         <v>400</v>
       </c>
@@ -60146,7 +60146,7 @@
         <v>88.916756092678028</v>
       </c>
     </row>
-    <row r="191" spans="2:26">
+    <row r="191" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B191" s="1">
         <v>500</v>
       </c>
@@ -60247,7 +60247,7 @@
         <v>89.215067905496866</v>
       </c>
     </row>
-    <row r="192" spans="2:26">
+    <row r="192" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B192" s="1">
         <v>600</v>
       </c>
@@ -60348,7 +60348,7 @@
         <v>89.363593379078395</v>
       </c>
     </row>
-    <row r="193" spans="2:26">
+    <row r="193" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B193" s="1">
         <v>700</v>
       </c>
@@ -60449,7 +60449,7 @@
         <v>89.389734337735248</v>
       </c>
     </row>
-    <row r="194" spans="2:26">
+    <row r="194" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B194" s="1">
         <v>800</v>
       </c>
@@ -60550,7 +60550,7 @@
         <v>89.319151395601438</v>
       </c>
     </row>
-    <row r="195" spans="2:26">
+    <row r="195" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B195" s="1">
         <v>900</v>
       </c>
@@ -60651,7 +60651,7 @@
         <v>89.173581088111334</v>
       </c>
     </row>
-    <row r="196" spans="2:26">
+    <row r="196" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B196" s="1">
         <v>1000</v>
       </c>
@@ -60752,7 +60752,7 @@
         <v>88.970768457855456</v>
       </c>
     </row>
-    <row r="197" spans="2:26">
+    <row r="197" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B197" s="1">
         <v>2000</v>
       </c>
@@ -60853,7 +60853,7 @@
         <v>85.764814425830934</v>
       </c>
     </row>
-    <row r="198" spans="2:26">
+    <row r="198" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B198" s="1">
         <v>3000</v>
       </c>
@@ -60954,7 +60954,7 @@
         <v>82.305598358942021</v>
       </c>
     </row>
-    <row r="199" spans="2:26">
+    <row r="199" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B199" s="1">
         <v>4000</v>
       </c>
@@ -61055,7 +61055,7 @@
         <v>78.991676351548875</v>
       </c>
     </row>
-    <row r="200" spans="2:26">
+    <row r="200" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B200" s="1">
         <v>5000</v>
       </c>
@@ -61156,7 +61156,7 @@
         <v>75.790816983428243</v>
       </c>
     </row>
-    <row r="201" spans="2:26">
+    <row r="201" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B201" s="1">
         <v>6000</v>
       </c>
@@ -61257,7 +61257,7 @@
         <v>72.670319353423807</v>
       </c>
     </row>
-    <row r="202" spans="2:26">
+    <row r="202" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B202" s="1">
         <v>7000</v>
       </c>
@@ -61358,7 +61358,7 @@
         <v>69.612140245480262</v>
       </c>
     </row>
-    <row r="203" spans="2:26">
+    <row r="203" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B203" s="1">
         <v>8000</v>
       </c>
@@ -61459,7 +61459,7 @@
         <v>66.606891153188968</v>
       </c>
     </row>
-    <row r="204" spans="2:26">
+    <row r="204" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B204" s="1">
         <v>9000</v>
       </c>
@@ -61560,7 +61560,7 @@
         <v>63.649746439495509</v>
       </c>
     </row>
-    <row r="205" spans="2:26">
+    <row r="205" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B205" s="1">
         <v>10000</v>
       </c>
@@ -61661,7 +61661,7 @@
         <v>60.73826418833373</v>
       </c>
     </row>
-    <row r="206" spans="2:26">
+    <row r="206" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B206" s="1">
         <v>20000</v>
       </c>
@@ -61762,7 +61762,7 @@
         <v>33.995225820952975</v>
       </c>
     </row>
-    <row r="207" spans="2:26">
+    <row r="207" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B207" s="1">
         <v>30000</v>
       </c>
@@ -61863,7 +61863,7 @@
         <v>11.088608157312487</v>
       </c>
     </row>
-    <row r="208" spans="2:26">
+    <row r="208" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B208" s="1">
         <v>40000</v>
       </c>
@@ -61964,7 +61964,7 @@
         <v>-8.7932615449543192</v>
       </c>
     </row>
-    <row r="209" spans="1:26">
+    <row r="209" spans="1:26" x14ac:dyDescent="0.15">
       <c r="B209" s="1">
         <v>50000</v>
       </c>
@@ -62065,7 +62065,7 @@
         <v>-25.999073858005577</v>
       </c>
     </row>
-    <row r="210" spans="1:26">
+    <row r="210" spans="1:26" x14ac:dyDescent="0.15">
       <c r="B210" s="1">
         <v>60000</v>
       </c>
@@ -62166,7 +62166,7 @@
         <v>-40.564972166969746</v>
       </c>
     </row>
-    <row r="211" spans="1:26">
+    <row r="211" spans="1:26" x14ac:dyDescent="0.15">
       <c r="B211" s="1">
         <v>70000</v>
       </c>
@@ -62267,7 +62267,7 @@
         <v>-52.63211954528748</v>
       </c>
     </row>
-    <row r="212" spans="1:26">
+    <row r="212" spans="1:26" x14ac:dyDescent="0.15">
       <c r="B212" s="1">
         <v>80000</v>
       </c>
@@ -62368,7 +62368,7 @@
         <v>-62.537280871225718</v>
       </c>
     </row>
-    <row r="213" spans="1:26">
+    <row r="213" spans="1:26" x14ac:dyDescent="0.15">
       <c r="B213" s="1">
         <v>90000</v>
       </c>
@@ -62469,7 +62469,7 @@
         <v>-70.696812128811956</v>
       </c>
     </row>
-    <row r="214" spans="1:26">
+    <row r="214" spans="1:26" x14ac:dyDescent="0.15">
       <c r="B214" s="1">
         <v>100000</v>
       </c>
@@ -62570,7 +62570,7 @@
         <v>-77.498565962477656</v>
       </c>
     </row>
-    <row r="215" spans="1:26">
+    <row r="215" spans="1:26" x14ac:dyDescent="0.15">
       <c r="B215" s="1">
         <v>200000</v>
       </c>
@@ -62671,7 +62671,7 @@
         <v>-113.15904264668734</v>
       </c>
     </row>
-    <row r="216" spans="1:26">
+    <row r="216" spans="1:26" x14ac:dyDescent="0.15">
       <c r="B216" s="1">
         <v>300000</v>
       </c>
@@ -62772,7 +62772,7 @@
         <v>-129.75654420956869</v>
       </c>
     </row>
-    <row r="217" spans="1:26">
+    <row r="217" spans="1:26" x14ac:dyDescent="0.15">
       <c r="B217" s="1">
         <v>400000</v>
       </c>
@@ -62873,7 +62873,7 @@
         <v>-140.01330194702967</v>
       </c>
     </row>
-    <row r="218" spans="1:26">
+    <row r="218" spans="1:26" x14ac:dyDescent="0.15">
       <c r="B218" s="1">
         <v>500000</v>
       </c>
@@ -62974,7 +62974,7 @@
         <v>-146.95470465329845</v>
       </c>
     </row>
-    <row r="219" spans="1:26">
+    <row r="219" spans="1:26" x14ac:dyDescent="0.15">
       <c r="B219" s="1">
         <v>600000</v>
       </c>
@@ -63075,7 +63075,7 @@
         <v>-151.9241771319671</v>
       </c>
     </row>
-    <row r="220" spans="1:26">
+    <row r="220" spans="1:26" x14ac:dyDescent="0.15">
       <c r="B220" s="1">
         <v>700000</v>
       </c>
@@ -63176,7 +63176,7 @@
         <v>-155.63619825593378</v>
       </c>
     </row>
-    <row r="221" spans="1:26">
+    <row r="221" spans="1:26" x14ac:dyDescent="0.15">
       <c r="B221" s="1">
         <v>800000</v>
       </c>
@@ -63277,7 +63277,7 @@
         <v>-158.50387837306428</v>
       </c>
     </row>
-    <row r="222" spans="1:26">
+    <row r="222" spans="1:26" x14ac:dyDescent="0.15">
       <c r="B222" s="1">
         <v>900000</v>
       </c>
@@ -63378,7 +63378,7 @@
         <v>-160.78047751837079</v>
       </c>
     </row>
-    <row r="223" spans="1:26" ht="15" thickBot="1">
+    <row r="223" spans="1:26" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B223" s="98">
         <v>1000000</v>
       </c>
@@ -63479,7 +63479,7 @@
         <v>-162.62876689683299</v>
       </c>
     </row>
-    <row r="224" spans="1:26">
+    <row r="224" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A224" s="82" t="s">
         <v>407</v>
       </c>
@@ -63584,7 +63584,7 @@
         <v>74.221919339621223</v>
       </c>
     </row>
-    <row r="225" spans="1:26">
+    <row r="225" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A225" t="s">
         <v>449</v>
       </c>
@@ -63689,7 +63689,7 @@
         <v>87.787386605967441</v>
       </c>
     </row>
-    <row r="226" spans="1:26">
+    <row r="226" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A226" t="s">
         <v>450</v>
       </c>
@@ -63794,7 +63794,7 @@
         <v>-124.96668437915375</v>
       </c>
     </row>
-    <row r="227" spans="1:26">
+    <row r="227" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A227" t="s">
         <v>451</v>
       </c>
@@ -63899,7 +63899,7 @@
         <v>87.779226086165551</v>
       </c>
     </row>
-    <row r="228" spans="1:26" ht="15" thickBot="1">
+    <row r="228" spans="1:26" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
         <v>452</v>
       </c>
@@ -64006,25 +64006,18 @@
     </row>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="B76:C77"/>
-    <mergeCell ref="D77:F77"/>
-    <mergeCell ref="J77:L77"/>
-    <mergeCell ref="BC166:BN166"/>
-    <mergeCell ref="BO166:BZ166"/>
-    <mergeCell ref="BC167:BE167"/>
-    <mergeCell ref="BF167:BH167"/>
-    <mergeCell ref="BI167:BK167"/>
-    <mergeCell ref="BL167:BN167"/>
-    <mergeCell ref="BO167:BQ167"/>
-    <mergeCell ref="BR167:BT167"/>
-    <mergeCell ref="BU167:BW167"/>
-    <mergeCell ref="BX167:BZ167"/>
-    <mergeCell ref="CD166:CO166"/>
-    <mergeCell ref="CA167:CC167"/>
-    <mergeCell ref="CD167:CF167"/>
-    <mergeCell ref="CG167:CI167"/>
-    <mergeCell ref="CJ167:CL167"/>
-    <mergeCell ref="CM167:CO167"/>
+    <mergeCell ref="X167:Z167"/>
+    <mergeCell ref="G77:I77"/>
+    <mergeCell ref="M77:N77"/>
+    <mergeCell ref="D76:T76"/>
+    <mergeCell ref="O77:Q77"/>
+    <mergeCell ref="R77:T77"/>
+    <mergeCell ref="U77:W77"/>
+    <mergeCell ref="R167:T167"/>
+    <mergeCell ref="M166:N166"/>
+    <mergeCell ref="O166:Q166"/>
+    <mergeCell ref="R166:T166"/>
+    <mergeCell ref="U167:W167"/>
     <mergeCell ref="D5:F6"/>
     <mergeCell ref="G5:I6"/>
     <mergeCell ref="J5:L6"/>
@@ -64041,18 +64034,25 @@
     <mergeCell ref="M167:N167"/>
     <mergeCell ref="O167:Q167"/>
     <mergeCell ref="AB167:AD167"/>
-    <mergeCell ref="X167:Z167"/>
-    <mergeCell ref="G77:I77"/>
-    <mergeCell ref="M77:N77"/>
-    <mergeCell ref="D76:T76"/>
-    <mergeCell ref="O77:Q77"/>
-    <mergeCell ref="R77:T77"/>
-    <mergeCell ref="U77:W77"/>
-    <mergeCell ref="R167:T167"/>
-    <mergeCell ref="M166:N166"/>
-    <mergeCell ref="O166:Q166"/>
-    <mergeCell ref="R166:T166"/>
-    <mergeCell ref="U167:W167"/>
+    <mergeCell ref="BR167:BT167"/>
+    <mergeCell ref="BU167:BW167"/>
+    <mergeCell ref="BX167:BZ167"/>
+    <mergeCell ref="CD166:CO166"/>
+    <mergeCell ref="CA167:CC167"/>
+    <mergeCell ref="CD167:CF167"/>
+    <mergeCell ref="CG167:CI167"/>
+    <mergeCell ref="CJ167:CL167"/>
+    <mergeCell ref="CM167:CO167"/>
+    <mergeCell ref="BC167:BE167"/>
+    <mergeCell ref="BF167:BH167"/>
+    <mergeCell ref="BI167:BK167"/>
+    <mergeCell ref="BL167:BN167"/>
+    <mergeCell ref="BO167:BQ167"/>
+    <mergeCell ref="B76:C77"/>
+    <mergeCell ref="D77:F77"/>
+    <mergeCell ref="J77:L77"/>
+    <mergeCell ref="BC166:BN166"/>
+    <mergeCell ref="BO166:BZ166"/>
   </mergeCells>
   <phoneticPr fontId="30"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -64066,7 +64066,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
   <phoneticPr fontId="30"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -64077,16 +64077,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:I48"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="34.6640625" style="12" customWidth="1"/>
-    <col min="2" max="2" width="9.1640625" style="5"/>
+    <col min="1" max="1" width="34.625" style="12" customWidth="1"/>
+    <col min="2" max="2" width="9.125" style="5"/>
     <col min="3" max="3" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.1640625" style="6"/>
-    <col min="5" max="5" width="9.1640625" style="13"/>
+    <col min="4" max="4" width="9.125" style="6"/>
+    <col min="5" max="5" width="9.125" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1" s="10" t="s">
         <v>17</v>
       </c>
@@ -64103,16 +64103,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A2" s="220" t="s">
         <v>91</v>
       </c>
-      <c r="B2" s="197"/>
-      <c r="C2" s="197"/>
-      <c r="D2" s="197"/>
+      <c r="B2" s="201"/>
+      <c r="C2" s="201"/>
+      <c r="D2" s="201"/>
       <c r="E2" s="221"/>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A3" s="12" t="s">
         <v>22</v>
       </c>
@@ -64124,7 +64124,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A4" s="12" t="s">
         <v>41</v>
       </c>
@@ -64136,7 +64136,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A5" s="12" t="s">
         <v>43</v>
       </c>
@@ -64147,7 +64147,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A6" s="12" t="s">
         <v>185</v>
       </c>
@@ -64158,7 +64158,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A7" s="12" t="s">
         <v>46</v>
       </c>
@@ -64169,7 +64169,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A8" s="12" t="s">
         <v>47</v>
       </c>
@@ -64180,7 +64180,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A9" s="12" t="s">
         <v>64</v>
       </c>
@@ -64192,7 +64192,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A10" s="12" t="s">
         <v>45</v>
       </c>
@@ -64206,7 +64206,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A11" s="12" t="s">
         <v>69</v>
       </c>
@@ -64217,7 +64217,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A12" s="12" t="s">
         <v>66</v>
       </c>
@@ -64228,7 +64228,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A13" s="12" t="s">
         <v>180</v>
       </c>
@@ -64240,7 +64240,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A14" s="12" t="s">
         <v>65</v>
       </c>
@@ -64251,7 +64251,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A15" s="12" t="s">
         <v>48</v>
       </c>
@@ -64263,7 +64263,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A16" s="12" t="s">
         <v>49</v>
       </c>
@@ -64274,7 +64274,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A17" s="12" t="s">
         <v>53</v>
       </c>
@@ -64286,7 +64286,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A18" s="12" t="s">
         <v>52</v>
       </c>
@@ -64297,7 +64297,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A19" s="12" t="s">
         <v>54</v>
       </c>
@@ -64309,7 +64309,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A20" s="12" t="s">
         <v>55</v>
       </c>
@@ -64321,7 +64321,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A21" s="12" t="s">
         <v>57</v>
       </c>
@@ -64333,7 +64333,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A22" s="12" t="s">
         <v>63</v>
       </c>
@@ -64345,7 +64345,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A23" s="12" t="s">
         <v>62</v>
       </c>
@@ -64357,7 +64357,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A24" s="12" t="s">
         <v>58</v>
       </c>
@@ -64369,7 +64369,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A25" s="12" t="s">
         <v>59</v>
       </c>
@@ -64381,7 +64381,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A26" s="12" t="s">
         <v>60</v>
       </c>
@@ -64393,7 +64393,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A27" s="12" t="s">
         <v>230</v>
       </c>
@@ -64405,7 +64405,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A28" s="12" t="s">
         <v>68</v>
       </c>
@@ -64416,7 +64416,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A29" s="12" t="s">
         <v>235</v>
       </c>
@@ -64428,7 +64428,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A30" s="12" t="s">
         <v>236</v>
       </c>
@@ -64440,7 +64440,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A31" s="12" t="s">
         <v>248</v>
       </c>
@@ -64452,7 +64452,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A32" s="12" t="s">
         <v>249</v>
       </c>
@@ -64464,7 +64464,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A33" s="12" t="s">
         <v>67</v>
       </c>
@@ -64476,7 +64476,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A34" s="12" t="s">
         <v>159</v>
       </c>
@@ -64487,7 +64487,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A36" s="12" t="s">
         <v>92</v>
       </c>
@@ -64501,7 +64501,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A37" s="12" t="s">
         <v>93</v>
       </c>
@@ -64515,7 +64515,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A38" s="12" t="s">
         <v>94</v>
       </c>
@@ -64529,7 +64529,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A39" s="12" t="s">
         <v>95</v>
       </c>
@@ -64543,7 +64543,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="40" spans="1:5">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A40" s="12" t="s">
         <v>96</v>
       </c>
@@ -64557,7 +64557,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="43" spans="1:5">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A43" s="12" t="s">
         <v>105</v>
       </c>
@@ -64568,7 +64568,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A44" s="12" t="s">
         <v>106</v>
       </c>
@@ -64579,7 +64579,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:5">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A46" s="12" t="s">
         <v>116</v>
       </c>
@@ -64590,7 +64590,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:5">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A48" s="12" t="s">
         <v>187</v>
       </c>
@@ -64617,9 +64617,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:G3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>171</v>
       </c>
@@ -64633,7 +64633,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15">
+    <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="43" t="s">
         <v>172</v>
       </c>
@@ -64647,7 +64647,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>173</v>
       </c>
@@ -64672,23 +64672,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:A4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="2" max="2" width="137.33203125" customWidth="1"/>
+    <col min="2" max="2" width="137.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="2" spans="1:1">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A2" t="str">
         <f>"schematic_1"</f>
         <v>schematic_1</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="343.5" customHeight="1"/>
+    <row r="4" spans="1:1" ht="343.5" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <phoneticPr fontId="30"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
